--- a/R63 Data.xlsx
+++ b/R63 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Documents\GitHub\r63-stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CEBB17-C06C-4DC8-9EFC-7426D6AD4378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D08E608-B825-4A89-A9F2-0D6B2DD28F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">BA!$A$1:$AG$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Old Bow'!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Old Bow'!$A$1:$AD$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="123">
   <si>
     <t>Player</t>
   </si>
@@ -665,7 +665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -892,6 +892,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1208,6 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1328,6 +1332,12 @@
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D2" s="34">
         <v>190</v>
       </c>
@@ -1418,6 +1428,12 @@
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D3" s="34">
         <v>5</v>
       </c>
@@ -1508,6 +1524,12 @@
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D4" s="34">
         <v>98</v>
       </c>
@@ -1598,6 +1620,12 @@
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D5" s="34">
         <v>213</v>
       </c>
@@ -1688,6 +1716,12 @@
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B6" s="81" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D6" s="36">
         <v>5</v>
       </c>
@@ -1778,6 +1812,12 @@
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="B7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D7" s="34">
         <v>117</v>
       </c>
@@ -1871,7 +1911,9 @@
       <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D8" s="34">
         <v>161</v>
       </c>
@@ -1965,7 +2007,9 @@
       <c r="B9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D9" s="34">
         <v>153</v>
       </c>
@@ -2056,8 +2100,12 @@
       <c r="A10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D10" s="34">
         <v>0</v>
       </c>
@@ -2144,6 +2192,12 @@
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D11" s="34">
         <v>67</v>
       </c>
@@ -2234,6 +2288,12 @@
       <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D12" s="34">
         <v>26</v>
       </c>
@@ -2324,6 +2384,12 @@
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="B13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D13" s="34">
         <v>5</v>
       </c>
@@ -2414,6 +2480,12 @@
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D14" s="36">
         <v>12</v>
       </c>
@@ -2507,6 +2579,9 @@
       <c r="B15" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="C15" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D15" s="34">
         <v>167</v>
       </c>
@@ -2600,6 +2675,9 @@
       <c r="B16" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="C16" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D16" s="34">
         <v>132</v>
       </c>
@@ -2690,6 +2768,10 @@
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D17" s="34">
         <v>160</v>
       </c>
@@ -2783,6 +2865,9 @@
       <c r="B18" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D18" s="34">
         <v>178</v>
       </c>
@@ -2876,7 +2961,9 @@
       <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D19" s="34">
         <v>43</v>
       </c>
@@ -2967,6 +3054,12 @@
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D20" s="34">
         <v>150</v>
       </c>
@@ -3057,6 +3150,12 @@
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D21" s="34">
         <v>196</v>
       </c>
@@ -3147,6 +3246,12 @@
       <c r="A22" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="B22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D22" s="34">
         <v>36</v>
       </c>
@@ -3233,7 +3338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
@@ -3333,6 +3438,12 @@
       <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D24" s="34">
         <v>445</v>
       </c>
@@ -3423,6 +3534,12 @@
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="B25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D25" s="36">
         <v>4</v>
       </c>
@@ -3516,7 +3633,9 @@
       <c r="B26" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D26" s="34">
         <v>581</v>
       </c>
@@ -3607,6 +3726,12 @@
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D27" s="34">
         <v>260</v>
       </c>
@@ -3700,7 +3825,9 @@
       <c r="B28" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D28" s="34">
         <v>65</v>
       </c>
@@ -3794,6 +3921,9 @@
       <c r="B29" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="C29" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D29" s="34">
         <v>210</v>
       </c>
@@ -3884,6 +4014,12 @@
       <c r="A30" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="B30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D30" s="34">
         <v>13</v>
       </c>
@@ -3974,6 +4110,12 @@
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="B31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D31" s="34">
         <v>37</v>
       </c>
@@ -4064,6 +4206,12 @@
       <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="B32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D32" s="34">
         <v>534</v>
       </c>
@@ -4154,6 +4302,12 @@
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D33" s="34">
         <v>274</v>
       </c>
@@ -4244,6 +4398,12 @@
       <c r="A34" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="B34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D34" s="34">
         <v>268</v>
       </c>
@@ -4330,7 +4490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
@@ -4430,6 +4590,12 @@
       <c r="A36" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D36" s="34">
         <v>33</v>
       </c>
@@ -4520,6 +4686,12 @@
       <c r="A37" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="B37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D37" s="38">
         <v>65</v>
       </c>
@@ -4607,7 +4779,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD1" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}"/>
+  <autoFilter ref="A1:AD37" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}">
+    <filterColumn colId="2">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/R63 Data.xlsx
+++ b/R63 Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Documents\GitHub\r63-stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Downloads\excel-filter-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D08E608-B825-4A89-A9F2-0D6B2DD28F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2B7C7B-03C2-49FC-87AA-47E03B730905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
   </bookViews>
   <sheets>
     <sheet name="Old Bow" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Match Analyzer Old Bow" sheetId="4" r:id="rId3"/>
     <sheet name="BA" sheetId="3" r:id="rId4"/>
     <sheet name="BA comments" sheetId="6" r:id="rId5"/>
-    <sheet name="Match Analyzer BA" sheetId="5" r:id="rId6"/>
+    <sheet name="Match Analyzer BA" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">BA!$A$1:$AG$46</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="126">
   <si>
     <t>Player</t>
   </si>
@@ -404,6 +404,15 @@
   <si>
     <t>*1/31 match not added due to incomplete data</t>
   </si>
+  <si>
+    <t>Map %</t>
+  </si>
+  <si>
+    <t>Round %</t>
+  </si>
+  <si>
+    <t>Match %</t>
+  </si>
 </sst>
 </file>
 
@@ -665,7 +674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -861,9 +870,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -874,6 +880,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -893,7 +902,25 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1211,7 +1238,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AD37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1262,7 +1288,7 @@
         <v>98</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="J1" s="50" t="s">
         <v>64</v>
@@ -1271,7 +1297,7 @@
         <v>101</v>
       </c>
       <c r="L1" s="23" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="M1" s="51" t="s">
         <v>99</v>
@@ -1280,7 +1306,7 @@
         <v>100</v>
       </c>
       <c r="O1" s="46" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="P1" s="31" t="s">
         <v>41</v>
@@ -1716,7 +1742,7 @@
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="73" t="s">
         <v>79</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3338,7 +3364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
@@ -4490,7 +4516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
@@ -4779,11 +4805,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD37" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}">
-    <filterColumn colId="2">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AD37" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4933,46 +4955,46 @@
       <c r="O2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="S2" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="21" t="s">
+      <c r="T2" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="21" t="s">
+      <c r="U2" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="V2" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="W2" s="22" t="s">
+      <c r="W2" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="21" t="s">
+      <c r="X2" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" s="21" t="s">
+      <c r="Y2" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" s="21" t="s">
+      <c r="Z2" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AA2" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="AB2" s="21" t="s">
+      <c r="AB2" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AC2" s="87" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4981,55 +5003,55 @@
         <v>75</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="D3" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>17.272727272727273</v>
       </c>
       <c r="E3" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F3" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H3" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="I3" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J3" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K3" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0.43181818181818182</v>
       </c>
       <c r="L3" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="M3" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="N3" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.75</v>
+        <v>0.46629213483146065</v>
       </c>
       <c r="O3" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5041,7 +5063,7 @@
       </c>
       <c r="Q3" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5049,7 +5071,7 @@
       </c>
       <c r="S3" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5057,11 +5079,11 @@
       </c>
       <c r="U3" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W3" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5069,11 +5091,11 @@
       </c>
       <c r="X3" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z3" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$3, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5095,19 +5117,19 @@
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C4" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D4" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>17.272727272727273</v>
+        <v>20</v>
       </c>
       <c r="E4" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F4" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5115,35 +5137,35 @@
       </c>
       <c r="G4" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H4" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.36363636363636365</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J4" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K4" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.43181818181818182</v>
+        <v>0.46875</v>
       </c>
       <c r="L4" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="M4" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="N4" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.46629213483146065</v>
+        <v>0.47445255474452552</v>
       </c>
       <c r="O4" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5151,7 +5173,7 @@
       </c>
       <c r="P4" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5159,11 +5181,11 @@
       </c>
       <c r="R4" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5171,11 +5193,11 @@
       </c>
       <c r="U4" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V4" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5183,11 +5205,11 @@
       </c>
       <c r="X4" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5209,35 +5231,35 @@
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="7" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C5" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>98</v>
+        <v>274</v>
       </c>
       <c r="D5" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9.8000000000000007</v>
+        <v>22.833333333333332</v>
       </c>
       <c r="E5" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F5" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="I5" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J5" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5245,39 +5267,39 @@
       </c>
       <c r="K5" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.51282051282051277</v>
+        <v>0.61224489795918369</v>
       </c>
       <c r="L5" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="M5" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="N5" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.52229299363057324</v>
+        <v>0.53588516746411485</v>
       </c>
       <c r="O5" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5285,11 +5307,11 @@
       </c>
       <c r="U5" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V5" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5297,11 +5319,11 @@
       </c>
       <c r="X5" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5309,7 +5331,7 @@
       </c>
       <c r="AA5" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5323,75 +5345,75 @@
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C6" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="D6" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>11.210526315789474</v>
+        <v>13.636363636363637</v>
       </c>
       <c r="E6" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F6" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H6" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.31578947368421051</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="I6" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J6" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K6" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.40259740259740262</v>
+        <v>0.56521739130434778</v>
       </c>
       <c r="L6" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="M6" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="N6" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.45283018867924529</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="O6" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5399,23 +5421,23 @@
       </c>
       <c r="U6" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V6" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z6" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5423,37 +5445,37 @@
       </c>
       <c r="AA6" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="14">
         <f>INDEX('Old Bow'!X2:X37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="80"/>
       <c r="B7" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="D7" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>14.625</v>
+        <v>11.76923076923077</v>
       </c>
       <c r="E7" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5461,39 +5483,39 @@
       </c>
       <c r="H7" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.625</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="I7" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J7" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K7" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.625</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="L7" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="M7" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="N7" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.57777777777777772</v>
+        <v>0.58371040723981904</v>
       </c>
       <c r="O7" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5501,11 +5523,11 @@
       </c>
       <c r="R7" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5513,27 +5535,27 @@
       </c>
       <c r="U7" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V7" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W7" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X7" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA7" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5541,77 +5563,77 @@
       </c>
       <c r="AB7" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="14">
         <f>INDEX('Old Bow'!X2:X37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="80"/>
       <c r="B8" s="7" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C8" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="D8" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>13.416666666666666</v>
+        <v>2.6</v>
       </c>
       <c r="E8" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F8" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G8" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I8" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J8" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K8" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.46938775510204084</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="L8" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="M8" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="N8" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.48076923076923078</v>
+        <v>0.51428571428571423</v>
       </c>
       <c r="O8" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P8" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5619,7 +5641,7 @@
       </c>
       <c r="S8" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5627,7 +5649,7 @@
       </c>
       <c r="U8" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V8" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5635,19 +5657,19 @@
       </c>
       <c r="W8" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5893,21 +5915,21 @@
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D11" s="8">
         <f>SUM(D3:D10)</f>
-        <v>71.324920255183414</v>
+        <v>88.111655011655017</v>
       </c>
       <c r="H11" s="9">
         <f>AVERAGE(H3:H10)</f>
-        <v>0.56740430622009574</v>
+        <v>0.60320512820512817</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="9">
         <f>AVERAGE(K3:K10)</f>
-        <v>0.57360397538968966</v>
+        <v>0.55444052061498772</v>
       </c>
       <c r="N11" s="9">
         <f>AVERAGE(N3:N10)</f>
-        <v>0.54166038761471469</v>
+        <v>0.51733962387858612</v>
       </c>
       <c r="O11" s="5">
         <f>SUM(O3:O10)</f>
@@ -5915,19 +5937,19 @@
       </c>
       <c r="P11" s="5">
         <f t="shared" ref="P11:AC11" si="0">SUM(P3:P10)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="0"/>
@@ -5935,15 +5957,15 @@
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W11" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X11" s="5">
         <f t="shared" si="0"/>
@@ -5959,7 +5981,7 @@
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="5">
         <f t="shared" si="0"/>
@@ -6101,63 +6123,63 @@
         <v>77</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C17" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>581</v>
       </c>
       <c r="D17" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>27.666666666666668</v>
       </c>
       <c r="E17" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="F17" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G17" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H17" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I17" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J17" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K17" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0.56470588235294117</v>
       </c>
       <c r="L17" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9</v>
+        <v>188</v>
       </c>
       <c r="M17" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="N17" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.75</v>
+        <v>0.53561253561253563</v>
       </c>
       <c r="O17" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P17" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6165,121 +6187,121 @@
       </c>
       <c r="R17" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S17" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T17" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V17" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W17" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y17" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB17" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="14">
         <f>INDEX('Old Bow'!X2:X37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="76"/>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C18" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D18" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E18" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F18" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I18" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J18" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K18" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="L18" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="M18" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="N18" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.18181818181818182</v>
+        <v>0.51412429378531077</v>
       </c>
       <c r="O18" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6291,11 +6313,11 @@
       </c>
       <c r="U18" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6303,11 +6325,11 @@
       </c>
       <c r="X18" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6329,59 +6351,59 @@
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="76"/>
       <c r="B19" s="7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="D19" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="E19" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F19" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I19" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J19" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K19" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>0.40740740740740738</v>
       </c>
       <c r="L19" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M19" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="N19" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.30769230769230771</v>
+        <v>0.45045045045045046</v>
       </c>
       <c r="O19" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6389,15 +6411,15 @@
       </c>
       <c r="Q19" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6405,11 +6427,11 @@
       </c>
       <c r="U19" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6417,7 +6439,7 @@
       </c>
       <c r="X19" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6443,87 +6465,87 @@
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="76"/>
       <c r="B20" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D20" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>11.210526315789474</v>
+        <v>13.066666666666666</v>
       </c>
       <c r="E20" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.31578947368421051</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I20" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J20" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K20" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.40259740259740262</v>
+        <v>0.46031746031746029</v>
       </c>
       <c r="L20" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="M20" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="N20" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.45283018867924529</v>
+        <v>0.48496240601503759</v>
       </c>
       <c r="O20" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P20" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S20" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V20" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W20" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6531,11 +6553,11 @@
       </c>
       <c r="X20" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6543,33 +6565,33 @@
       </c>
       <c r="AA20" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="14">
         <f>INDEX('Old Bow'!X2:X37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="76"/>
       <c r="B21" s="7" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C21" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="D21" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>23</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E21" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F21" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6585,43 +6607,43 @@
       </c>
       <c r="I21" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K21" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.51162790697674421</v>
+        <v>0.51282051282051277</v>
       </c>
       <c r="L21" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="M21" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="N21" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.49714285714285716</v>
+        <v>0.52229299363057324</v>
       </c>
       <c r="O21" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6633,19 +6655,19 @@
       </c>
       <c r="U21" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V21" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X21" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6653,11 +6675,11 @@
       </c>
       <c r="Z21" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6671,63 +6693,63 @@
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="76"/>
       <c r="B22" s="7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>457</v>
+        <v>132</v>
       </c>
       <c r="D22" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>25.388888888888889</v>
+        <v>9.4285714285714288</v>
       </c>
       <c r="E22" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="F22" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G22" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.55555555555555558</v>
+        <v>0.5</v>
       </c>
       <c r="I22" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J22" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K22" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.52054794520547942</v>
+        <v>0.48214285714285715</v>
       </c>
       <c r="L22" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="M22" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="N22" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.50162866449511401</v>
+        <v>0.49367088607594939</v>
       </c>
       <c r="O22" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P22" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="26">
         <f>INDEX('Old Bow'!AC2:AC37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6735,35 +6757,35 @@
       </c>
       <c r="R22" s="26">
         <f>INDEX('Old Bow'!Q2:Q37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S22" s="26">
         <f>INDEX('Old Bow'!AB2:AB37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T22" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V22" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W22" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z22" s="26">
         <f>INDEX('Old Bow'!T2:T37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6771,7 +6793,7 @@
       </c>
       <c r="AA22" s="26">
         <f>INDEX('Old Bow'!Z2:Z37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="26">
         <f>INDEX('Old Bow'!Y2:Y37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -7013,65 +7035,65 @@
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D25" s="8">
         <f>SUM(D17:D24)</f>
-        <v>74.599415204678365</v>
+        <v>95.533333333333331</v>
       </c>
       <c r="H25" s="9">
         <f>AVERAGE(H17:H24)</f>
-        <v>0.41189083820662775</v>
+        <v>0.48095238095238085</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="9">
         <f>AVERAGE(K17:K24)</f>
-        <v>0.40579554246327104</v>
+        <v>0.49186727397511709</v>
       </c>
       <c r="N25" s="9">
         <f>AVERAGE(N17:N24)</f>
-        <v>0.4485186999712843</v>
+        <v>0.50018559426164277</v>
       </c>
       <c r="O25" s="5">
         <f>SUM(O17:O24)</f>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P25" s="5">
         <f t="shared" ref="P25" si="1">SUM(P17:P24)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" ref="Q25" si="2">SUM(Q17:Q24)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" ref="R25" si="3">SUM(R17:R24)</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S25" s="5">
         <f t="shared" ref="S25" si="4">SUM(S17:S24)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T25" s="5">
         <f t="shared" ref="T25" si="5">SUM(T17:T24)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" ref="U25" si="6">SUM(U17:U24)</f>
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" ref="V25" si="7">SUM(V17:V24)</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="W25" s="5">
         <f t="shared" ref="W25" si="8">SUM(W17:W24)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X25" s="5">
         <f t="shared" ref="X25" si="9">SUM(X17:X24)</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Y25" s="5">
         <f t="shared" ref="Y25" si="10">SUM(Y17:Y24)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z25" s="5">
         <f t="shared" ref="Z25" si="11">SUM(Z17:Z24)</f>
@@ -7079,7 +7101,7 @@
       </c>
       <c r="AA25" s="5">
         <f t="shared" ref="AA25" si="12">SUM(AA17:AA24)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB25" s="5">
         <f t="shared" ref="AB25" si="13">SUM(AB17:AB24)</f>
@@ -7162,11 +7184,11 @@
       </c>
       <c r="C34" s="13" t="str">
         <f>INDEX(O2:AC2, MATCH(LARGE(O11:AC11, 1), O11:AC11, 0))</f>
-        <v>Training</v>
+        <v>Garage</v>
       </c>
       <c r="D34" s="14" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 1), O25:AC25, 0))</f>
-        <v>Training</v>
+        <v>Garage</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
@@ -7175,11 +7197,11 @@
       </c>
       <c r="C35" s="13" t="str">
         <f>INDEX(O2:AC2, MATCH(LARGE(O11:AC11, 2), O11:AC11, 0))</f>
-        <v>Garage</v>
+        <v>Training</v>
       </c>
       <c r="D35" s="14" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 2), O25:AC25, 0))</f>
-        <v>Garage</v>
+        <v>Scharins</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7297,7 +7319,7 @@
         <v>98</v>
       </c>
       <c r="G1" s="46" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="H1" s="51" t="s">
         <v>64</v>
@@ -7306,7 +7328,7 @@
         <v>101</v>
       </c>
       <c r="J1" s="46" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="K1" s="51" t="s">
         <v>99</v>
@@ -7315,66 +7337,66 @@
         <v>100</v>
       </c>
       <c r="M1" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="N1" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="O1" s="71" t="s">
+      <c r="O1" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="71" t="s">
+      <c r="P1" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="72" t="s">
+      <c r="Q1" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="R1" s="72" t="s">
+      <c r="R1" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="S1" s="71" t="s">
+      <c r="S1" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="72" t="s">
+      <c r="T1" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="71" t="s">
+      <c r="U1" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="V1" s="72" t="s">
+      <c r="V1" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="71" t="s">
+      <c r="W1" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="X1" s="71" t="s">
+      <c r="X1" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" s="72" t="s">
+      <c r="Y1" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="71" t="s">
+      <c r="Z1" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="AA1" s="72" t="s">
+      <c r="AA1" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="72" t="s">
+      <c r="AB1" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="AC1" s="71" t="s">
+      <c r="AC1" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="AD1" s="71" t="s">
+      <c r="AD1" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="71" t="s">
+      <c r="AE1" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="AF1" s="72" t="s">
+      <c r="AF1" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="73" t="s">
+      <c r="AG1" s="72" t="s">
         <v>96</v>
       </c>
     </row>
@@ -7398,7 +7420,7 @@
       <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="G2" s="41">
+      <c r="G2" s="83">
         <f t="shared" ref="G2:G12" si="1">E2/(E2+F2)</f>
         <v>0.42857142857142855</v>
       </c>
@@ -7408,7 +7430,7 @@
       <c r="I2" s="2">
         <v>14</v>
       </c>
-      <c r="J2" s="41">
+      <c r="J2" s="83">
         <f t="shared" ref="J2:J12" si="2">H2/(H2+I2)</f>
         <v>0.54838709677419351</v>
       </c>
@@ -7418,7 +7440,7 @@
       <c r="L2" s="2">
         <v>62</v>
       </c>
-      <c r="M2" s="41">
+      <c r="M2" s="83">
         <f t="shared" ref="M2:M12" si="3">K2/(K2+L2)</f>
         <v>0.52671755725190839</v>
       </c>
@@ -7503,7 +7525,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="83">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7513,7 +7535,7 @@
       <c r="I3" s="2">
         <v>3</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="83">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
@@ -7523,7 +7545,7 @@
       <c r="L3" s="2">
         <v>11</v>
       </c>
-      <c r="M3" s="41">
+      <c r="M3" s="83">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
@@ -7608,7 +7630,7 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -7618,7 +7640,7 @@
       <c r="I4" s="2">
         <v>5</v>
       </c>
-      <c r="J4" s="41">
+      <c r="J4" s="83">
         <f t="shared" si="2"/>
         <v>0.44444444444444442</v>
       </c>
@@ -7628,7 +7650,7 @@
       <c r="L4" s="2">
         <v>20</v>
       </c>
-      <c r="M4" s="41">
+      <c r="M4" s="83">
         <f t="shared" si="3"/>
         <v>0.42857142857142855</v>
       </c>
@@ -7713,7 +7735,7 @@
       <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="83">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7723,7 +7745,7 @@
       <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="83">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
@@ -7733,7 +7755,7 @@
       <c r="L5" s="1">
         <v>11</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="83">
         <f t="shared" si="3"/>
         <v>0.42105263157894735</v>
       </c>
@@ -7818,7 +7840,7 @@
       <c r="F6" s="2">
         <v>10</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="83">
         <f t="shared" si="1"/>
         <v>0.375</v>
       </c>
@@ -7828,7 +7850,7 @@
       <c r="I6" s="2">
         <v>38</v>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="83">
         <f t="shared" si="2"/>
         <v>0.44117647058823528</v>
       </c>
@@ -7838,7 +7860,7 @@
       <c r="L6" s="2">
         <v>144</v>
       </c>
-      <c r="M6" s="41">
+      <c r="M6" s="83">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
@@ -7923,7 +7945,7 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="83">
         <f t="shared" si="1"/>
         <v>0.81818181818181823</v>
       </c>
@@ -7933,7 +7955,7 @@
       <c r="I7" s="2">
         <v>16</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="83">
         <f t="shared" si="2"/>
         <v>0.65217391304347827</v>
       </c>
@@ -7943,7 +7965,7 @@
       <c r="L7" s="2">
         <v>79</v>
       </c>
-      <c r="M7" s="41">
+      <c r="M7" s="83">
         <f t="shared" si="3"/>
         <v>0.572972972972973</v>
       </c>
@@ -8028,7 +8050,7 @@
       <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="83">
         <f t="shared" si="1"/>
         <v>0.55555555555555558</v>
       </c>
@@ -8038,7 +8060,7 @@
       <c r="I8" s="2">
         <v>20</v>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="83">
         <f t="shared" si="2"/>
         <v>0.48717948717948717</v>
       </c>
@@ -8048,7 +8070,7 @@
       <c r="L8" s="2">
         <v>84</v>
       </c>
-      <c r="M8" s="41">
+      <c r="M8" s="83">
         <f t="shared" si="3"/>
         <v>0.48780487804878048</v>
       </c>
@@ -8133,7 +8155,7 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="83">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8143,7 +8165,7 @@
       <c r="I9" s="2">
         <v>5</v>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="83">
         <f t="shared" si="2"/>
         <v>0.58333333333333337</v>
       </c>
@@ -8153,7 +8175,7 @@
       <c r="L9" s="2">
         <v>19</v>
       </c>
-      <c r="M9" s="41">
+      <c r="M9" s="83">
         <f t="shared" si="3"/>
         <v>0.58695652173913049</v>
       </c>
@@ -8238,7 +8260,7 @@
       <c r="F10" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="83">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
@@ -8248,7 +8270,7 @@
       <c r="I10" s="1">
         <v>11</v>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="83">
         <f t="shared" si="2"/>
         <v>0.3888888888888889</v>
       </c>
@@ -8258,7 +8280,7 @@
       <c r="L10" s="1">
         <v>39</v>
       </c>
-      <c r="M10" s="41">
+      <c r="M10" s="83">
         <f t="shared" si="3"/>
         <v>0.44285714285714284</v>
       </c>
@@ -8343,7 +8365,7 @@
       <c r="F11" s="2">
         <v>2</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -8353,7 +8375,7 @@
       <c r="I11" s="2">
         <v>9</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="83">
         <f t="shared" si="2"/>
         <v>0.52631578947368418</v>
       </c>
@@ -8363,7 +8385,7 @@
       <c r="L11" s="2">
         <v>41</v>
       </c>
-      <c r="M11" s="41">
+      <c r="M11" s="83">
         <f t="shared" si="3"/>
         <v>0.48749999999999999</v>
       </c>
@@ -8448,7 +8470,7 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="83">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8458,7 +8480,7 @@
       <c r="I12" s="1">
         <v>3</v>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="83">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
@@ -8468,7 +8490,7 @@
       <c r="L12" s="1">
         <v>13</v>
       </c>
-      <c r="M12" s="41">
+      <c r="M12" s="83">
         <f t="shared" si="3"/>
         <v>0.43478260869565216</v>
       </c>
@@ -8552,7 +8574,7 @@
       <c r="F13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="83" t="s">
         <v>79</v>
       </c>
       <c r="H13" s="36">
@@ -8561,7 +8583,7 @@
       <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="83" t="s">
         <v>79</v>
       </c>
       <c r="K13" s="36">
@@ -8570,7 +8592,7 @@
       <c r="L13" s="1">
         <v>0</v>
       </c>
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="83" t="s">
         <v>79</v>
       </c>
       <c r="N13" s="36">
@@ -8654,7 +8676,7 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="83">
         <f t="shared" ref="G14:G46" si="5">E14/(E14+F14)</f>
         <v>0</v>
       </c>
@@ -8664,7 +8686,7 @@
       <c r="I14" s="2">
         <v>3</v>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="83">
         <f t="shared" ref="J14:J46" si="6">H14/(H14+I14)</f>
         <v>0.25</v>
       </c>
@@ -8674,7 +8696,7 @@
       <c r="L14" s="2">
         <v>9</v>
       </c>
-      <c r="M14" s="41">
+      <c r="M14" s="83">
         <f t="shared" ref="M14:M46" si="7">K14/(K14+L14)</f>
         <v>0.4</v>
       </c>
@@ -8759,7 +8781,7 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="83">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -8769,7 +8791,7 @@
       <c r="I15" s="2">
         <v>3</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="83">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -8779,7 +8801,7 @@
       <c r="L15" s="2">
         <v>9</v>
       </c>
-      <c r="M15" s="41">
+      <c r="M15" s="83">
         <f t="shared" si="7"/>
         <v>0.30769230769230771</v>
       </c>
@@ -8864,7 +8886,7 @@
       <c r="F16" s="2">
         <v>1</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="83">
         <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8874,7 +8896,7 @@
       <c r="I16" s="2">
         <v>5</v>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="83">
         <f t="shared" si="6"/>
         <v>0.61538461538461542</v>
       </c>
@@ -8884,7 +8906,7 @@
       <c r="L16" s="2">
         <v>27</v>
       </c>
-      <c r="M16" s="41">
+      <c r="M16" s="83">
         <f t="shared" si="7"/>
         <v>0.5423728813559322</v>
       </c>
@@ -8969,7 +8991,7 @@
       <c r="F17" s="2">
         <v>7</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="83">
         <f t="shared" si="5"/>
         <v>0.58823529411764708</v>
       </c>
@@ -8979,7 +9001,7 @@
       <c r="I17" s="2">
         <v>33</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="83">
         <f t="shared" si="6"/>
         <v>0.54166666666666663</v>
       </c>
@@ -8989,7 +9011,7 @@
       <c r="L17" s="2">
         <v>152</v>
       </c>
-      <c r="M17" s="41">
+      <c r="M17" s="83">
         <f t="shared" si="7"/>
         <v>0.51592356687898089</v>
       </c>
@@ -9074,7 +9096,7 @@
       <c r="F18" s="2">
         <v>4</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="83">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
@@ -9084,7 +9106,7 @@
       <c r="I18" s="2">
         <v>14</v>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="83">
         <f t="shared" si="6"/>
         <v>0.36363636363636365</v>
       </c>
@@ -9094,7 +9116,7 @@
       <c r="L18" s="2">
         <v>52</v>
       </c>
-      <c r="M18" s="41">
+      <c r="M18" s="83">
         <f t="shared" si="7"/>
         <v>0.39534883720930231</v>
       </c>
@@ -9179,7 +9201,7 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="83">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
@@ -9189,7 +9211,7 @@
       <c r="I19" s="2">
         <v>9</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="83">
         <f t="shared" si="6"/>
         <v>0.60869565217391308</v>
       </c>
@@ -9199,7 +9221,7 @@
       <c r="L19" s="2">
         <v>40</v>
       </c>
-      <c r="M19" s="41">
+      <c r="M19" s="83">
         <f t="shared" si="7"/>
         <v>0.56521739130434778</v>
       </c>
@@ -9284,7 +9306,7 @@
       <c r="F20" s="2">
         <v>4</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="83">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
@@ -9294,7 +9316,7 @@
       <c r="I20" s="2">
         <v>19</v>
       </c>
-      <c r="J20" s="41">
+      <c r="J20" s="83">
         <f t="shared" si="6"/>
         <v>0.44117647058823528</v>
       </c>
@@ -9304,7 +9326,7 @@
       <c r="L20" s="2">
         <v>78</v>
       </c>
-      <c r="M20" s="41">
+      <c r="M20" s="83">
         <f t="shared" si="7"/>
         <v>0.48684210526315791</v>
       </c>
@@ -9389,7 +9411,7 @@
       <c r="F21" s="1">
         <v>0</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -9399,7 +9421,7 @@
       <c r="I21" s="1">
         <v>4</v>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="83">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
@@ -9409,7 +9431,7 @@
       <c r="L21" s="1">
         <v>19</v>
       </c>
-      <c r="M21" s="41">
+      <c r="M21" s="83">
         <f t="shared" si="7"/>
         <v>0.55813953488372092</v>
       </c>
@@ -9494,7 +9516,7 @@
       <c r="F22" s="2">
         <v>8</v>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="83">
         <f t="shared" si="5"/>
         <v>0.33333333333333331</v>
       </c>
@@ -9504,7 +9526,7 @@
       <c r="I22" s="2">
         <v>31</v>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="83">
         <f t="shared" si="6"/>
         <v>0.43636363636363634</v>
       </c>
@@ -9514,7 +9536,7 @@
       <c r="L22" s="2">
         <v>116</v>
       </c>
-      <c r="M22" s="41">
+      <c r="M22" s="83">
         <f t="shared" si="7"/>
         <v>0.49122807017543857</v>
       </c>
@@ -9599,7 +9621,7 @@
       <c r="F23" s="2">
         <v>5</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="83">
         <f t="shared" si="5"/>
         <v>0.44444444444444442</v>
       </c>
@@ -9609,7 +9631,7 @@
       <c r="I23" s="2">
         <v>19</v>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="83">
         <f t="shared" si="6"/>
         <v>0.47222222222222221</v>
       </c>
@@ -9619,7 +9641,7 @@
       <c r="L23" s="2">
         <v>78</v>
       </c>
-      <c r="M23" s="41">
+      <c r="M23" s="83">
         <f t="shared" si="7"/>
         <v>0.4935064935064935</v>
       </c>
@@ -9704,7 +9726,7 @@
       <c r="F24" s="2">
         <v>5</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="83">
         <f t="shared" si="5"/>
         <v>0.375</v>
       </c>
@@ -9714,7 +9736,7 @@
       <c r="I24" s="2">
         <v>17</v>
       </c>
-      <c r="J24" s="41">
+      <c r="J24" s="83">
         <f t="shared" si="6"/>
         <v>0.46875</v>
       </c>
@@ -9724,7 +9746,7 @@
       <c r="L24" s="2">
         <v>68</v>
       </c>
-      <c r="M24" s="41">
+      <c r="M24" s="83">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
@@ -9809,7 +9831,7 @@
       <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="83">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -9819,7 +9841,7 @@
       <c r="I25" s="2">
         <v>3</v>
       </c>
-      <c r="J25" s="41">
+      <c r="J25" s="83">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -9829,7 +9851,7 @@
       <c r="L25" s="2">
         <v>9</v>
       </c>
-      <c r="M25" s="41">
+      <c r="M25" s="83">
         <f t="shared" si="7"/>
         <v>0.18181818181818182</v>
       </c>
@@ -9914,7 +9936,7 @@
       <c r="F26" s="2">
         <v>3</v>
       </c>
-      <c r="G26" s="41">
+      <c r="G26" s="83">
         <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
@@ -9924,7 +9946,7 @@
       <c r="I26" s="2">
         <v>11</v>
       </c>
-      <c r="J26" s="41">
+      <c r="J26" s="83">
         <f t="shared" si="6"/>
         <v>0.42105263157894735</v>
       </c>
@@ -9934,7 +9956,7 @@
       <c r="L26" s="2">
         <v>40</v>
       </c>
-      <c r="M26" s="41">
+      <c r="M26" s="83">
         <f t="shared" si="7"/>
         <v>0.44444444444444442</v>
       </c>
@@ -10019,7 +10041,7 @@
       <c r="F27" s="2">
         <v>5</v>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="83">
         <f t="shared" si="5"/>
         <v>0.2857142857142857</v>
       </c>
@@ -10029,7 +10051,7 @@
       <c r="I27" s="2">
         <v>20</v>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="83">
         <f t="shared" si="6"/>
         <v>0.44444444444444442</v>
       </c>
@@ -10039,7 +10061,7 @@
       <c r="L27" s="2">
         <v>83</v>
       </c>
-      <c r="M27" s="41">
+      <c r="M27" s="83">
         <f t="shared" si="7"/>
         <v>0.4713375796178344</v>
       </c>
@@ -10124,7 +10146,7 @@
       <c r="F28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -10134,7 +10156,7 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="41">
+      <c r="J28" s="83">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -10144,7 +10166,7 @@
       <c r="L28" s="2">
         <v>5</v>
       </c>
-      <c r="M28" s="41">
+      <c r="M28" s="83">
         <f t="shared" si="7"/>
         <v>0.6428571428571429</v>
       </c>
@@ -10229,7 +10251,7 @@
       <c r="F29" s="2">
         <v>2</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="83">
         <f t="shared" si="5"/>
         <v>0.33333333333333331</v>
       </c>
@@ -10239,7 +10261,7 @@
       <c r="I29" s="2">
         <v>8</v>
       </c>
-      <c r="J29" s="41">
+      <c r="J29" s="83">
         <f t="shared" si="6"/>
         <v>0.46666666666666667</v>
       </c>
@@ -10249,7 +10271,7 @@
       <c r="L29" s="2">
         <v>35</v>
       </c>
-      <c r="M29" s="41">
+      <c r="M29" s="83">
         <f t="shared" si="7"/>
         <v>0.44444444444444442</v>
       </c>
@@ -10334,7 +10356,7 @@
       <c r="F30" s="2">
         <v>6</v>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="83">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
@@ -10344,7 +10366,7 @@
       <c r="I30" s="2">
         <v>28</v>
       </c>
-      <c r="J30" s="41">
+      <c r="J30" s="83">
         <f t="shared" si="6"/>
         <v>0.55555555555555558</v>
       </c>
@@ -10354,7 +10376,7 @@
       <c r="L30" s="2">
         <v>123</v>
       </c>
-      <c r="M30" s="41">
+      <c r="M30" s="83">
         <f t="shared" si="7"/>
         <v>0.52325581395348841</v>
       </c>
@@ -10439,7 +10461,7 @@
       <c r="F31" s="2">
         <v>11</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="83">
         <f t="shared" si="5"/>
         <v>0.3888888888888889</v>
       </c>
@@ -10449,7 +10471,7 @@
       <c r="I31" s="2">
         <v>44</v>
       </c>
-      <c r="J31" s="41">
+      <c r="J31" s="83">
         <f t="shared" si="6"/>
         <v>0.46341463414634149</v>
       </c>
@@ -10459,7 +10481,7 @@
       <c r="L31" s="2">
         <v>177</v>
       </c>
-      <c r="M31" s="41">
+      <c r="M31" s="83">
         <f t="shared" si="7"/>
         <v>0.47941176470588237</v>
       </c>
@@ -10544,7 +10566,7 @@
       <c r="F32" s="2">
         <v>1</v>
       </c>
-      <c r="G32" s="41">
+      <c r="G32" s="83">
         <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
@@ -10554,7 +10576,7 @@
       <c r="I32" s="2">
         <v>6</v>
       </c>
-      <c r="J32" s="41">
+      <c r="J32" s="83">
         <f t="shared" si="6"/>
         <v>0.66666666666666663</v>
       </c>
@@ -10564,7 +10586,7 @@
       <c r="L32" s="2">
         <v>35</v>
       </c>
-      <c r="M32" s="41">
+      <c r="M32" s="83">
         <f t="shared" si="7"/>
         <v>0.54545454545454541</v>
       </c>
@@ -10649,7 +10671,7 @@
       <c r="F33" s="2">
         <v>1</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="83">
         <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
@@ -10659,7 +10681,7 @@
       <c r="I33" s="2">
         <v>6</v>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="83">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
@@ -10669,7 +10691,7 @@
       <c r="L33" s="2">
         <v>25</v>
       </c>
-      <c r="M33" s="41">
+      <c r="M33" s="83">
         <f t="shared" si="7"/>
         <v>0.46808510638297873</v>
       </c>
@@ -10754,7 +10776,7 @@
       <c r="F34" s="2">
         <v>8</v>
       </c>
-      <c r="G34" s="41">
+      <c r="G34" s="83">
         <f t="shared" si="5"/>
         <v>0.42857142857142855</v>
       </c>
@@ -10764,7 +10786,7 @@
       <c r="I34" s="2">
         <v>34</v>
       </c>
-      <c r="J34" s="41">
+      <c r="J34" s="83">
         <f t="shared" si="6"/>
         <v>0.53424657534246578</v>
       </c>
@@ -10774,7 +10796,7 @@
       <c r="L34" s="2">
         <v>139</v>
       </c>
-      <c r="M34" s="41">
+      <c r="M34" s="83">
         <f t="shared" si="7"/>
         <v>0.48134328358208955</v>
       </c>
@@ -10859,7 +10881,7 @@
       <c r="F35" s="2">
         <v>9</v>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="83">
         <f t="shared" si="5"/>
         <v>0.35714285714285715</v>
       </c>
@@ -10869,7 +10891,7 @@
       <c r="I35" s="2">
         <v>33</v>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="83">
         <f t="shared" si="6"/>
         <v>0.45</v>
       </c>
@@ -10879,7 +10901,7 @@
       <c r="L35" s="2">
         <v>124</v>
       </c>
-      <c r="M35" s="41">
+      <c r="M35" s="83">
         <f t="shared" si="7"/>
         <v>0.48760330578512395</v>
       </c>
@@ -10964,7 +10986,7 @@
       <c r="F36" s="1">
         <v>0</v>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -10974,7 +10996,7 @@
       <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="J36" s="41">
+      <c r="J36" s="83">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
@@ -10984,7 +11006,7 @@
       <c r="L36" s="1">
         <v>10</v>
       </c>
-      <c r="M36" s="41">
+      <c r="M36" s="83">
         <f t="shared" si="7"/>
         <v>0.47368421052631576</v>
       </c>
@@ -11069,7 +11091,7 @@
       <c r="F37" s="1">
         <v>0</v>
       </c>
-      <c r="G37" s="41">
+      <c r="G37" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11079,7 +11101,7 @@
       <c r="I37" s="1">
         <v>1</v>
       </c>
-      <c r="J37" s="41">
+      <c r="J37" s="83">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
@@ -11089,7 +11111,7 @@
       <c r="L37" s="1">
         <v>5</v>
       </c>
-      <c r="M37" s="41">
+      <c r="M37" s="83">
         <f t="shared" si="7"/>
         <v>0.6428571428571429</v>
       </c>
@@ -11174,7 +11196,7 @@
       <c r="F38" s="2">
         <v>4</v>
       </c>
-      <c r="G38" s="41">
+      <c r="G38" s="83">
         <f t="shared" si="5"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11184,7 +11206,7 @@
       <c r="I38" s="2">
         <v>29</v>
       </c>
-      <c r="J38" s="41">
+      <c r="J38" s="83">
         <f t="shared" si="6"/>
         <v>0.62337662337662336</v>
       </c>
@@ -11194,7 +11216,7 @@
       <c r="L38" s="2">
         <v>145</v>
       </c>
-      <c r="M38" s="41">
+      <c r="M38" s="83">
         <f t="shared" si="7"/>
         <v>0.55108359133126938</v>
       </c>
@@ -11279,7 +11301,7 @@
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11289,7 +11311,7 @@
       <c r="I39" s="2">
         <v>2</v>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="83">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
@@ -11299,7 +11321,7 @@
       <c r="L39" s="2">
         <v>14</v>
       </c>
-      <c r="M39" s="41">
+      <c r="M39" s="83">
         <f t="shared" si="7"/>
         <v>0.58823529411764708</v>
       </c>
@@ -11384,7 +11406,7 @@
       <c r="F40" s="1">
         <v>2</v>
       </c>
-      <c r="G40" s="41">
+      <c r="G40" s="83">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
@@ -11394,7 +11416,7 @@
       <c r="I40" s="1">
         <v>10</v>
       </c>
-      <c r="J40" s="41">
+      <c r="J40" s="83">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
@@ -11404,7 +11426,7 @@
       <c r="L40" s="1">
         <v>42</v>
       </c>
-      <c r="M40" s="41">
+      <c r="M40" s="83">
         <f t="shared" si="7"/>
         <v>0.48148148148148145</v>
       </c>
@@ -11489,7 +11511,7 @@
       <c r="F41" s="2">
         <v>5</v>
       </c>
-      <c r="G41" s="41">
+      <c r="G41" s="83">
         <f t="shared" si="5"/>
         <v>0.44444444444444442</v>
       </c>
@@ -11499,7 +11521,7 @@
       <c r="I41" s="2">
         <v>23</v>
       </c>
-      <c r="J41" s="41">
+      <c r="J41" s="83">
         <f t="shared" si="6"/>
         <v>0.43902439024390244</v>
       </c>
@@ -11509,7 +11531,7 @@
       <c r="L41" s="2">
         <v>86</v>
       </c>
-      <c r="M41" s="41">
+      <c r="M41" s="83">
         <f t="shared" si="7"/>
         <v>0.47878787878787876</v>
       </c>
@@ -11594,7 +11616,7 @@
       <c r="F42" s="2">
         <v>0</v>
       </c>
-      <c r="G42" s="41">
+      <c r="G42" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11604,7 +11626,7 @@
       <c r="I42" s="2">
         <v>2</v>
       </c>
-      <c r="J42" s="41">
+      <c r="J42" s="83">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
@@ -11614,7 +11636,7 @@
       <c r="L42" s="2">
         <v>15</v>
       </c>
-      <c r="M42" s="41">
+      <c r="M42" s="83">
         <f t="shared" si="7"/>
         <v>0.55882352941176472</v>
       </c>
@@ -11699,7 +11721,7 @@
       <c r="F43" s="2">
         <v>7</v>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="83">
         <f t="shared" si="5"/>
         <v>0.22222222222222221</v>
       </c>
@@ -11709,7 +11731,7 @@
       <c r="I43" s="2">
         <v>24</v>
       </c>
-      <c r="J43" s="41">
+      <c r="J43" s="83">
         <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
@@ -11719,7 +11741,7 @@
       <c r="L43" s="2">
         <v>93</v>
       </c>
-      <c r="M43" s="41">
+      <c r="M43" s="83">
         <f t="shared" si="7"/>
         <v>0.44970414201183434</v>
       </c>
@@ -11804,7 +11826,7 @@
       <c r="F44" s="1">
         <v>2</v>
       </c>
-      <c r="G44" s="41">
+      <c r="G44" s="83">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
@@ -11814,7 +11836,7 @@
       <c r="I44" s="1">
         <v>10</v>
       </c>
-      <c r="J44" s="41">
+      <c r="J44" s="83">
         <f t="shared" si="6"/>
         <v>0.56521739130434778</v>
       </c>
@@ -11824,7 +11846,7 @@
       <c r="L44" s="1">
         <v>49</v>
       </c>
-      <c r="M44" s="41">
+      <c r="M44" s="83">
         <f t="shared" si="7"/>
         <v>0.53773584905660377</v>
       </c>
@@ -11909,7 +11931,7 @@
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="83">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11919,7 +11941,7 @@
       <c r="I45" s="2">
         <v>2</v>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="83">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
@@ -11929,7 +11951,7 @@
       <c r="L45" s="2">
         <v>10</v>
       </c>
-      <c r="M45" s="41">
+      <c r="M45" s="83">
         <f t="shared" si="7"/>
         <v>0.52380952380952384</v>
       </c>
@@ -12014,7 +12036,7 @@
       <c r="F46" s="48">
         <v>1</v>
       </c>
-      <c r="G46" s="69">
+      <c r="G46" s="84">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -12024,7 +12046,7 @@
       <c r="I46" s="48">
         <v>3</v>
       </c>
-      <c r="J46" s="69">
+      <c r="J46" s="84">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -12034,7 +12056,7 @@
       <c r="L46" s="48">
         <v>9</v>
       </c>
-      <c r="M46" s="69">
+      <c r="M46" s="84">
         <f t="shared" si="7"/>
         <v>0.30769230769230771</v>
       </c>
@@ -12160,7 +12182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF6821A-FB65-442B-9DB8-237F622F44FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED0A237-5C74-4CF2-9F1D-8BC50443A1F4}">
   <dimension ref="A1:AH36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12349,7 +12371,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>4</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="81">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>0.42857142857142855</v>
       </c>
@@ -12361,7 +12383,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>14</v>
       </c>
-      <c r="K3" s="27">
+      <c r="K3" s="81">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>0.54838709677419351</v>
       </c>
@@ -12373,7 +12395,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>62</v>
       </c>
-      <c r="N3" s="27">
+      <c r="N3" s="81">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>0.52671755725190839</v>
       </c>
@@ -12483,7 +12505,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>4</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="81">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>0.42857142857142855</v>
       </c>
@@ -12495,7 +12517,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>14</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="81">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>0.54838709677419351</v>
       </c>
@@ -12507,7 +12529,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>62</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="81">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>0.52671755725190839</v>
       </c>
@@ -12617,7 +12639,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>10</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="81">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>0.375</v>
       </c>
@@ -12629,7 +12651,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>38</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="81">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>0.44117647058823528</v>
       </c>
@@ -12641,7 +12663,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>144</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="81">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>0.5</v>
       </c>
@@ -12751,7 +12773,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>2</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="81">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>0.81818181818181823</v>
       </c>
@@ -12763,7 +12785,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>16</v>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="81">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>0.65217391304347827</v>
       </c>
@@ -12775,7 +12797,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>79</v>
       </c>
-      <c r="N6" s="27">
+      <c r="N6" s="81">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>0.572972972972973</v>
       </c>
@@ -12885,7 +12907,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>1</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="81">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>0.66666666666666663</v>
       </c>
@@ -12897,7 +12919,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>5</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="81">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>0.58333333333333337</v>
       </c>
@@ -12909,7 +12931,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>19</v>
       </c>
-      <c r="N7" s="27">
+      <c r="N7" s="81">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>0.58695652173913049</v>
       </c>
@@ -13019,7 +13041,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="81">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>0.5</v>
       </c>
@@ -13031,7 +13053,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>9</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="81">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>0.52631578947368418</v>
       </c>
@@ -13043,7 +13065,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>41</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="81">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>0.48749999999999999</v>
       </c>
@@ -13153,7 +13175,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="27" t="str">
+      <c r="H9" s="81" t="str">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13165,7 +13187,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="27" t="str">
+      <c r="K9" s="81" t="str">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13177,7 +13199,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="27" t="str">
+      <c r="N9" s="81" t="str">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13287,7 +13309,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="30" t="str">
+      <c r="H10" s="82" t="str">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13299,7 +13321,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="30" t="str">
+      <c r="K10" s="82" t="str">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13311,7 +13333,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="30" t="str">
+      <c r="N10" s="82" t="str">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -14961,17 +14983,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="Select Player Name" prompt="Select Player Name" xr:uid="{585A4370-F636-4515-B14E-B67D7C237AA4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Team Builder" prompt="Select Player name from drop down list" xr:uid="{E3F0B27D-B9F0-4BB5-8456-75066D0F630B}">
+          <x14:formula1>
+            <xm:f>BA!$A$2:$A$45</xm:f>
+          </x14:formula1>
+          <xm:sqref>B17:B24</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="Select Player Name" prompt="Select Player Name" xr:uid="{7CF85145-1224-4D7F-A47C-6F9DFE0593DF}">
           <x14:formula1>
             <xm:f>BA!$A$2:$A$45</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Team Builder" prompt="Select Player name from drop down list" xr:uid="{FEE24750-61DD-4E3B-AB60-CC8C7258B2CD}">
-          <x14:formula1>
-            <xm:f>BA!$A$2:$A$45</xm:f>
-          </x14:formula1>
-          <xm:sqref>B17:B24</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/R63 Data.xlsx
+++ b/R63 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Downloads\excel-filter-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2B7C7B-03C2-49FC-87AA-47E03B730905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C472A47-5A50-40D5-AA2D-9B662319DFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
   </bookViews>

--- a/R63 Data.xlsx
+++ b/R63 Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Downloads\excel-filter-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C472A47-5A50-40D5-AA2D-9B662319DFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A91CF7-A357-4FC7-829A-0E2A3C312009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
+    <workbookView xWindow="5490" yWindow="4065" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
   </bookViews>
   <sheets>
     <sheet name="Old Bow" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="127">
   <si>
     <t>Player</t>
   </si>
@@ -396,9 +396,6 @@
     <t>Sureshol</t>
   </si>
   <si>
-    <t>Includes match data from 1/1/26 thru 2/22/26</t>
-  </si>
-  <si>
     <t>*2/19 match not added due to incomplete data</t>
   </si>
   <si>
@@ -413,12 +410,18 @@
   <si>
     <t>Match %</t>
   </si>
+  <si>
+    <t>🏆🏆</t>
+  </si>
+  <si>
+    <t>Includes match data from 1/1/26 thru 3/1/26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,9 +473,17 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF001D35"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -674,7 +685,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -860,7 +871,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -885,6 +895,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -902,27 +933,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1238,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}">
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -1288,7 +1303,7 @@
         <v>98</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J1" s="50" t="s">
         <v>64</v>
@@ -1297,7 +1312,7 @@
         <v>101</v>
       </c>
       <c r="L1" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M1" s="51" t="s">
         <v>99</v>
@@ -1306,7 +1321,7 @@
         <v>100</v>
       </c>
       <c r="O1" s="46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P1" s="31" t="s">
         <v>41</v>
@@ -1546,55 +1561,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
+      <c r="B4" s="87" t="s">
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D4" s="34">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
+        <v>10.454545454545455</v>
       </c>
       <c r="F4" s="35">
         <v>21</v>
       </c>
       <c r="G4" s="34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2">
         <v>4</v>
       </c>
       <c r="I4" s="41">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="J4" s="34">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2">
         <v>20</v>
-      </c>
-      <c r="K4" s="2">
-        <v>19</v>
       </c>
       <c r="L4" s="41">
         <f t="shared" si="2"/>
-        <v>0.51282051282051277</v>
+        <v>0.53488372093023251</v>
       </c>
       <c r="M4" s="34">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O4" s="41">
         <f t="shared" si="3"/>
-        <v>0.52229299363057324</v>
+        <v>0.53757225433526012</v>
       </c>
       <c r="P4" s="34">
         <v>2</v>
@@ -1606,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" s="2">
         <v>0</v>
@@ -1630,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="AA4" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="2">
         <v>3</v>
@@ -1639,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="AD4" s="47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -1742,7 +1757,7 @@
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="72" t="s">
         <v>79</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1830,7 +1845,7 @@
       <c r="AC6" s="1">
         <v>0</v>
       </c>
-      <c r="AD6" s="66">
+      <c r="AD6" s="65">
         <v>0</v>
       </c>
     </row>
@@ -2037,44 +2052,44 @@
         <v>79</v>
       </c>
       <c r="D9" s="34">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
-        <v>11.76923076923077</v>
+        <v>12.642857142857142</v>
       </c>
       <c r="F9" s="35">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G9" s="34">
         <v>10</v>
       </c>
       <c r="H9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="41">
         <f t="shared" si="1"/>
-        <v>0.76923076923076927</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J9" s="34">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K9" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L9" s="41">
         <f t="shared" si="2"/>
-        <v>0.660377358490566</v>
+        <v>0.63157894736842102</v>
       </c>
       <c r="M9" s="34">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="O9" s="41">
         <f t="shared" si="3"/>
-        <v>0.58371040723981904</v>
+        <v>0.56540084388185652</v>
       </c>
       <c r="P9" s="34">
         <v>1</v>
@@ -2098,7 +2113,7 @@
         <v>3</v>
       </c>
       <c r="W9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" s="2">
         <v>1</v>
@@ -2214,55 +2229,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>79</v>
+      <c r="B11" s="87" t="s">
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D11" s="34">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="F11" s="35">
         <v>17</v>
       </c>
       <c r="G11" s="36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1">
         <v>5</v>
       </c>
       <c r="I11" s="42">
         <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="J11" s="36">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K11" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L11" s="42">
         <f t="shared" si="2"/>
-        <v>0.40740740740740738</v>
+        <v>0.45161290322580644</v>
       </c>
       <c r="M11" s="36">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N11" s="1">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="O11" s="42">
         <f t="shared" si="3"/>
-        <v>0.45045045045045046</v>
+        <v>0.48031496062992124</v>
       </c>
       <c r="P11" s="34">
         <v>0</v>
@@ -2274,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" s="2">
         <v>0</v>
@@ -2298,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="2">
         <v>3</v>
@@ -2307,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
@@ -2594,7 +2609,7 @@
       <c r="AC14" s="2">
         <v>0</v>
       </c>
-      <c r="AD14" s="66">
+      <c r="AD14" s="65">
         <v>1</v>
       </c>
     </row>
@@ -2699,50 +2714,50 @@
         <v>29</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D16" s="34">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>9.4285714285714288</v>
+        <v>9.7333333333333325</v>
       </c>
       <c r="F16" s="35">
         <v>21</v>
       </c>
       <c r="G16" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="2">
         <v>7</v>
       </c>
       <c r="I16" s="41">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J16" s="34">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K16" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L16" s="41">
         <f t="shared" si="2"/>
-        <v>0.48214285714285715</v>
+        <v>0.5</v>
       </c>
       <c r="M16" s="34">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O16" s="41">
         <f t="shared" si="3"/>
-        <v>0.49367088607594939</v>
+        <v>0.50592885375494068</v>
       </c>
       <c r="P16" s="34">
         <v>2</v>
@@ -2754,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="S16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" s="1">
         <v>1</v>
@@ -2778,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="AA16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB16" s="2">
         <v>5</v>
@@ -2787,7 +2802,7 @@
         <v>2</v>
       </c>
       <c r="AD16" s="47">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -2799,11 +2814,11 @@
         <v>79</v>
       </c>
       <c r="D17" s="34">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="F17" s="35">
         <v>36</v>
@@ -2812,31 +2827,31 @@
         <v>4</v>
       </c>
       <c r="H17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="41">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="J17" s="34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L17" s="41">
         <f t="shared" si="2"/>
-        <v>0.46875</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="M17" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N17" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="O17" s="41">
         <f t="shared" si="3"/>
-        <v>0.47445255474452552</v>
+        <v>0.45751633986928103</v>
       </c>
       <c r="P17" s="34">
         <v>0</v>
@@ -2860,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
@@ -3087,11 +3102,11 @@
         <v>79</v>
       </c>
       <c r="D20" s="34">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>13.636363636363637</v>
+        <v>13.916666666666666</v>
       </c>
       <c r="F20" s="35">
         <v>22</v>
@@ -3100,31 +3115,31 @@
         <v>7</v>
       </c>
       <c r="H20" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="42">
         <f t="shared" si="1"/>
-        <v>0.63636363636363635</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J20" s="36">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L20" s="42">
         <f t="shared" si="2"/>
-        <v>0.56521739130434778</v>
+        <v>0.54</v>
       </c>
       <c r="M20" s="36">
+        <v>104</v>
+      </c>
+      <c r="N20" s="1">
         <v>99</v>
-      </c>
-      <c r="N20" s="1">
-        <v>88</v>
       </c>
       <c r="O20" s="42">
         <f t="shared" si="3"/>
-        <v>0.52941176470588236</v>
+        <v>0.51231527093596063</v>
       </c>
       <c r="P20" s="34">
         <v>4</v>
@@ -3148,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
@@ -3172,55 +3187,55 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>79</v>
+      <c r="B21" s="87" t="s">
+        <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D21" s="34">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>13.066666666666666</v>
+        <v>13.3125</v>
       </c>
       <c r="F21" s="35">
         <v>28</v>
       </c>
       <c r="G21" s="34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="2">
         <v>10</v>
       </c>
       <c r="I21" s="41">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="J21" s="34">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K21" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L21" s="41">
         <f t="shared" si="2"/>
-        <v>0.46031746031746029</v>
+        <v>0.47761194029850745</v>
       </c>
       <c r="M21" s="34">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="N21" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O21" s="41">
         <f t="shared" si="3"/>
-        <v>0.48496240601503759</v>
+        <v>0.49645390070921985</v>
       </c>
       <c r="P21" s="34">
         <v>1</v>
@@ -3232,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" s="1">
         <v>0</v>
@@ -3256,7 +3271,7 @@
         <v>2</v>
       </c>
       <c r="AA21" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB21" s="2">
         <v>5</v>
@@ -3265,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="AD21" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -3648,7 +3663,7 @@
       <c r="AC25" s="2">
         <v>0</v>
       </c>
-      <c r="AD25" s="66">
+      <c r="AD25" s="65">
         <v>1</v>
       </c>
     </row>
@@ -3657,50 +3672,50 @@
         <v>13</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="D26" s="34">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>27.666666666666668</v>
+        <v>28.363636363636363</v>
       </c>
       <c r="F26" s="35">
         <v>57</v>
       </c>
       <c r="G26" s="34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2">
         <v>7</v>
       </c>
       <c r="I26" s="41">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="J26" s="34">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K26" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L26" s="41">
         <f t="shared" si="2"/>
-        <v>0.56470588235294117</v>
+        <v>0.5730337078651685</v>
       </c>
       <c r="M26" s="34">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="N26" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="O26" s="41">
         <f t="shared" si="3"/>
-        <v>0.53561253561253563</v>
+        <v>0.54223433242506813</v>
       </c>
       <c r="P26" s="34">
         <v>2</v>
@@ -3712,7 +3727,7 @@
         <v>2</v>
       </c>
       <c r="S26" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" s="2">
         <v>2</v>
@@ -3736,7 +3751,7 @@
         <v>2</v>
       </c>
       <c r="AA26" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26" s="2">
         <v>6</v>
@@ -3745,58 +3760,58 @@
         <v>0</v>
       </c>
       <c r="AD26" s="47">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>79</v>
+      <c r="B27" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="34">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F27" s="35">
         <v>42</v>
       </c>
       <c r="G27" s="34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="2">
         <v>5</v>
       </c>
       <c r="I27" s="41">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="J27" s="34">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K27" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L27" s="41">
         <f t="shared" si="2"/>
-        <v>0.52380952380952384</v>
+        <v>0.54347826086956519</v>
       </c>
       <c r="M27" s="34">
+        <v>102</v>
+      </c>
+      <c r="N27" s="2">
         <v>91</v>
-      </c>
-      <c r="N27" s="2">
-        <v>86</v>
       </c>
       <c r="O27" s="41">
         <f t="shared" si="3"/>
-        <v>0.51412429378531077</v>
+        <v>0.52849740932642486</v>
       </c>
       <c r="P27" s="34">
         <v>2</v>
@@ -3808,7 +3823,7 @@
         <v>2</v>
       </c>
       <c r="S27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" s="2">
         <v>0</v>
@@ -3832,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB27" s="2">
         <v>0</v>
@@ -3841,7 +3856,7 @@
         <v>4</v>
       </c>
       <c r="AD27" s="47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -4047,11 +4062,11 @@
         <v>79</v>
       </c>
       <c r="D30" s="34">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="F30" s="35">
         <v>6</v>
@@ -4060,31 +4075,31 @@
         <v>3</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="41">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" s="34">
+        <v>11</v>
+      </c>
+      <c r="K30" s="2">
         <v>10</v>
-      </c>
-      <c r="K30" s="2">
-        <v>7</v>
       </c>
       <c r="L30" s="41">
         <f t="shared" si="2"/>
-        <v>0.58823529411764708</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="M30" s="34">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N30" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O30" s="41">
         <f t="shared" si="3"/>
-        <v>0.51428571428571423</v>
+        <v>0.47674418604651164</v>
       </c>
       <c r="P30" s="34">
         <v>1</v>
@@ -4108,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
@@ -4335,11 +4350,11 @@
         <v>79</v>
       </c>
       <c r="D33" s="34">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>22.833333333333332</v>
+        <v>23.53846153846154</v>
       </c>
       <c r="F33" s="35">
         <v>43</v>
@@ -4348,31 +4363,31 @@
         <v>9</v>
       </c>
       <c r="H33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="41">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="J33" s="34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L33" s="41">
         <f t="shared" si="2"/>
-        <v>0.61224489795918369</v>
+        <v>0.58490566037735847</v>
       </c>
       <c r="M33" s="34">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N33" s="2">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="O33" s="41">
         <f t="shared" si="3"/>
-        <v>0.53588516746411485</v>
+        <v>0.52</v>
       </c>
       <c r="P33" s="34">
         <v>1</v>
@@ -4396,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="2">
         <v>0</v>
@@ -4431,11 +4446,11 @@
         <v>79</v>
       </c>
       <c r="D34" s="34">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="0"/>
-        <v>26.8</v>
+        <v>26.636363636363637</v>
       </c>
       <c r="F34" s="35">
         <v>41</v>
@@ -4444,31 +4459,31 @@
         <v>4</v>
       </c>
       <c r="H34" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="41">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="J34" s="34">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K34" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L34" s="41">
         <f t="shared" si="2"/>
-        <v>0.45238095238095238</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="M34" s="34">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N34" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="O34" s="41">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.48351648351648352</v>
       </c>
       <c r="P34" s="34">
         <v>2</v>
@@ -4492,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="W34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="2">
         <v>0</v>
@@ -4803,6 +4818,12 @@
       <c r="AD37" s="49">
         <v>1</v>
       </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="F43" s="88"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="F45" s="88"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AD37" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}"/>
@@ -4820,8 +4841,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
-        <v>120</v>
+      <c r="A1" s="89" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4830,18 +4851,18 @@
       <c r="C3" s="54"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="54"/>
@@ -4874,43 +4895,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="77" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="78"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="77" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="78"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="77" t="s">
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="78"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="78" t="s">
+      <c r="M1" s="84"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="79"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="85"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -4955,51 +4976,51 @@
       <c r="O2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="85" t="s">
+      <c r="P2" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="85" t="s">
+      <c r="Q2" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="85" t="s">
+      <c r="R2" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="85" t="s">
+      <c r="S2" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="85" t="s">
+      <c r="T2" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="85" t="s">
+      <c r="U2" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="85" t="s">
+      <c r="V2" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="W2" s="86" t="s">
+      <c r="W2" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="85" t="s">
+      <c r="X2" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" s="85" t="s">
+      <c r="Y2" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" s="85" t="s">
+      <c r="Z2" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="85" t="s">
+      <c r="AA2" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="AB2" s="85" t="s">
+      <c r="AB2" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="AC2" s="87" t="s">
+      <c r="AC2" s="79" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="86" t="s">
         <v>75</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -5115,17 +5136,17 @@
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
+      <c r="A4" s="86"/>
       <c r="B4" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="D4" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>20</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="E4" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5137,35 +5158,35 @@
       </c>
       <c r="G4" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.5</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="I4" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K4" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.46875</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="L4" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M4" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="N4" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.47445255474452552</v>
+        <v>0.45751633986928103</v>
       </c>
       <c r="O4" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5189,7 +5210,7 @@
       </c>
       <c r="T4" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$4, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5229,17 +5250,17 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
+      <c r="A5" s="86"/>
       <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="D5" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>22.833333333333332</v>
+        <v>23.53846153846154</v>
       </c>
       <c r="E5" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5251,35 +5272,35 @@
       </c>
       <c r="G5" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.75</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="I5" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K5" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.61224489795918369</v>
+        <v>0.58490566037735847</v>
       </c>
       <c r="L5" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M5" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="N5" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.53588516746411485</v>
+        <v>0.52</v>
       </c>
       <c r="O5" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5303,7 +5324,7 @@
       </c>
       <c r="T5" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$5, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5343,17 +5364,17 @@
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
+      <c r="A6" s="86"/>
       <c r="B6" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C6" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D6" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>13.636363636363637</v>
+        <v>13.916666666666666</v>
       </c>
       <c r="E6" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5365,35 +5386,35 @@
       </c>
       <c r="G6" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.63636363636363635</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I6" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K6" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.56521739130434778</v>
+        <v>0.54</v>
       </c>
       <c r="L6" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="M6" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N6" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.52941176470588236</v>
+        <v>0.51231527093596063</v>
       </c>
       <c r="O6" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5417,7 +5438,7 @@
       </c>
       <c r="T6" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$6, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5457,21 +5478,21 @@
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="80"/>
+      <c r="A7" s="86"/>
       <c r="B7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D7" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>11.76923076923077</v>
+        <v>12.642857142857142</v>
       </c>
       <c r="E7" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5479,35 +5500,35 @@
       </c>
       <c r="G7" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.76923076923076927</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I7" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K7" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.660377358490566</v>
+        <v>0.63157894736842102</v>
       </c>
       <c r="L7" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="M7" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N7" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.58371040723981904</v>
+        <v>0.56540084388185652</v>
       </c>
       <c r="O7" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5531,7 +5552,7 @@
       </c>
       <c r="T7" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$7, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5571,17 +5592,17 @@
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
+      <c r="A8" s="86"/>
       <c r="B8" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2.6</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="E8" s="26">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5593,35 +5614,35 @@
       </c>
       <c r="G8" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K8" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.58823529411764708</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="L8" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M8" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N8" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.51428571428571423</v>
+        <v>0.47674418604651164</v>
       </c>
       <c r="O8" s="26">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5645,7 +5666,7 @@
       </c>
       <c r="T8" s="26">
         <f>INDEX('Old Bow'!W2:W37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="26">
         <f>INDEX('Old Bow'!U2:U37, MATCH($B$8, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -5685,7 +5706,7 @@
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="80"/>
+      <c r="A9" s="86"/>
       <c r="B9" s="7" t="s">
         <v>78</v>
       </c>
@@ -5799,7 +5820,7 @@
       </c>
     </row>
     <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="80"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="7" t="s">
         <v>78</v>
       </c>
@@ -5915,21 +5936,21 @@
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D11" s="8">
         <f>SUM(D3:D10)</f>
-        <v>88.111655011655017</v>
+        <v>90.537379287379281</v>
       </c>
       <c r="H11" s="9">
         <f>AVERAGE(H3:H10)</f>
-        <v>0.60320512820512817</v>
+        <v>0.54966792466792469</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="9">
         <f>AVERAGE(K3:K10)</f>
-        <v>0.55444052061498772</v>
+        <v>0.52609279296965494</v>
       </c>
       <c r="N11" s="9">
         <f>AVERAGE(N3:N10)</f>
-        <v>0.51733962387858612</v>
+        <v>0.49971146259417837</v>
       </c>
       <c r="O11" s="5">
         <f>SUM(O3:O10)</f>
@@ -5953,7 +5974,7 @@
       </c>
       <c r="T11" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
@@ -5994,43 +6015,43 @@
     </row>
     <row r="14" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="77" t="s">
+      <c r="D15" s="84"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="78"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="77" t="s">
+      <c r="G15" s="84"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="78"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="77" t="s">
+      <c r="J15" s="84"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="78"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="77" t="s">
+      <c r="M15" s="84"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="78"/>
-      <c r="AC15" s="79"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="85"/>
     </row>
     <row r="16" spans="1:29" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
@@ -6119,7 +6140,7 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="82" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -6127,11 +6148,11 @@
       </c>
       <c r="C17" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="D17" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>27.666666666666668</v>
+        <v>28.363636363636363</v>
       </c>
       <c r="E17" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6139,7 +6160,7 @@
       </c>
       <c r="F17" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6147,35 +6168,35 @@
       </c>
       <c r="H17" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.66666666666666663</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="I17" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J17" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K17" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.56470588235294117</v>
+        <v>0.5730337078651685</v>
       </c>
       <c r="L17" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="M17" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="N17" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.53561253561253563</v>
+        <v>0.54223433242506813</v>
       </c>
       <c r="O17" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6203,7 +6224,7 @@
       </c>
       <c r="V17" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6211,7 +6232,7 @@
       </c>
       <c r="X17" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$17, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6235,17 +6256,17 @@
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
+      <c r="A18" s="82"/>
       <c r="B18" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="D18" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6253,7 +6274,7 @@
       </c>
       <c r="F18" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6261,35 +6282,35 @@
       </c>
       <c r="H18" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.5</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="I18" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J18" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.52380952380952384</v>
+        <v>0.54347826086956519</v>
       </c>
       <c r="L18" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M18" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="N18" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.51412429378531077</v>
+        <v>0.52849740932642486</v>
       </c>
       <c r="O18" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6317,7 +6338,7 @@
       </c>
       <c r="V18" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W18" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6325,7 +6346,7 @@
       </c>
       <c r="X18" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$18, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6349,17 +6370,17 @@
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A19" s="76"/>
+      <c r="A19" s="82"/>
       <c r="B19" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D19" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6367,7 +6388,7 @@
       </c>
       <c r="F19" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6375,35 +6396,35 @@
       </c>
       <c r="H19" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.2857142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="I19" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J19" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.40740740740740738</v>
+        <v>0.45161290322580644</v>
       </c>
       <c r="L19" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M19" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N19" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.45045045045045046</v>
+        <v>0.48031496062992124</v>
       </c>
       <c r="O19" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6431,7 +6452,7 @@
       </c>
       <c r="V19" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6439,7 +6460,7 @@
       </c>
       <c r="X19" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$19, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6463,17 +6484,17 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
+      <c r="A20" s="82"/>
       <c r="B20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D20" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>13.066666666666666</v>
+        <v>13.3125</v>
       </c>
       <c r="E20" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6481,7 +6502,7 @@
       </c>
       <c r="F20" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6489,35 +6510,35 @@
       </c>
       <c r="H20" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="I20" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J20" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.46031746031746029</v>
+        <v>0.47761194029850745</v>
       </c>
       <c r="L20" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="M20" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N20" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.48496240601503759</v>
+        <v>0.49645390070921985</v>
       </c>
       <c r="O20" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6545,7 +6566,7 @@
       </c>
       <c r="V20" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6553,7 +6574,7 @@
       </c>
       <c r="X20" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$20, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6577,17 +6598,17 @@
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="76"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D21" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9.8000000000000007</v>
+        <v>10.454545454545455</v>
       </c>
       <c r="E21" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6595,7 +6616,7 @@
       </c>
       <c r="F21" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6603,35 +6624,35 @@
       </c>
       <c r="H21" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="I21" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J21" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.51282051282051277</v>
+        <v>0.53488372093023251</v>
       </c>
       <c r="L21" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="M21" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N21" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.52229299363057324</v>
+        <v>0.53757225433526012</v>
       </c>
       <c r="O21" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6659,7 +6680,7 @@
       </c>
       <c r="V21" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W21" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6667,7 +6688,7 @@
       </c>
       <c r="X21" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$21, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6691,17 +6712,17 @@
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="76"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="13">
         <f>INDEX('Old Bow'!D2:D37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D22" s="25">
         <f>INDEX('Old Bow'!E2:E37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>9.4285714285714288</v>
+        <v>9.7333333333333325</v>
       </c>
       <c r="E22" s="14">
         <f>INDEX('Old Bow'!F2:F37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6709,7 +6730,7 @@
       </c>
       <c r="F22" s="13">
         <f>INDEX('Old Bow'!G2:G37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" s="26">
         <f>INDEX('Old Bow'!H2:H37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6717,35 +6738,35 @@
       </c>
       <c r="H22" s="27">
         <f>INDEX('Old Bow'!I2:I37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.5</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="I22" s="13">
         <f>INDEX('Old Bow'!J2:J37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J22" s="26">
         <f>INDEX('Old Bow'!K2:K37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" s="27">
         <f>INDEX('Old Bow'!L2:L37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.48214285714285715</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="13">
         <f>INDEX('Old Bow'!M2:M37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="M22" s="26">
         <f>INDEX('Old Bow'!N2:N37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="N22" s="27">
         <f>INDEX('Old Bow'!O2:O37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>0.49367088607594939</v>
+        <v>0.50592885375494068</v>
       </c>
       <c r="O22" s="13">
         <f>INDEX('Old Bow'!AA2:AA37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P22" s="26">
         <f>INDEX('Old Bow'!R2:R37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6773,7 +6794,7 @@
       </c>
       <c r="V22" s="26">
         <f>INDEX('Old Bow'!S2:S37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W22" s="26">
         <f>INDEX('Old Bow'!V2:V37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6781,7 +6802,7 @@
       </c>
       <c r="X22" s="26">
         <f>INDEX('Old Bow'!AD2:AD37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y22" s="26">
         <f>INDEX('Old Bow'!P2:P37, MATCH($B$22, 'Old Bow'!$A$2:$A$37, 0))</f>
@@ -6805,7 +6826,7 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="76"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7" t="s">
         <v>80</v>
       </c>
@@ -6919,7 +6940,7 @@
       </c>
     </row>
     <row r="24" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="76"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7" t="s">
         <v>80</v>
       </c>
@@ -7035,25 +7056,25 @@
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D25" s="8">
         <f>SUM(D17:D24)</f>
-        <v>95.533333333333331</v>
+        <v>98.864015151515147</v>
       </c>
       <c r="H25" s="9">
         <f>AVERAGE(H17:H24)</f>
-        <v>0.48095238095238085</v>
+        <v>0.52449494949494946</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="9">
         <f>AVERAGE(K17:K24)</f>
-        <v>0.49186727397511709</v>
+        <v>0.51343675553154677</v>
       </c>
       <c r="N25" s="9">
         <f>AVERAGE(N17:N24)</f>
-        <v>0.50018559426164277</v>
+        <v>0.51516695186347239</v>
       </c>
       <c r="O25" s="5">
         <f>SUM(O17:O24)</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P25" s="5">
         <f t="shared" ref="P25" si="1">SUM(P17:P24)</f>
@@ -7081,7 +7102,7 @@
       </c>
       <c r="V25" s="5">
         <f t="shared" ref="V25" si="7">SUM(V17:V24)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="W25" s="5">
         <f t="shared" ref="W25" si="8">SUM(W17:W24)</f>
@@ -7089,7 +7110,7 @@
       </c>
       <c r="X25" s="5">
         <f t="shared" ref="X25" si="9">SUM(X17:X24)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y25" s="5">
         <f t="shared" ref="Y25" si="10">SUM(Y17:Y24)</f>
@@ -7171,11 +7192,11 @@
       </c>
       <c r="C33" s="13" t="str">
         <f>IF(N25&gt;N11,"","✔")</f>
-        <v>✔</v>
+        <v/>
       </c>
       <c r="D33" s="14" t="str">
         <f>IF(C33="✔", "", "✔")</f>
-        <v/>
+        <v>✔</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7188,7 +7209,7 @@
       </c>
       <c r="D34" s="14" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 1), O25:AC25, 0))</f>
-        <v>Garage</v>
+        <v>Scharins</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
@@ -7201,7 +7222,7 @@
       </c>
       <c r="D35" s="14" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 2), O25:AC25, 0))</f>
-        <v>Scharins</v>
+        <v>Garage</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7214,7 +7235,7 @@
       </c>
       <c r="D36" s="18" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 3), O25:AC25, 0))</f>
-        <v>Scharins</v>
+        <v>Garage</v>
       </c>
     </row>
   </sheetData>
@@ -7319,7 +7340,7 @@
         <v>98</v>
       </c>
       <c r="G1" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H1" s="51" t="s">
         <v>64</v>
@@ -7328,7 +7349,7 @@
         <v>101</v>
       </c>
       <c r="J1" s="46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K1" s="51" t="s">
         <v>99</v>
@@ -7337,66 +7358,66 @@
         <v>100</v>
       </c>
       <c r="M1" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="N1" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="O1" s="70" t="s">
+      <c r="O1" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="70" t="s">
+      <c r="P1" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="71" t="s">
+      <c r="Q1" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="R1" s="71" t="s">
+      <c r="R1" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="S1" s="70" t="s">
+      <c r="S1" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="71" t="s">
+      <c r="T1" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="70" t="s">
+      <c r="U1" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="V1" s="71" t="s">
+      <c r="V1" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="70" t="s">
+      <c r="W1" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="X1" s="70" t="s">
+      <c r="X1" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" s="71" t="s">
+      <c r="Y1" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="70" t="s">
+      <c r="Z1" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="AA1" s="71" t="s">
+      <c r="AA1" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="71" t="s">
+      <c r="AB1" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="AC1" s="70" t="s">
+      <c r="AC1" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="AD1" s="70" t="s">
+      <c r="AD1" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="AE1" s="70" t="s">
+      <c r="AE1" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="AF1" s="71" t="s">
+      <c r="AF1" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="AG1" s="72" t="s">
+      <c r="AG1" s="71" t="s">
         <v>96</v>
       </c>
     </row>
@@ -7407,7 +7428,7 @@
       <c r="B2" s="34">
         <v>95</v>
       </c>
-      <c r="C2" s="67">
+      <c r="C2" s="66">
         <f t="shared" ref="C2:C12" si="0">B2/(E2+F2)</f>
         <v>13.571428571428571</v>
       </c>
@@ -7420,7 +7441,7 @@
       <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="G2" s="83">
+      <c r="G2" s="75">
         <f t="shared" ref="G2:G12" si="1">E2/(E2+F2)</f>
         <v>0.42857142857142855</v>
       </c>
@@ -7430,7 +7451,7 @@
       <c r="I2" s="2">
         <v>14</v>
       </c>
-      <c r="J2" s="83">
+      <c r="J2" s="75">
         <f t="shared" ref="J2:J12" si="2">H2/(H2+I2)</f>
         <v>0.54838709677419351</v>
       </c>
@@ -7440,7 +7461,7 @@
       <c r="L2" s="2">
         <v>62</v>
       </c>
-      <c r="M2" s="83">
+      <c r="M2" s="75">
         <f t="shared" ref="M2:M12" si="3">K2/(K2+L2)</f>
         <v>0.52671755725190839</v>
       </c>
@@ -7512,7 +7533,7 @@
       <c r="B3" s="34">
         <v>9</v>
       </c>
-      <c r="C3" s="67">
+      <c r="C3" s="66">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -7525,7 +7546,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="83">
+      <c r="G3" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7535,7 +7556,7 @@
       <c r="I3" s="2">
         <v>3</v>
       </c>
-      <c r="J3" s="83">
+      <c r="J3" s="75">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
@@ -7545,7 +7566,7 @@
       <c r="L3" s="2">
         <v>11</v>
       </c>
-      <c r="M3" s="83">
+      <c r="M3" s="75">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
@@ -7617,7 +7638,7 @@
       <c r="B4" s="34">
         <v>21</v>
       </c>
-      <c r="C4" s="67">
+      <c r="C4" s="66">
         <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
@@ -7630,7 +7651,7 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="83">
+      <c r="G4" s="75">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -7640,7 +7661,7 @@
       <c r="I4" s="2">
         <v>5</v>
       </c>
-      <c r="J4" s="83">
+      <c r="J4" s="75">
         <f t="shared" si="2"/>
         <v>0.44444444444444442</v>
       </c>
@@ -7650,7 +7671,7 @@
       <c r="L4" s="2">
         <v>20</v>
       </c>
-      <c r="M4" s="83">
+      <c r="M4" s="75">
         <f t="shared" si="3"/>
         <v>0.42857142857142855</v>
       </c>
@@ -7722,11 +7743,11 @@
       <c r="B5" s="36">
         <v>6</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="66">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="65">
         <v>6</v>
       </c>
       <c r="E5" s="36">
@@ -7735,7 +7756,7 @@
       <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="83">
+      <c r="G5" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7745,7 +7766,7 @@
       <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="J5" s="83">
+      <c r="J5" s="75">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
@@ -7755,7 +7776,7 @@
       <c r="L5" s="1">
         <v>11</v>
       </c>
-      <c r="M5" s="83">
+      <c r="M5" s="75">
         <f t="shared" si="3"/>
         <v>0.42105263157894735</v>
       </c>
@@ -7816,7 +7837,7 @@
       <c r="AF5" s="1">
         <v>0</v>
       </c>
-      <c r="AG5" s="66">
+      <c r="AG5" s="65">
         <v>0</v>
       </c>
     </row>
@@ -7827,7 +7848,7 @@
       <c r="B6" s="34">
         <v>188</v>
       </c>
-      <c r="C6" s="67">
+      <c r="C6" s="66">
         <f t="shared" si="0"/>
         <v>11.75</v>
       </c>
@@ -7840,7 +7861,7 @@
       <c r="F6" s="2">
         <v>10</v>
       </c>
-      <c r="G6" s="83">
+      <c r="G6" s="75">
         <f t="shared" si="1"/>
         <v>0.375</v>
       </c>
@@ -7850,7 +7871,7 @@
       <c r="I6" s="2">
         <v>38</v>
       </c>
-      <c r="J6" s="83">
+      <c r="J6" s="75">
         <f t="shared" si="2"/>
         <v>0.44117647058823528</v>
       </c>
@@ -7860,7 +7881,7 @@
       <c r="L6" s="2">
         <v>144</v>
       </c>
-      <c r="M6" s="83">
+      <c r="M6" s="75">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
@@ -7932,7 +7953,7 @@
       <c r="B7" s="34">
         <v>88</v>
       </c>
-      <c r="C7" s="67">
+      <c r="C7" s="66">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -7945,7 +7966,7 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="75">
         <f t="shared" si="1"/>
         <v>0.81818181818181823</v>
       </c>
@@ -7955,7 +7976,7 @@
       <c r="I7" s="2">
         <v>16</v>
       </c>
-      <c r="J7" s="83">
+      <c r="J7" s="75">
         <f t="shared" si="2"/>
         <v>0.65217391304347827</v>
       </c>
@@ -7965,7 +7986,7 @@
       <c r="L7" s="2">
         <v>79</v>
       </c>
-      <c r="M7" s="83">
+      <c r="M7" s="75">
         <f t="shared" si="3"/>
         <v>0.572972972972973</v>
       </c>
@@ -8037,7 +8058,7 @@
       <c r="B8" s="34">
         <v>143</v>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="66">
         <f t="shared" si="0"/>
         <v>15.888888888888889</v>
       </c>
@@ -8050,7 +8071,7 @@
       <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="75">
         <f t="shared" si="1"/>
         <v>0.55555555555555558</v>
       </c>
@@ -8060,7 +8081,7 @@
       <c r="I8" s="2">
         <v>20</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="75">
         <f t="shared" si="2"/>
         <v>0.48717948717948717</v>
       </c>
@@ -8070,7 +8091,7 @@
       <c r="L8" s="2">
         <v>84</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="75">
         <f t="shared" si="3"/>
         <v>0.48780487804878048</v>
       </c>
@@ -8142,7 +8163,7 @@
       <c r="B9" s="34">
         <v>24</v>
       </c>
-      <c r="C9" s="67">
+      <c r="C9" s="66">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -8155,7 +8176,7 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="75">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8165,7 +8186,7 @@
       <c r="I9" s="2">
         <v>5</v>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="75">
         <f t="shared" si="2"/>
         <v>0.58333333333333337</v>
       </c>
@@ -8175,7 +8196,7 @@
       <c r="L9" s="2">
         <v>19</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="75">
         <f t="shared" si="3"/>
         <v>0.58695652173913049</v>
       </c>
@@ -8247,11 +8268,11 @@
       <c r="B10" s="36">
         <v>44</v>
       </c>
-      <c r="C10" s="67">
+      <c r="C10" s="66">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="65">
         <v>14</v>
       </c>
       <c r="E10" s="36">
@@ -8260,7 +8281,7 @@
       <c r="F10" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="75">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
@@ -8270,7 +8291,7 @@
       <c r="I10" s="1">
         <v>11</v>
       </c>
-      <c r="J10" s="83">
+      <c r="J10" s="75">
         <f t="shared" si="2"/>
         <v>0.3888888888888889</v>
       </c>
@@ -8280,7 +8301,7 @@
       <c r="L10" s="1">
         <v>39</v>
       </c>
-      <c r="M10" s="83">
+      <c r="M10" s="75">
         <f t="shared" si="3"/>
         <v>0.44285714285714284</v>
       </c>
@@ -8341,7 +8362,7 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="66">
+      <c r="AG10" s="65">
         <v>0</v>
       </c>
     </row>
@@ -8352,7 +8373,7 @@
       <c r="B11" s="34">
         <v>61</v>
       </c>
-      <c r="C11" s="67">
+      <c r="C11" s="66">
         <f t="shared" si="0"/>
         <v>15.25</v>
       </c>
@@ -8365,7 +8386,7 @@
       <c r="F11" s="2">
         <v>2</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="75">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -8375,7 +8396,7 @@
       <c r="I11" s="2">
         <v>9</v>
       </c>
-      <c r="J11" s="83">
+      <c r="J11" s="75">
         <f t="shared" si="2"/>
         <v>0.52631578947368418</v>
       </c>
@@ -8385,7 +8406,7 @@
       <c r="L11" s="2">
         <v>41</v>
       </c>
-      <c r="M11" s="83">
+      <c r="M11" s="75">
         <f t="shared" si="3"/>
         <v>0.48749999999999999</v>
       </c>
@@ -8457,11 +8478,11 @@
       <c r="B12" s="36">
         <v>3</v>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="66">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="65">
         <v>3</v>
       </c>
       <c r="E12" s="36">
@@ -8470,7 +8491,7 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8480,7 +8501,7 @@
       <c r="I12" s="1">
         <v>3</v>
       </c>
-      <c r="J12" s="83">
+      <c r="J12" s="75">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
@@ -8490,7 +8511,7 @@
       <c r="L12" s="1">
         <v>13</v>
       </c>
-      <c r="M12" s="83">
+      <c r="M12" s="75">
         <f t="shared" si="3"/>
         <v>0.43478260869565216</v>
       </c>
@@ -8562,10 +8583,10 @@
       <c r="B13" s="36">
         <v>0</v>
       </c>
-      <c r="C13" s="67">
-        <v>0</v>
-      </c>
-      <c r="D13" s="66">
+      <c r="C13" s="66">
+        <v>0</v>
+      </c>
+      <c r="D13" s="65">
         <v>0</v>
       </c>
       <c r="E13" s="36">
@@ -8574,7 +8595,7 @@
       <c r="F13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="83" t="s">
+      <c r="G13" s="75" t="s">
         <v>79</v>
       </c>
       <c r="H13" s="36">
@@ -8583,7 +8604,7 @@
       <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="J13" s="83" t="s">
+      <c r="J13" s="75" t="s">
         <v>79</v>
       </c>
       <c r="K13" s="36">
@@ -8592,7 +8613,7 @@
       <c r="L13" s="1">
         <v>0</v>
       </c>
-      <c r="M13" s="83" t="s">
+      <c r="M13" s="75" t="s">
         <v>79</v>
       </c>
       <c r="N13" s="36">
@@ -8652,7 +8673,7 @@
       <c r="AF13" s="1">
         <v>0</v>
       </c>
-      <c r="AG13" s="66">
+      <c r="AG13" s="65">
         <v>0</v>
       </c>
     </row>
@@ -8663,7 +8684,7 @@
       <c r="B14" s="34">
         <v>9</v>
       </c>
-      <c r="C14" s="67">
+      <c r="C14" s="66">
         <f t="shared" ref="C14:C46" si="4">B14/(E14+F14)</f>
         <v>9</v>
       </c>
@@ -8676,7 +8697,7 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="75">
         <f t="shared" ref="G14:G46" si="5">E14/(E14+F14)</f>
         <v>0</v>
       </c>
@@ -8686,7 +8707,7 @@
       <c r="I14" s="2">
         <v>3</v>
       </c>
-      <c r="J14" s="83">
+      <c r="J14" s="75">
         <f t="shared" ref="J14:J46" si="6">H14/(H14+I14)</f>
         <v>0.25</v>
       </c>
@@ -8696,7 +8717,7 @@
       <c r="L14" s="2">
         <v>9</v>
       </c>
-      <c r="M14" s="83">
+      <c r="M14" s="75">
         <f t="shared" ref="M14:M46" si="7">K14/(K14+L14)</f>
         <v>0.4</v>
       </c>
@@ -8768,7 +8789,7 @@
       <c r="B15" s="34">
         <v>3</v>
       </c>
-      <c r="C15" s="67">
+      <c r="C15" s="66">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
@@ -8781,7 +8802,7 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -8791,7 +8812,7 @@
       <c r="I15" s="2">
         <v>3</v>
       </c>
-      <c r="J15" s="83">
+      <c r="J15" s="75">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -8801,7 +8822,7 @@
       <c r="L15" s="2">
         <v>9</v>
       </c>
-      <c r="M15" s="83">
+      <c r="M15" s="75">
         <f t="shared" si="7"/>
         <v>0.30769230769230771</v>
       </c>
@@ -8873,7 +8894,7 @@
       <c r="B16" s="34">
         <v>32</v>
       </c>
-      <c r="C16" s="67">
+      <c r="C16" s="66">
         <f t="shared" si="4"/>
         <v>10.666666666666666</v>
       </c>
@@ -8886,7 +8907,7 @@
       <c r="F16" s="2">
         <v>1</v>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="75">
         <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8896,7 +8917,7 @@
       <c r="I16" s="2">
         <v>5</v>
       </c>
-      <c r="J16" s="83">
+      <c r="J16" s="75">
         <f t="shared" si="6"/>
         <v>0.61538461538461542</v>
       </c>
@@ -8906,7 +8927,7 @@
       <c r="L16" s="2">
         <v>27</v>
       </c>
-      <c r="M16" s="83">
+      <c r="M16" s="75">
         <f t="shared" si="7"/>
         <v>0.5423728813559322</v>
       </c>
@@ -8978,7 +8999,7 @@
       <c r="B17" s="34">
         <v>370</v>
       </c>
-      <c r="C17" s="67">
+      <c r="C17" s="66">
         <f t="shared" si="4"/>
         <v>21.764705882352942</v>
       </c>
@@ -8991,7 +9012,7 @@
       <c r="F17" s="2">
         <v>7</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="75">
         <f t="shared" si="5"/>
         <v>0.58823529411764708</v>
       </c>
@@ -9001,7 +9022,7 @@
       <c r="I17" s="2">
         <v>33</v>
       </c>
-      <c r="J17" s="83">
+      <c r="J17" s="75">
         <f t="shared" si="6"/>
         <v>0.54166666666666663</v>
       </c>
@@ -9011,7 +9032,7 @@
       <c r="L17" s="2">
         <v>152</v>
       </c>
-      <c r="M17" s="83">
+      <c r="M17" s="75">
         <f t="shared" si="7"/>
         <v>0.51592356687898089</v>
       </c>
@@ -9083,7 +9104,7 @@
       <c r="B18" s="34">
         <v>58</v>
       </c>
-      <c r="C18" s="67">
+      <c r="C18" s="66">
         <f t="shared" si="4"/>
         <v>11.6</v>
       </c>
@@ -9096,7 +9117,7 @@
       <c r="F18" s="2">
         <v>4</v>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="75">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
@@ -9106,7 +9127,7 @@
       <c r="I18" s="2">
         <v>14</v>
       </c>
-      <c r="J18" s="83">
+      <c r="J18" s="75">
         <f t="shared" si="6"/>
         <v>0.36363636363636365</v>
       </c>
@@ -9116,7 +9137,7 @@
       <c r="L18" s="2">
         <v>52</v>
       </c>
-      <c r="M18" s="83">
+      <c r="M18" s="75">
         <f t="shared" si="7"/>
         <v>0.39534883720930231</v>
       </c>
@@ -9188,7 +9209,7 @@
       <c r="B19" s="34">
         <v>94</v>
       </c>
-      <c r="C19" s="67">
+      <c r="C19" s="66">
         <f t="shared" si="4"/>
         <v>18.8</v>
       </c>
@@ -9201,7 +9222,7 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="75">
         <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
@@ -9211,7 +9232,7 @@
       <c r="I19" s="2">
         <v>9</v>
       </c>
-      <c r="J19" s="83">
+      <c r="J19" s="75">
         <f t="shared" si="6"/>
         <v>0.60869565217391308</v>
       </c>
@@ -9221,7 +9242,7 @@
       <c r="L19" s="2">
         <v>40</v>
       </c>
-      <c r="M19" s="83">
+      <c r="M19" s="75">
         <f t="shared" si="7"/>
         <v>0.56521739130434778</v>
       </c>
@@ -9293,7 +9314,7 @@
       <c r="B20" s="34">
         <v>239</v>
       </c>
-      <c r="C20" s="67">
+      <c r="C20" s="66">
         <f t="shared" si="4"/>
         <v>29.875</v>
       </c>
@@ -9306,7 +9327,7 @@
       <c r="F20" s="2">
         <v>4</v>
       </c>
-      <c r="G20" s="83">
+      <c r="G20" s="75">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
@@ -9316,7 +9337,7 @@
       <c r="I20" s="2">
         <v>19</v>
       </c>
-      <c r="J20" s="83">
+      <c r="J20" s="75">
         <f t="shared" si="6"/>
         <v>0.44117647058823528</v>
       </c>
@@ -9326,7 +9347,7 @@
       <c r="L20" s="2">
         <v>78</v>
       </c>
-      <c r="M20" s="83">
+      <c r="M20" s="75">
         <f t="shared" si="7"/>
         <v>0.48684210526315791</v>
       </c>
@@ -9398,11 +9419,11 @@
       <c r="B21" s="36">
         <v>19</v>
       </c>
-      <c r="C21" s="67">
+      <c r="C21" s="66">
         <f t="shared" si="4"/>
         <v>9.5</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="65">
         <v>11</v>
       </c>
       <c r="E21" s="36">
@@ -9411,7 +9432,7 @@
       <c r="F21" s="1">
         <v>0</v>
       </c>
-      <c r="G21" s="83">
+      <c r="G21" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -9421,7 +9442,7 @@
       <c r="I21" s="1">
         <v>4</v>
       </c>
-      <c r="J21" s="83">
+      <c r="J21" s="75">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
@@ -9431,7 +9452,7 @@
       <c r="L21" s="1">
         <v>19</v>
       </c>
-      <c r="M21" s="83">
+      <c r="M21" s="75">
         <f t="shared" si="7"/>
         <v>0.55813953488372092</v>
       </c>
@@ -9492,7 +9513,7 @@
       <c r="AF21" s="1">
         <v>0</v>
       </c>
-      <c r="AG21" s="66">
+      <c r="AG21" s="65">
         <v>2</v>
       </c>
     </row>
@@ -9503,7 +9524,7 @@
       <c r="B22" s="34">
         <v>244</v>
       </c>
-      <c r="C22" s="67">
+      <c r="C22" s="66">
         <f t="shared" si="4"/>
         <v>20.333333333333332</v>
       </c>
@@ -9516,7 +9537,7 @@
       <c r="F22" s="2">
         <v>8</v>
       </c>
-      <c r="G22" s="83">
+      <c r="G22" s="75">
         <f t="shared" si="5"/>
         <v>0.33333333333333331</v>
       </c>
@@ -9526,7 +9547,7 @@
       <c r="I22" s="2">
         <v>31</v>
       </c>
-      <c r="J22" s="83">
+      <c r="J22" s="75">
         <f t="shared" si="6"/>
         <v>0.43636363636363634</v>
       </c>
@@ -9536,7 +9557,7 @@
       <c r="L22" s="2">
         <v>116</v>
       </c>
-      <c r="M22" s="83">
+      <c r="M22" s="75">
         <f t="shared" si="7"/>
         <v>0.49122807017543857</v>
       </c>
@@ -9608,7 +9629,7 @@
       <c r="B23" s="34">
         <v>141</v>
       </c>
-      <c r="C23" s="67">
+      <c r="C23" s="66">
         <f t="shared" si="4"/>
         <v>15.666666666666666</v>
       </c>
@@ -9621,7 +9642,7 @@
       <c r="F23" s="2">
         <v>5</v>
       </c>
-      <c r="G23" s="83">
+      <c r="G23" s="75">
         <f t="shared" si="5"/>
         <v>0.44444444444444442</v>
       </c>
@@ -9631,7 +9652,7 @@
       <c r="I23" s="2">
         <v>19</v>
       </c>
-      <c r="J23" s="83">
+      <c r="J23" s="75">
         <f t="shared" si="6"/>
         <v>0.47222222222222221</v>
       </c>
@@ -9641,7 +9662,7 @@
       <c r="L23" s="2">
         <v>78</v>
       </c>
-      <c r="M23" s="83">
+      <c r="M23" s="75">
         <f t="shared" si="7"/>
         <v>0.4935064935064935</v>
       </c>
@@ -9713,7 +9734,7 @@
       <c r="B24" s="34">
         <v>143</v>
       </c>
-      <c r="C24" s="67">
+      <c r="C24" s="66">
         <f t="shared" si="4"/>
         <v>17.875</v>
       </c>
@@ -9726,7 +9747,7 @@
       <c r="F24" s="2">
         <v>5</v>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="75">
         <f t="shared" si="5"/>
         <v>0.375</v>
       </c>
@@ -9736,7 +9757,7 @@
       <c r="I24" s="2">
         <v>17</v>
       </c>
-      <c r="J24" s="83">
+      <c r="J24" s="75">
         <f t="shared" si="6"/>
         <v>0.46875</v>
       </c>
@@ -9746,7 +9767,7 @@
       <c r="L24" s="2">
         <v>68</v>
       </c>
-      <c r="M24" s="83">
+      <c r="M24" s="75">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
@@ -9818,7 +9839,7 @@
       <c r="B25" s="34">
         <v>5</v>
       </c>
-      <c r="C25" s="67">
+      <c r="C25" s="66">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -9831,7 +9852,7 @@
       <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c r="G25" s="83">
+      <c r="G25" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -9841,7 +9862,7 @@
       <c r="I25" s="2">
         <v>3</v>
       </c>
-      <c r="J25" s="83">
+      <c r="J25" s="75">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -9851,7 +9872,7 @@
       <c r="L25" s="2">
         <v>9</v>
       </c>
-      <c r="M25" s="83">
+      <c r="M25" s="75">
         <f t="shared" si="7"/>
         <v>0.18181818181818182</v>
       </c>
@@ -9923,7 +9944,7 @@
       <c r="B26" s="34">
         <v>21</v>
       </c>
-      <c r="C26" s="67">
+      <c r="C26" s="66">
         <f t="shared" si="4"/>
         <v>5.25</v>
       </c>
@@ -9936,7 +9957,7 @@
       <c r="F26" s="2">
         <v>3</v>
       </c>
-      <c r="G26" s="83">
+      <c r="G26" s="75">
         <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
@@ -9946,7 +9967,7 @@
       <c r="I26" s="2">
         <v>11</v>
       </c>
-      <c r="J26" s="83">
+      <c r="J26" s="75">
         <f t="shared" si="6"/>
         <v>0.42105263157894735</v>
       </c>
@@ -9956,7 +9977,7 @@
       <c r="L26" s="2">
         <v>40</v>
       </c>
-      <c r="M26" s="83">
+      <c r="M26" s="75">
         <f t="shared" si="7"/>
         <v>0.44444444444444442</v>
       </c>
@@ -10028,7 +10049,7 @@
       <c r="B27" s="34">
         <v>166</v>
       </c>
-      <c r="C27" s="67">
+      <c r="C27" s="66">
         <f t="shared" si="4"/>
         <v>23.714285714285715</v>
       </c>
@@ -10041,7 +10062,7 @@
       <c r="F27" s="2">
         <v>5</v>
       </c>
-      <c r="G27" s="83">
+      <c r="G27" s="75">
         <f t="shared" si="5"/>
         <v>0.2857142857142857</v>
       </c>
@@ -10051,7 +10072,7 @@
       <c r="I27" s="2">
         <v>20</v>
       </c>
-      <c r="J27" s="83">
+      <c r="J27" s="75">
         <f t="shared" si="6"/>
         <v>0.44444444444444442</v>
       </c>
@@ -10061,7 +10082,7 @@
       <c r="L27" s="2">
         <v>83</v>
       </c>
-      <c r="M27" s="83">
+      <c r="M27" s="75">
         <f t="shared" si="7"/>
         <v>0.4713375796178344</v>
       </c>
@@ -10133,7 +10154,7 @@
       <c r="B28" s="34">
         <v>3</v>
       </c>
-      <c r="C28" s="67">
+      <c r="C28" s="66">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
@@ -10146,7 +10167,7 @@
       <c r="F28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="83">
+      <c r="G28" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -10156,7 +10177,7 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="83">
+      <c r="J28" s="75">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -10166,7 +10187,7 @@
       <c r="L28" s="2">
         <v>5</v>
       </c>
-      <c r="M28" s="83">
+      <c r="M28" s="75">
         <f t="shared" si="7"/>
         <v>0.6428571428571429</v>
       </c>
@@ -10238,7 +10259,7 @@
       <c r="B29" s="34">
         <v>28</v>
       </c>
-      <c r="C29" s="67">
+      <c r="C29" s="66">
         <f t="shared" si="4"/>
         <v>9.3333333333333339</v>
       </c>
@@ -10251,7 +10272,7 @@
       <c r="F29" s="2">
         <v>2</v>
       </c>
-      <c r="G29" s="83">
+      <c r="G29" s="75">
         <f t="shared" si="5"/>
         <v>0.33333333333333331</v>
       </c>
@@ -10261,7 +10282,7 @@
       <c r="I29" s="2">
         <v>8</v>
       </c>
-      <c r="J29" s="83">
+      <c r="J29" s="75">
         <f t="shared" si="6"/>
         <v>0.46666666666666667</v>
       </c>
@@ -10271,7 +10292,7 @@
       <c r="L29" s="2">
         <v>35</v>
       </c>
-      <c r="M29" s="83">
+      <c r="M29" s="75">
         <f t="shared" si="7"/>
         <v>0.44444444444444442</v>
       </c>
@@ -10343,7 +10364,7 @@
       <c r="B30" s="34">
         <v>354</v>
       </c>
-      <c r="C30" s="67">
+      <c r="C30" s="66">
         <f t="shared" si="4"/>
         <v>23.6</v>
       </c>
@@ -10356,7 +10377,7 @@
       <c r="F30" s="2">
         <v>6</v>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="75">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
@@ -10366,7 +10387,7 @@
       <c r="I30" s="2">
         <v>28</v>
       </c>
-      <c r="J30" s="83">
+      <c r="J30" s="75">
         <f t="shared" si="6"/>
         <v>0.55555555555555558</v>
       </c>
@@ -10376,7 +10397,7 @@
       <c r="L30" s="2">
         <v>123</v>
       </c>
-      <c r="M30" s="83">
+      <c r="M30" s="75">
         <f t="shared" si="7"/>
         <v>0.52325581395348841</v>
       </c>
@@ -10448,7 +10469,7 @@
       <c r="B31" s="34">
         <v>487</v>
       </c>
-      <c r="C31" s="67">
+      <c r="C31" s="66">
         <f t="shared" si="4"/>
         <v>27.055555555555557</v>
       </c>
@@ -10461,7 +10482,7 @@
       <c r="F31" s="2">
         <v>11</v>
       </c>
-      <c r="G31" s="83">
+      <c r="G31" s="75">
         <f t="shared" si="5"/>
         <v>0.3888888888888889</v>
       </c>
@@ -10471,7 +10492,7 @@
       <c r="I31" s="2">
         <v>44</v>
       </c>
-      <c r="J31" s="83">
+      <c r="J31" s="75">
         <f t="shared" si="6"/>
         <v>0.46341463414634149</v>
       </c>
@@ -10481,7 +10502,7 @@
       <c r="L31" s="2">
         <v>177</v>
       </c>
-      <c r="M31" s="83">
+      <c r="M31" s="75">
         <f t="shared" si="7"/>
         <v>0.47941176470588237</v>
       </c>
@@ -10553,7 +10574,7 @@
       <c r="B32" s="34">
         <v>111</v>
       </c>
-      <c r="C32" s="67">
+      <c r="C32" s="66">
         <f t="shared" si="4"/>
         <v>27.75</v>
       </c>
@@ -10566,7 +10587,7 @@
       <c r="F32" s="2">
         <v>1</v>
       </c>
-      <c r="G32" s="83">
+      <c r="G32" s="75">
         <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
@@ -10576,7 +10597,7 @@
       <c r="I32" s="2">
         <v>6</v>
       </c>
-      <c r="J32" s="83">
+      <c r="J32" s="75">
         <f t="shared" si="6"/>
         <v>0.66666666666666663</v>
       </c>
@@ -10586,7 +10607,7 @@
       <c r="L32" s="2">
         <v>35</v>
       </c>
-      <c r="M32" s="83">
+      <c r="M32" s="75">
         <f t="shared" si="7"/>
         <v>0.54545454545454541</v>
       </c>
@@ -10658,7 +10679,7 @@
       <c r="B33" s="34">
         <v>9</v>
       </c>
-      <c r="C33" s="67">
+      <c r="C33" s="66">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
@@ -10671,7 +10692,7 @@
       <c r="F33" s="2">
         <v>1</v>
       </c>
-      <c r="G33" s="83">
+      <c r="G33" s="75">
         <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
@@ -10681,7 +10702,7 @@
       <c r="I33" s="2">
         <v>6</v>
       </c>
-      <c r="J33" s="83">
+      <c r="J33" s="75">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
@@ -10691,7 +10712,7 @@
       <c r="L33" s="2">
         <v>25</v>
       </c>
-      <c r="M33" s="83">
+      <c r="M33" s="75">
         <f t="shared" si="7"/>
         <v>0.46808510638297873</v>
       </c>
@@ -10763,7 +10784,7 @@
       <c r="B34" s="34">
         <v>259</v>
       </c>
-      <c r="C34" s="67">
+      <c r="C34" s="66">
         <f t="shared" si="4"/>
         <v>18.5</v>
       </c>
@@ -10776,7 +10797,7 @@
       <c r="F34" s="2">
         <v>8</v>
       </c>
-      <c r="G34" s="83">
+      <c r="G34" s="75">
         <f t="shared" si="5"/>
         <v>0.42857142857142855</v>
       </c>
@@ -10786,7 +10807,7 @@
       <c r="I34" s="2">
         <v>34</v>
       </c>
-      <c r="J34" s="83">
+      <c r="J34" s="75">
         <f t="shared" si="6"/>
         <v>0.53424657534246578</v>
       </c>
@@ -10796,7 +10817,7 @@
       <c r="L34" s="2">
         <v>139</v>
       </c>
-      <c r="M34" s="83">
+      <c r="M34" s="75">
         <f t="shared" si="7"/>
         <v>0.48134328358208955</v>
       </c>
@@ -10868,7 +10889,7 @@
       <c r="B35" s="34">
         <v>302</v>
       </c>
-      <c r="C35" s="67">
+      <c r="C35" s="66">
         <f t="shared" si="4"/>
         <v>21.571428571428573</v>
       </c>
@@ -10881,7 +10902,7 @@
       <c r="F35" s="2">
         <v>9</v>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="75">
         <f t="shared" si="5"/>
         <v>0.35714285714285715</v>
       </c>
@@ -10891,7 +10912,7 @@
       <c r="I35" s="2">
         <v>33</v>
       </c>
-      <c r="J35" s="83">
+      <c r="J35" s="75">
         <f t="shared" si="6"/>
         <v>0.45</v>
       </c>
@@ -10901,7 +10922,7 @@
       <c r="L35" s="2">
         <v>124</v>
       </c>
-      <c r="M35" s="83">
+      <c r="M35" s="75">
         <f t="shared" si="7"/>
         <v>0.48760330578512395</v>
       </c>
@@ -10973,11 +10994,11 @@
       <c r="B36" s="36">
         <v>12</v>
       </c>
-      <c r="C36" s="67">
+      <c r="C36" s="66">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="D36" s="66">
+      <c r="D36" s="65">
         <v>12</v>
       </c>
       <c r="E36" s="36">
@@ -10986,7 +11007,7 @@
       <c r="F36" s="1">
         <v>0</v>
       </c>
-      <c r="G36" s="83">
+      <c r="G36" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -10996,7 +11017,7 @@
       <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="J36" s="83">
+      <c r="J36" s="75">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
@@ -11006,7 +11027,7 @@
       <c r="L36" s="1">
         <v>10</v>
       </c>
-      <c r="M36" s="83">
+      <c r="M36" s="75">
         <f t="shared" si="7"/>
         <v>0.47368421052631576</v>
       </c>
@@ -11082,7 +11103,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="D37" s="66">
+      <c r="D37" s="65">
         <v>10</v>
       </c>
       <c r="E37" s="36">
@@ -11091,7 +11112,7 @@
       <c r="F37" s="1">
         <v>0</v>
       </c>
-      <c r="G37" s="83">
+      <c r="G37" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11101,7 +11122,7 @@
       <c r="I37" s="1">
         <v>1</v>
       </c>
-      <c r="J37" s="83">
+      <c r="J37" s="75">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
@@ -11111,7 +11132,7 @@
       <c r="L37" s="1">
         <v>5</v>
       </c>
-      <c r="M37" s="83">
+      <c r="M37" s="75">
         <f t="shared" si="7"/>
         <v>0.6428571428571429</v>
       </c>
@@ -11172,7 +11193,7 @@
       <c r="AF37" s="1">
         <v>0</v>
       </c>
-      <c r="AG37" s="66">
+      <c r="AG37" s="65">
         <v>0</v>
       </c>
     </row>
@@ -11183,7 +11204,7 @@
       <c r="B38" s="34">
         <v>424</v>
       </c>
-      <c r="C38" s="67">
+      <c r="C38" s="66">
         <f t="shared" si="4"/>
         <v>23.555555555555557</v>
       </c>
@@ -11196,7 +11217,7 @@
       <c r="F38" s="2">
         <v>4</v>
       </c>
-      <c r="G38" s="83">
+      <c r="G38" s="75">
         <f t="shared" si="5"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11206,7 +11227,7 @@
       <c r="I38" s="2">
         <v>29</v>
       </c>
-      <c r="J38" s="83">
+      <c r="J38" s="75">
         <f t="shared" si="6"/>
         <v>0.62337662337662336</v>
       </c>
@@ -11216,7 +11237,7 @@
       <c r="L38" s="2">
         <v>145</v>
       </c>
-      <c r="M38" s="83">
+      <c r="M38" s="75">
         <f t="shared" si="7"/>
         <v>0.55108359133126938</v>
       </c>
@@ -11288,7 +11309,7 @@
       <c r="B39" s="34">
         <v>38</v>
       </c>
-      <c r="C39" s="67">
+      <c r="C39" s="66">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
@@ -11301,7 +11322,7 @@
       <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="83">
+      <c r="G39" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11311,7 +11332,7 @@
       <c r="I39" s="2">
         <v>2</v>
       </c>
-      <c r="J39" s="83">
+      <c r="J39" s="75">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
@@ -11321,7 +11342,7 @@
       <c r="L39" s="2">
         <v>14</v>
       </c>
-      <c r="M39" s="83">
+      <c r="M39" s="75">
         <f t="shared" si="7"/>
         <v>0.58823529411764708</v>
       </c>
@@ -11393,11 +11414,11 @@
       <c r="B40" s="36">
         <v>82</v>
       </c>
-      <c r="C40" s="67">
+      <c r="C40" s="66">
         <f t="shared" si="4"/>
         <v>20.5</v>
       </c>
-      <c r="D40" s="66">
+      <c r="D40" s="65">
         <v>28</v>
       </c>
       <c r="E40" s="36">
@@ -11406,7 +11427,7 @@
       <c r="F40" s="1">
         <v>2</v>
       </c>
-      <c r="G40" s="83">
+      <c r="G40" s="75">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
@@ -11416,7 +11437,7 @@
       <c r="I40" s="1">
         <v>10</v>
       </c>
-      <c r="J40" s="83">
+      <c r="J40" s="75">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
@@ -11426,7 +11447,7 @@
       <c r="L40" s="1">
         <v>42</v>
       </c>
-      <c r="M40" s="83">
+      <c r="M40" s="75">
         <f t="shared" si="7"/>
         <v>0.48148148148148145</v>
       </c>
@@ -11487,7 +11508,7 @@
       <c r="AF40" s="1">
         <v>1</v>
       </c>
-      <c r="AG40" s="66">
+      <c r="AG40" s="65">
         <v>0</v>
       </c>
     </row>
@@ -11498,7 +11519,7 @@
       <c r="B41" s="34">
         <v>158</v>
       </c>
-      <c r="C41" s="67">
+      <c r="C41" s="66">
         <f t="shared" si="4"/>
         <v>17.555555555555557</v>
       </c>
@@ -11511,7 +11532,7 @@
       <c r="F41" s="2">
         <v>5</v>
       </c>
-      <c r="G41" s="83">
+      <c r="G41" s="75">
         <f t="shared" si="5"/>
         <v>0.44444444444444442</v>
       </c>
@@ -11521,7 +11542,7 @@
       <c r="I41" s="2">
         <v>23</v>
       </c>
-      <c r="J41" s="83">
+      <c r="J41" s="75">
         <f t="shared" si="6"/>
         <v>0.43902439024390244</v>
       </c>
@@ -11531,7 +11552,7 @@
       <c r="L41" s="2">
         <v>86</v>
       </c>
-      <c r="M41" s="83">
+      <c r="M41" s="75">
         <f t="shared" si="7"/>
         <v>0.47878787878787876</v>
       </c>
@@ -11603,7 +11624,7 @@
       <c r="B42" s="34">
         <v>25</v>
       </c>
-      <c r="C42" s="67">
+      <c r="C42" s="66">
         <f t="shared" si="4"/>
         <v>12.5</v>
       </c>
@@ -11616,7 +11637,7 @@
       <c r="F42" s="2">
         <v>0</v>
       </c>
-      <c r="G42" s="83">
+      <c r="G42" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11626,7 +11647,7 @@
       <c r="I42" s="2">
         <v>2</v>
       </c>
-      <c r="J42" s="83">
+      <c r="J42" s="75">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
@@ -11636,7 +11657,7 @@
       <c r="L42" s="2">
         <v>15</v>
       </c>
-      <c r="M42" s="83">
+      <c r="M42" s="75">
         <f t="shared" si="7"/>
         <v>0.55882352941176472</v>
       </c>
@@ -11708,7 +11729,7 @@
       <c r="B43" s="34">
         <v>238</v>
       </c>
-      <c r="C43" s="67">
+      <c r="C43" s="66">
         <f t="shared" si="4"/>
         <v>26.444444444444443</v>
       </c>
@@ -11721,7 +11742,7 @@
       <c r="F43" s="2">
         <v>7</v>
       </c>
-      <c r="G43" s="83">
+      <c r="G43" s="75">
         <f t="shared" si="5"/>
         <v>0.22222222222222221</v>
       </c>
@@ -11731,7 +11752,7 @@
       <c r="I43" s="2">
         <v>24</v>
       </c>
-      <c r="J43" s="83">
+      <c r="J43" s="75">
         <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
@@ -11741,7 +11762,7 @@
       <c r="L43" s="2">
         <v>93</v>
       </c>
-      <c r="M43" s="83">
+      <c r="M43" s="75">
         <f t="shared" si="7"/>
         <v>0.44970414201183434</v>
       </c>
@@ -11813,11 +11834,11 @@
       <c r="B44" s="36">
         <v>69</v>
       </c>
-      <c r="C44" s="67">
+      <c r="C44" s="66">
         <f t="shared" si="4"/>
         <v>13.8</v>
       </c>
-      <c r="D44" s="66">
+      <c r="D44" s="65">
         <v>24</v>
       </c>
       <c r="E44" s="36">
@@ -11826,7 +11847,7 @@
       <c r="F44" s="1">
         <v>2</v>
       </c>
-      <c r="G44" s="83">
+      <c r="G44" s="75">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
@@ -11836,7 +11857,7 @@
       <c r="I44" s="1">
         <v>10</v>
       </c>
-      <c r="J44" s="83">
+      <c r="J44" s="75">
         <f t="shared" si="6"/>
         <v>0.56521739130434778</v>
       </c>
@@ -11846,7 +11867,7 @@
       <c r="L44" s="1">
         <v>49</v>
       </c>
-      <c r="M44" s="83">
+      <c r="M44" s="75">
         <f t="shared" si="7"/>
         <v>0.53773584905660377</v>
       </c>
@@ -11918,7 +11939,7 @@
       <c r="B45" s="34">
         <v>18</v>
       </c>
-      <c r="C45" s="67">
+      <c r="C45" s="66">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
@@ -11931,7 +11952,7 @@
       <c r="F45" s="2">
         <v>0</v>
       </c>
-      <c r="G45" s="83">
+      <c r="G45" s="75">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -11941,7 +11962,7 @@
       <c r="I45" s="2">
         <v>2</v>
       </c>
-      <c r="J45" s="83">
+      <c r="J45" s="75">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
@@ -11951,7 +11972,7 @@
       <c r="L45" s="2">
         <v>10</v>
       </c>
-      <c r="M45" s="83">
+      <c r="M45" s="75">
         <f t="shared" si="7"/>
         <v>0.52380952380952384</v>
       </c>
@@ -12023,7 +12044,7 @@
       <c r="B46" s="38">
         <v>6</v>
       </c>
-      <c r="C46" s="68">
+      <c r="C46" s="67">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
@@ -12036,7 +12057,7 @@
       <c r="F46" s="48">
         <v>1</v>
       </c>
-      <c r="G46" s="84">
+      <c r="G46" s="76">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -12046,7 +12067,7 @@
       <c r="I46" s="48">
         <v>3</v>
       </c>
-      <c r="J46" s="84">
+      <c r="J46" s="76">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -12056,7 +12077,7 @@
       <c r="L46" s="48">
         <v>9</v>
       </c>
-      <c r="M46" s="84">
+      <c r="M46" s="76">
         <f t="shared" si="7"/>
         <v>0.30769230769230771</v>
       </c>
@@ -12200,43 +12221,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="77" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="78"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="77" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="78"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="77" t="s">
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="78"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="77" t="s">
+      <c r="M1" s="84"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
       <c r="AD1" s="55"/>
       <c r="AE1" s="55"/>
       <c r="AF1" s="55"/>
@@ -12345,7 +12366,7 @@
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="86" t="s">
         <v>75</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -12371,7 +12392,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>4</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>0.42857142857142855</v>
       </c>
@@ -12383,7 +12404,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>14</v>
       </c>
-      <c r="K3" s="81">
+      <c r="K3" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>0.54838709677419351</v>
       </c>
@@ -12395,7 +12416,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>62</v>
       </c>
-      <c r="N3" s="81">
+      <c r="N3" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
         <v>0.52671755725190839</v>
       </c>
@@ -12481,7 +12502,7 @@
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
+      <c r="A4" s="86"/>
       <c r="B4" s="7" t="s">
         <v>37</v>
       </c>
@@ -12505,7 +12526,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>4</v>
       </c>
-      <c r="H4" s="81">
+      <c r="H4" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>0.42857142857142855</v>
       </c>
@@ -12517,7 +12538,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>14</v>
       </c>
-      <c r="K4" s="81">
+      <c r="K4" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>0.54838709677419351</v>
       </c>
@@ -12529,7 +12550,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>62</v>
       </c>
-      <c r="N4" s="81">
+      <c r="N4" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
         <v>0.52671755725190839</v>
       </c>
@@ -12615,7 +12636,7 @@
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
+      <c r="A5" s="86"/>
       <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
@@ -12639,7 +12660,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>10</v>
       </c>
-      <c r="H5" s="81">
+      <c r="H5" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>0.375</v>
       </c>
@@ -12651,7 +12672,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>38</v>
       </c>
-      <c r="K5" s="81">
+      <c r="K5" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>0.44117647058823528</v>
       </c>
@@ -12663,7 +12684,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>144</v>
       </c>
-      <c r="N5" s="81">
+      <c r="N5" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
         <v>0.5</v>
       </c>
@@ -12749,7 +12770,7 @@
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
+      <c r="A6" s="86"/>
       <c r="B6" s="7" t="s">
         <v>19</v>
       </c>
@@ -12773,7 +12794,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>2</v>
       </c>
-      <c r="H6" s="81">
+      <c r="H6" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>0.81818181818181823</v>
       </c>
@@ -12785,7 +12806,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>16</v>
       </c>
-      <c r="K6" s="81">
+      <c r="K6" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>0.65217391304347827</v>
       </c>
@@ -12797,7 +12818,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>79</v>
       </c>
-      <c r="N6" s="81">
+      <c r="N6" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
         <v>0.572972972972973</v>
       </c>
@@ -12883,7 +12904,7 @@
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="80"/>
+      <c r="A7" s="86"/>
       <c r="B7" s="7" t="s">
         <v>25</v>
       </c>
@@ -12907,7 +12928,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>1</v>
       </c>
-      <c r="H7" s="81">
+      <c r="H7" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>0.66666666666666663</v>
       </c>
@@ -12919,7 +12940,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>5</v>
       </c>
-      <c r="K7" s="81">
+      <c r="K7" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>0.58333333333333337</v>
       </c>
@@ -12931,7 +12952,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>19</v>
       </c>
-      <c r="N7" s="81">
+      <c r="N7" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
         <v>0.58695652173913049</v>
       </c>
@@ -13017,7 +13038,7 @@
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
+      <c r="A8" s="86"/>
       <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
@@ -13041,7 +13062,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>2</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>0.5</v>
       </c>
@@ -13053,7 +13074,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>9</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>0.52631578947368418</v>
       </c>
@@ -13065,7 +13086,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>41</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
         <v>0.48749999999999999</v>
       </c>
@@ -13151,7 +13172,7 @@
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="80"/>
+      <c r="A9" s="86"/>
       <c r="B9" s="7" t="s">
         <v>78</v>
       </c>
@@ -13175,7 +13196,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="81" t="str">
+      <c r="H9" s="73" t="str">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13187,7 +13208,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="81" t="str">
+      <c r="K9" s="73" t="str">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13199,7 +13220,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="81" t="str">
+      <c r="N9" s="73" t="str">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13285,7 +13306,7 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="80"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="7" t="s">
         <v>78</v>
       </c>
@@ -13309,7 +13330,7 @@
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="82" t="str">
+      <c r="H10" s="74" t="str">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13321,7 +13342,7 @@
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="82" t="str">
+      <c r="K10" s="74" t="str">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13333,7 +13354,7 @@
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="82" t="str">
+      <c r="N10" s="74" t="str">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
         <v>-</v>
       </c>
@@ -13520,43 +13541,43 @@
     </row>
     <row r="14" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="77" t="s">
+      <c r="D15" s="84"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="78"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="77" t="s">
+      <c r="G15" s="84"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="78"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="77" t="s">
+      <c r="J15" s="84"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="78"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="77" t="s">
+      <c r="M15" s="84"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="78"/>
-      <c r="AC15" s="78"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
       <c r="AD15" s="55"/>
       <c r="AE15" s="55"/>
       <c r="AF15" s="55"/>
@@ -13665,7 +13686,7 @@
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="82" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -13801,7 +13822,7 @@
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
+      <c r="A18" s="82"/>
       <c r="B18" s="7" t="s">
         <v>42</v>
       </c>
@@ -13935,7 +13956,7 @@
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="76"/>
+      <c r="A19" s="82"/>
       <c r="B19" s="7" t="s">
         <v>52</v>
       </c>
@@ -14069,7 +14090,7 @@
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
+      <c r="A20" s="82"/>
       <c r="B20" s="7" t="s">
         <v>19</v>
       </c>
@@ -14203,7 +14224,7 @@
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="76"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7" t="s">
         <v>3</v>
       </c>
@@ -14337,7 +14358,7 @@
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="76"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7" t="s">
         <v>14</v>
       </c>
@@ -14471,7 +14492,7 @@
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="76"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7" t="s">
         <v>80</v>
       </c>
@@ -14605,7 +14626,7 @@
       </c>
     </row>
     <row r="24" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="76"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7" t="s">
         <v>80</v>
       </c>

--- a/R63 Data.xlsx
+++ b/R63 Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Downloads\excel-filter-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A91CF7-A357-4FC7-829A-0E2A3C312009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA3F42B-FBAE-42FB-9D5E-016E9DABE754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5490" yWindow="4065" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
+    <workbookView xWindow="4905" yWindow="3210" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
   </bookViews>
   <sheets>
     <sheet name="Old Bow" sheetId="1" r:id="rId1"/>
@@ -916,6 +916,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -933,11 +938,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1565,7 +1565,7 @@
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="80" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2233,7 +2233,7 @@
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="80" t="s">
         <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3191,7 +3191,7 @@
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="80" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -4820,10 +4820,10 @@
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="F43" s="88"/>
+      <c r="F43" s="81"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="F45" s="88"/>
+      <c r="F45" s="81"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AD37" xr:uid="{EEC03B8F-669F-4FC0-BA62-50F3D395660C}"/>
@@ -4841,7 +4841,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="82" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4851,18 +4851,18 @@
       <c r="C3" s="54"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="83" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="83" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="54"/>
@@ -4895,43 +4895,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="83" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="84"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="83" t="s">
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="83" t="s">
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="84"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="84" t="s">
+      <c r="M1" s="87"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
-      <c r="Z1" s="84"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="85"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
+      <c r="Z1" s="87"/>
+      <c r="AA1" s="87"/>
+      <c r="AB1" s="87"/>
+      <c r="AC1" s="88"/>
     </row>
     <row r="2" spans="1:29" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -5020,7 +5020,7 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="89" t="s">
         <v>75</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -5136,7 +5136,7 @@
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="7" t="s">
         <v>46</v>
       </c>
@@ -5250,7 +5250,7 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
+      <c r="A5" s="89"/>
       <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
@@ -5364,7 +5364,7 @@
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
+      <c r="A6" s="89"/>
       <c r="B6" s="7" t="s">
         <v>51</v>
       </c>
@@ -5478,7 +5478,7 @@
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="7" t="s">
         <v>26</v>
       </c>
@@ -5592,7 +5592,7 @@
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
+      <c r="A8" s="89"/>
       <c r="B8" s="7" t="s">
         <v>38</v>
       </c>
@@ -5706,7 +5706,7 @@
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="86"/>
+      <c r="A9" s="89"/>
       <c r="B9" s="7" t="s">
         <v>78</v>
       </c>
@@ -5820,7 +5820,7 @@
       </c>
     </row>
     <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+      <c r="A10" s="89"/>
       <c r="B10" s="7" t="s">
         <v>78</v>
       </c>
@@ -6015,43 +6015,43 @@
     </row>
     <row r="14" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="83" t="s">
+      <c r="D15" s="87"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="84"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="83" t="s">
+      <c r="G15" s="87"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="84"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="83" t="s">
+      <c r="J15" s="87"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="84"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="83" t="s">
+      <c r="M15" s="87"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="85"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="87"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="87"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="87"/>
+      <c r="AB15" s="87"/>
+      <c r="AC15" s="88"/>
     </row>
     <row r="16" spans="1:29" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
@@ -6140,7 +6140,7 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="85" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -6256,7 +6256,7 @@
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="82"/>
+      <c r="A18" s="85"/>
       <c r="B18" s="7" t="s">
         <v>2</v>
       </c>
@@ -6370,7 +6370,7 @@
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
+      <c r="A19" s="85"/>
       <c r="B19" s="7" t="s">
         <v>45</v>
       </c>
@@ -6484,7 +6484,7 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="82"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="7" t="s">
         <v>20</v>
       </c>
@@ -6598,7 +6598,7 @@
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="82"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="7" t="s">
         <v>35</v>
       </c>
@@ -6712,7 +6712,7 @@
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="82"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="7" t="s">
         <v>29</v>
       </c>
@@ -6826,7 +6826,7 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="82"/>
+      <c r="A23" s="85"/>
       <c r="B23" s="7" t="s">
         <v>80</v>
       </c>
@@ -6940,7 +6940,7 @@
       </c>
     </row>
     <row r="24" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="7" t="s">
         <v>80</v>
       </c>
@@ -7846,11 +7846,11 @@
         <v>35</v>
       </c>
       <c r="B6" s="34">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C6" s="66">
         <f t="shared" si="0"/>
-        <v>11.75</v>
+        <v>11.529411764705882</v>
       </c>
       <c r="D6" s="35">
         <v>20</v>
@@ -7859,31 +7859,31 @@
         <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="75">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="H6" s="34">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J6" s="75">
         <f t="shared" si="2"/>
-        <v>0.44117647058823528</v>
+        <v>0.43835616438356162</v>
       </c>
       <c r="K6" s="34">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L6" s="2">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="M6" s="75">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.4935064935064935</v>
       </c>
       <c r="N6" s="34">
         <v>0</v>
@@ -7928,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="AB6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC6" s="2">
         <v>0</v>
@@ -7937,7 +7937,7 @@
         <v>3</v>
       </c>
       <c r="AE6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF6" s="2">
         <v>3</v>
@@ -8056,56 +8056,56 @@
         <v>42</v>
       </c>
       <c r="B8" s="34">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C8" s="66">
         <f t="shared" si="0"/>
-        <v>15.888888888888889</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="D8" s="35">
         <v>31</v>
       </c>
       <c r="E8" s="34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
       </c>
       <c r="G8" s="75">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>0.6</v>
       </c>
       <c r="H8" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I8" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="75">
         <f t="shared" si="2"/>
-        <v>0.48717948717948717</v>
+        <v>0.51162790697674421</v>
       </c>
       <c r="K8" s="34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L8" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M8" s="75">
         <f t="shared" si="3"/>
-        <v>0.48780487804878048</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="N8" s="34">
         <v>0</v>
       </c>
       <c r="O8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P8" s="2">
         <v>1</v>
       </c>
       <c r="Q8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" s="2">
         <v>0</v>
@@ -8150,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="AF8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="47">
         <v>1</v>
@@ -8266,11 +8266,11 @@
         <v>116</v>
       </c>
       <c r="B10" s="36">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C10" s="66">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="D10" s="65">
         <v>14</v>
@@ -8279,31 +8279,31 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="75">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J10" s="75">
         <f t="shared" si="2"/>
-        <v>0.3888888888888889</v>
+        <v>0.39130434782608697</v>
       </c>
       <c r="K10" s="36">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L10" s="1">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M10" s="75">
         <f t="shared" si="3"/>
-        <v>0.44285714285714284</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="N10" s="36">
         <v>0</v>
@@ -8348,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="AB10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="1">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" s="1">
         <v>0</v>
@@ -8371,11 +8371,11 @@
         <v>27</v>
       </c>
       <c r="B11" s="34">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C11" s="66">
         <f t="shared" si="0"/>
-        <v>15.25</v>
+        <v>14.2</v>
       </c>
       <c r="D11" s="35">
         <v>20</v>
@@ -8384,31 +8384,31 @@
         <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="75">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J11" s="75">
         <f t="shared" si="2"/>
-        <v>0.52631578947368418</v>
+        <v>0.47826086956521741</v>
       </c>
       <c r="K11" s="34">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L11" s="2">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M11" s="75">
         <f t="shared" si="3"/>
-        <v>0.48749999999999999</v>
+        <v>0.45744680851063829</v>
       </c>
       <c r="N11" s="34">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE11" s="2">
         <v>1</v>
@@ -8997,11 +8997,11 @@
         <v>50</v>
       </c>
       <c r="B17" s="34">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C17" s="66">
         <f t="shared" si="4"/>
-        <v>21.764705882352942</v>
+        <v>21.111111111111111</v>
       </c>
       <c r="D17" s="35">
         <v>31</v>
@@ -9010,31 +9010,31 @@
         <v>10</v>
       </c>
       <c r="F17" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="75">
         <f t="shared" si="5"/>
-        <v>0.58823529411764708</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="H17" s="34">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="6"/>
-        <v>0.54166666666666663</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="K17" s="34">
+        <v>166</v>
+      </c>
+      <c r="L17" s="2">
         <v>162</v>
-      </c>
-      <c r="L17" s="2">
-        <v>152</v>
       </c>
       <c r="M17" s="75">
         <f t="shared" si="7"/>
-        <v>0.51592356687898089</v>
+        <v>0.50609756097560976</v>
       </c>
       <c r="N17" s="34">
         <v>1</v>
@@ -9085,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="AD17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE17" s="2">
         <v>1</v>
@@ -9102,56 +9102,56 @@
         <v>52</v>
       </c>
       <c r="B18" s="34">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C18" s="66">
         <f t="shared" si="4"/>
-        <v>11.6</v>
+        <v>12.428571428571429</v>
       </c>
       <c r="D18" s="35">
         <v>19</v>
       </c>
       <c r="E18" s="34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="75">
         <f t="shared" si="5"/>
-        <v>0.2</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H18" s="34">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I18" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J18" s="75">
         <f t="shared" si="6"/>
-        <v>0.36363636363636365</v>
+        <v>0.41935483870967744</v>
       </c>
       <c r="K18" s="34">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="L18" s="2">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M18" s="75">
         <f t="shared" si="7"/>
-        <v>0.39534883720930231</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="N18" s="34">
         <v>0</v>
       </c>
       <c r="O18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" s="2">
         <v>0</v>
       </c>
       <c r="Q18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="2">
         <v>0</v>
@@ -9184,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC18" s="2">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>3</v>
       </c>
       <c r="AE18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="47">
         <v>0</v>
@@ -9207,11 +9207,11 @@
         <v>102</v>
       </c>
       <c r="B19" s="34">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C19" s="66">
         <f t="shared" si="4"/>
-        <v>18.8</v>
+        <v>17.5</v>
       </c>
       <c r="D19" s="35">
         <v>31</v>
@@ -9220,31 +9220,31 @@
         <v>4</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="75">
         <f t="shared" si="5"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H19" s="34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J19" s="75">
         <f t="shared" si="6"/>
-        <v>0.60869565217391308</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="K19" s="34">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L19" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M19" s="75">
         <f t="shared" si="7"/>
-        <v>0.56521739130434778</v>
+        <v>0.52830188679245282</v>
       </c>
       <c r="N19" s="34">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="AD19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" s="2">
         <v>1</v>
@@ -9312,11 +9312,11 @@
         <v>1</v>
       </c>
       <c r="B20" s="34">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C20" s="66">
         <f t="shared" si="4"/>
-        <v>29.875</v>
+        <v>29.111111111111111</v>
       </c>
       <c r="D20" s="35">
         <v>44</v>
@@ -9325,31 +9325,31 @@
         <v>4</v>
       </c>
       <c r="F20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="75">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="H20" s="34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" s="75">
         <f t="shared" si="6"/>
-        <v>0.44117647058823528</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="K20" s="34">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L20" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M20" s="75">
         <f t="shared" si="7"/>
-        <v>0.48684210526315791</v>
+        <v>0.46987951807228917</v>
       </c>
       <c r="N20" s="34">
         <v>1</v>
@@ -9400,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="AD20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="2">
         <v>1</v>
@@ -9627,56 +9627,56 @@
         <v>28</v>
       </c>
       <c r="B23" s="34">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C23" s="66">
         <f t="shared" si="4"/>
-        <v>15.666666666666666</v>
+        <v>16.2</v>
       </c>
       <c r="D23" s="35">
         <v>22</v>
       </c>
       <c r="E23" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2">
         <v>5</v>
       </c>
       <c r="G23" s="75">
         <f t="shared" si="5"/>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="H23" s="34">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I23" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="75">
         <f t="shared" si="6"/>
-        <v>0.47222222222222221</v>
+        <v>0.5</v>
       </c>
       <c r="K23" s="34">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L23" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M23" s="75">
         <f t="shared" si="7"/>
-        <v>0.4935064935064935</v>
+        <v>0.51190476190476186</v>
       </c>
       <c r="N23" s="34">
         <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="2">
         <v>1</v>
       </c>
       <c r="Q23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="1">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="AF23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG23" s="47">
         <v>0</v>
@@ -9732,11 +9732,11 @@
         <v>53</v>
       </c>
       <c r="B24" s="34">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C24" s="66">
         <f t="shared" si="4"/>
-        <v>17.875</v>
+        <v>17.777777777777779</v>
       </c>
       <c r="D24" s="35">
         <v>36</v>
@@ -9745,31 +9745,31 @@
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" s="75">
         <f t="shared" si="5"/>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H24" s="34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J24" s="75">
         <f t="shared" si="6"/>
-        <v>0.46875</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="K24" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L24" s="2">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="M24" s="75">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="N24" s="34">
         <v>0</v>
@@ -9820,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE24" s="2">
         <v>1</v>
@@ -10362,11 +10362,11 @@
         <v>2</v>
       </c>
       <c r="B30" s="34">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C30" s="66">
         <f t="shared" si="4"/>
-        <v>23.6</v>
+        <v>23.25</v>
       </c>
       <c r="D30" s="35">
         <v>35</v>
@@ -10375,31 +10375,31 @@
         <v>9</v>
       </c>
       <c r="F30" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G30" s="75">
         <f t="shared" si="5"/>
-        <v>0.6</v>
+        <v>0.5625</v>
       </c>
       <c r="H30" s="34">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I30" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J30" s="75">
         <f t="shared" si="6"/>
-        <v>0.55555555555555558</v>
+        <v>0.53731343283582089</v>
       </c>
       <c r="K30" s="34">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L30" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="M30" s="75">
         <f t="shared" si="7"/>
-        <v>0.52325581395348841</v>
+        <v>0.51102941176470584</v>
       </c>
       <c r="N30" s="34">
         <v>2</v>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="AD30" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30" s="2">
         <v>3</v>
@@ -10467,11 +10467,11 @@
         <v>54</v>
       </c>
       <c r="B31" s="34">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="C31" s="66">
         <f t="shared" si="4"/>
-        <v>27.055555555555557</v>
+        <v>26.894736842105264</v>
       </c>
       <c r="D31" s="35">
         <v>37</v>
@@ -10480,31 +10480,31 @@
         <v>7</v>
       </c>
       <c r="F31" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="75">
         <f t="shared" si="5"/>
-        <v>0.3888888888888889</v>
+        <v>0.36842105263157893</v>
       </c>
       <c r="H31" s="34">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J31" s="75">
         <f t="shared" si="6"/>
-        <v>0.46341463414634149</v>
+        <v>0.45977011494252873</v>
       </c>
       <c r="K31" s="34">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="L31" s="2">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="M31" s="75">
         <f t="shared" si="7"/>
-        <v>0.47941176470588237</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="N31" s="34">
         <v>1</v>
@@ -10549,7 +10549,7 @@
         <v>2</v>
       </c>
       <c r="AB31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC31" s="2">
         <v>0</v>
@@ -10558,7 +10558,7 @@
         <v>4</v>
       </c>
       <c r="AE31" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF31" s="2">
         <v>2</v>
@@ -10782,56 +10782,56 @@
         <v>40</v>
       </c>
       <c r="B34" s="34">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C34" s="66">
         <f t="shared" si="4"/>
-        <v>18.5</v>
+        <v>18.25</v>
       </c>
       <c r="D34" s="35">
         <v>29</v>
       </c>
       <c r="E34" s="34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G34" s="75">
         <f t="shared" si="5"/>
-        <v>0.42857142857142855</v>
+        <v>0.4375</v>
       </c>
       <c r="H34" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I34" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J34" s="75">
         <f t="shared" si="6"/>
-        <v>0.53424657534246578</v>
+        <v>0.53658536585365857</v>
       </c>
       <c r="K34" s="34">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="L34" s="2">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="M34" s="75">
         <f t="shared" si="7"/>
-        <v>0.48134328358208955</v>
+        <v>0.48675496688741721</v>
       </c>
       <c r="N34" s="34">
         <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P34" s="2">
         <v>4</v>
       </c>
       <c r="Q34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R34" s="2">
         <v>0</v>
@@ -10864,7 +10864,7 @@
         <v>1</v>
       </c>
       <c r="AB34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC34" s="2">
         <v>0</v>
@@ -10873,10 +10873,10 @@
         <v>1</v>
       </c>
       <c r="AE34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF34" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG34" s="47">
         <v>1</v>
@@ -10887,11 +10887,11 @@
         <v>17</v>
       </c>
       <c r="B35" s="34">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="C35" s="66">
         <f t="shared" si="4"/>
-        <v>21.571428571428573</v>
+        <v>21.8</v>
       </c>
       <c r="D35" s="35">
         <v>32</v>
@@ -10900,31 +10900,31 @@
         <v>5</v>
       </c>
       <c r="F35" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G35" s="75">
         <f t="shared" si="5"/>
-        <v>0.35714285714285715</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H35" s="34">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I35" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J35" s="75">
         <f t="shared" si="6"/>
-        <v>0.45</v>
+        <v>0.44615384615384618</v>
       </c>
       <c r="K35" s="34">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L35" s="2">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="M35" s="75">
         <f t="shared" si="7"/>
-        <v>0.48760330578512395</v>
+        <v>0.48091603053435117</v>
       </c>
       <c r="N35" s="34">
         <v>2</v>
@@ -10969,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC35" s="2">
         <v>0</v>
@@ -10978,7 +10978,7 @@
         <v>4</v>
       </c>
       <c r="AE35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF35" s="2">
         <v>3</v>
@@ -11202,56 +11202,56 @@
         <v>6</v>
       </c>
       <c r="B38" s="34">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C38" s="66">
         <f t="shared" si="4"/>
-        <v>23.555555555555557</v>
+        <v>23.157894736842106</v>
       </c>
       <c r="D38" s="35">
         <v>37</v>
       </c>
       <c r="E38" s="34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
       </c>
       <c r="G38" s="75">
         <f t="shared" si="5"/>
-        <v>0.77777777777777779</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="H38" s="34">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I38" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J38" s="75">
         <f t="shared" si="6"/>
-        <v>0.62337662337662336</v>
+        <v>0.62962962962962965</v>
       </c>
       <c r="K38" s="34">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L38" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M38" s="75">
         <f t="shared" si="7"/>
-        <v>0.55108359133126938</v>
+        <v>0.55786350148367958</v>
       </c>
       <c r="N38" s="34">
         <v>2</v>
       </c>
       <c r="O38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" s="2">
         <v>3</v>
       </c>
       <c r="Q38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" s="2">
         <v>0</v>
@@ -11296,7 +11296,7 @@
         <v>4</v>
       </c>
       <c r="AF38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG38" s="47">
         <v>3</v>
@@ -11727,56 +11727,56 @@
         <v>4</v>
       </c>
       <c r="B43" s="34">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C43" s="66">
         <f t="shared" si="4"/>
-        <v>26.444444444444443</v>
+        <v>25.6</v>
       </c>
       <c r="D43" s="35">
         <v>41</v>
       </c>
       <c r="E43" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="2">
         <v>7</v>
       </c>
       <c r="G43" s="75">
         <f t="shared" si="5"/>
-        <v>0.22222222222222221</v>
+        <v>0.3</v>
       </c>
       <c r="H43" s="34">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I43" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J43" s="75">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0.43181818181818182</v>
       </c>
       <c r="K43" s="34">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L43" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="M43" s="75">
         <f t="shared" si="7"/>
-        <v>0.44970414201183434</v>
+        <v>0.46994535519125685</v>
       </c>
       <c r="N43" s="34">
         <v>0</v>
       </c>
       <c r="O43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P43" s="2">
         <v>3</v>
       </c>
       <c r="Q43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -11821,7 +11821,7 @@
         <v>2</v>
       </c>
       <c r="AF43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG43" s="47">
         <v>0</v>
@@ -11832,11 +11832,11 @@
         <v>107</v>
       </c>
       <c r="B44" s="36">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C44" s="66">
         <f t="shared" si="4"/>
-        <v>13.8</v>
+        <v>14.166666666666666</v>
       </c>
       <c r="D44" s="65">
         <v>24</v>
@@ -11845,31 +11845,31 @@
         <v>3</v>
       </c>
       <c r="F44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" s="75">
         <f t="shared" si="5"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H44" s="36">
+        <v>15</v>
+      </c>
+      <c r="I44" s="1">
         <v>13</v>
-      </c>
-      <c r="I44" s="1">
-        <v>10</v>
       </c>
       <c r="J44" s="75">
         <f t="shared" si="6"/>
-        <v>0.56521739130434778</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="K44" s="36">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L44" s="1">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M44" s="75">
         <f t="shared" si="7"/>
-        <v>0.53773584905660377</v>
+        <v>0.51587301587301593</v>
       </c>
       <c r="N44" s="34">
         <v>0</v>
@@ -11914,7 +11914,7 @@
         <v>2</v>
       </c>
       <c r="AB44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC44" s="2">
         <v>0</v>
@@ -11923,7 +11923,7 @@
         <v>0</v>
       </c>
       <c r="AE44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF44" s="1">
         <v>1</v>
@@ -12199,6 +12199,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12221,43 +12222,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="83" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="84"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="83" t="s">
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="83" t="s">
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="84"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="83" t="s">
+      <c r="M1" s="87"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
-      <c r="Z1" s="84"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="84"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
+      <c r="Z1" s="87"/>
+      <c r="AA1" s="87"/>
+      <c r="AB1" s="87"/>
+      <c r="AC1" s="87"/>
       <c r="AD1" s="55"/>
       <c r="AE1" s="55"/>
       <c r="AF1" s="55"/>
@@ -12366,7 +12367,7 @@
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="89" t="s">
         <v>75</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -12502,7 +12503,7 @@
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="7" t="s">
         <v>37</v>
       </c>
@@ -12636,17 +12637,17 @@
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
+      <c r="A5" s="89"/>
       <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="13">
         <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D5" s="59">
         <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>11.75</v>
+        <v>11.529411764705882</v>
       </c>
       <c r="E5" s="14">
         <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
@@ -12658,35 +12659,35 @@
       </c>
       <c r="G5" s="26">
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>0.375</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="I5" s="13">
         <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J5" s="26">
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K5" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>0.44117647058823528</v>
+        <v>0.43835616438356162</v>
       </c>
       <c r="L5" s="13">
         <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="M5" s="26">
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="N5" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>0.5</v>
+        <v>0.4935064935064935</v>
       </c>
       <c r="O5" s="13">
         <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
@@ -12702,7 +12703,7 @@
       </c>
       <c r="R5" s="26">
         <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" s="26">
         <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
@@ -12726,7 +12727,7 @@
       </c>
       <c r="X5" s="26">
         <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y5" s="26">
         <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
@@ -12770,7 +12771,7 @@
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
+      <c r="A6" s="89"/>
       <c r="B6" s="7" t="s">
         <v>19</v>
       </c>
@@ -12904,7 +12905,7 @@
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="7" t="s">
         <v>25</v>
       </c>
@@ -13038,17 +13039,17 @@
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
+      <c r="A8" s="89"/>
       <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="13">
         <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D8" s="59">
         <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>15.25</v>
+        <v>14.2</v>
       </c>
       <c r="E8" s="14">
         <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
@@ -13060,35 +13061,35 @@
       </c>
       <c r="G8" s="26">
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="73">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="13">
         <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="26">
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K8" s="73">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>0.52631578947368418</v>
+        <v>0.47826086956521741</v>
       </c>
       <c r="L8" s="13">
         <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M8" s="26">
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N8" s="73">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>0.48749999999999999</v>
+        <v>0.45744680851063829</v>
       </c>
       <c r="O8" s="13">
         <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
@@ -13112,7 +13113,7 @@
       </c>
       <c r="T8" s="26">
         <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" s="26">
         <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
@@ -13172,7 +13173,7 @@
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="86"/>
+      <c r="A9" s="89"/>
       <c r="B9" s="7" t="s">
         <v>78</v>
       </c>
@@ -13306,7 +13307,7 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
+      <c r="A10" s="89"/>
       <c r="B10" s="7" t="s">
         <v>78</v>
       </c>
@@ -13442,21 +13443,21 @@
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="D11" s="8">
         <f>SUM(D3:D10)</f>
-        <v>70.142857142857139</v>
+        <v>68.872268907563026</v>
       </c>
       <c r="H11" s="9">
         <f>AVERAGE(H3:H10)</f>
-        <v>0.53616522366522368</v>
+        <v>0.51582208641032168</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="9">
         <f>AVERAGE(K3:K10)</f>
-        <v>0.54996228333118635</v>
+        <v>0.54148307897899628</v>
       </c>
       <c r="N11" s="9">
         <f>AVERAGE(N3:N10)</f>
-        <v>0.53347743486931998</v>
+        <v>0.52738631853884199</v>
       </c>
       <c r="O11" s="5">
         <f>SUM(O3:O10)</f>
@@ -13472,7 +13473,7 @@
       </c>
       <c r="R11" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="0"/>
@@ -13480,7 +13481,7 @@
       </c>
       <c r="T11" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
@@ -13496,7 +13497,7 @@
       </c>
       <c r="X11" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y11" s="5">
         <f t="shared" si="0"/>
@@ -13541,43 +13542,43 @@
     </row>
     <row r="14" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="83" t="s">
+      <c r="D15" s="87"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="84"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="83" t="s">
+      <c r="G15" s="87"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="84"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="83" t="s">
+      <c r="J15" s="87"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="84"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="83" t="s">
+      <c r="M15" s="87"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="87"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="87"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="87"/>
+      <c r="AB15" s="87"/>
+      <c r="AC15" s="87"/>
       <c r="AD15" s="55"/>
       <c r="AE15" s="55"/>
       <c r="AF15" s="55"/>
@@ -13686,7 +13687,7 @@
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="85" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -13694,11 +13695,11 @@
       </c>
       <c r="C17" s="13">
         <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D17" s="59">
         <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>11.75</v>
+        <v>11.529411764705882</v>
       </c>
       <c r="E17" s="14">
         <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
@@ -13710,35 +13711,35 @@
       </c>
       <c r="G17" s="26">
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="27">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>0.375</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="I17" s="13">
         <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J17" s="26">
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K17" s="27">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>0.44117647058823528</v>
+        <v>0.43835616438356162</v>
       </c>
       <c r="L17" s="13">
         <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="M17" s="26">
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="N17" s="27">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>0.5</v>
+        <v>0.4935064935064935</v>
       </c>
       <c r="O17" s="13">
         <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
@@ -13754,7 +13755,7 @@
       </c>
       <c r="R17" s="26">
         <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17" s="26">
         <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
@@ -13778,7 +13779,7 @@
       </c>
       <c r="X17" s="26">
         <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y17" s="26">
         <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
@@ -13822,17 +13823,17 @@
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="82"/>
+      <c r="A18" s="85"/>
       <c r="B18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="13">
         <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="D18" s="59">
         <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>15.888888888888889</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="E18" s="14">
         <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
@@ -13840,7 +13841,7 @@
       </c>
       <c r="F18" s="13">
         <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="26">
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
@@ -13848,31 +13849,31 @@
       </c>
       <c r="H18" s="27">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0.55555555555555558</v>
+        <v>0.6</v>
       </c>
       <c r="I18" s="13">
         <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J18" s="26">
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="27">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0.48717948717948717</v>
+        <v>0.51162790697674421</v>
       </c>
       <c r="L18" s="13">
         <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M18" s="26">
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N18" s="27">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0.48780487804878048</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="O18" s="13">
         <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
@@ -13880,7 +13881,7 @@
       </c>
       <c r="P18" s="26">
         <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="26">
         <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
@@ -13904,7 +13905,7 @@
       </c>
       <c r="V18" s="26">
         <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18" s="26">
         <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
@@ -13920,7 +13921,7 @@
       </c>
       <c r="Z18" s="26">
         <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="26">
         <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
@@ -13956,17 +13957,17 @@
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
+      <c r="A19" s="85"/>
       <c r="B19" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C19" s="13">
         <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="D19" s="59">
         <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>11.6</v>
+        <v>12.428571428571429</v>
       </c>
       <c r="E19" s="14">
         <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -13974,39 +13975,39 @@
       </c>
       <c r="F19" s="13">
         <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="26">
         <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="27">
         <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>0.2</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I19" s="13">
         <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J19" s="26">
         <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K19" s="27">
         <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>0.36363636363636365</v>
+        <v>0.41935483870967744</v>
       </c>
       <c r="L19" s="13">
         <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="M19" s="26">
         <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="N19" s="27">
         <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>0.39534883720930231</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="O19" s="13">
         <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -14014,7 +14015,7 @@
       </c>
       <c r="P19" s="26">
         <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="26">
         <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -14022,7 +14023,7 @@
       </c>
       <c r="R19" s="26">
         <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" s="26">
         <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -14038,7 +14039,7 @@
       </c>
       <c r="V19" s="26">
         <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="26">
         <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -14046,7 +14047,7 @@
       </c>
       <c r="X19" s="26">
         <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="26">
         <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -14054,7 +14055,7 @@
       </c>
       <c r="Z19" s="26">
         <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="26">
         <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
@@ -14090,7 +14091,7 @@
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="82"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="7" t="s">
         <v>19</v>
       </c>
@@ -14224,7 +14225,7 @@
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="82"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="7" t="s">
         <v>3</v>
       </c>
@@ -14358,7 +14359,7 @@
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="82"/>
+      <c r="A22" s="85"/>
       <c r="B22" s="7" t="s">
         <v>14</v>
       </c>
@@ -14492,7 +14493,7 @@
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="82"/>
+      <c r="A23" s="85"/>
       <c r="B23" s="7" t="s">
         <v>80</v>
       </c>
@@ -14626,7 +14627,7 @@
       </c>
     </row>
     <row r="24" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="7" t="s">
         <v>80</v>
       </c>
@@ -14762,21 +14763,21 @@
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="D25" s="8">
         <f>SUM(D17:D24)</f>
-        <v>88.50873015873016</v>
+        <v>90.327824463118588</v>
       </c>
       <c r="H25" s="9">
         <f>AVERAGE(H17:H24)</f>
-        <v>0.44648268398268404</v>
+        <v>0.46449933508757041</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="9">
         <f>AVERAGE(K17:K24)</f>
-        <v>0.47127251152265187</v>
+        <v>0.48416360963363475</v>
       </c>
       <c r="N25" s="9">
         <f>AVERAGE(N17:N24)</f>
-        <v>0.48437535777279478</v>
+        <v>0.49259270595776722</v>
       </c>
       <c r="O25" s="5">
         <f>SUM(O17:O24)</f>
@@ -14784,7 +14785,7 @@
       </c>
       <c r="P25" s="5">
         <f t="shared" ref="P25:AH25" si="1">SUM(P17:P24)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="1"/>
@@ -14792,7 +14793,7 @@
       </c>
       <c r="R25" s="5">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S25" s="5">
         <f t="shared" si="1"/>
@@ -14808,7 +14809,7 @@
       </c>
       <c r="V25" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W25" s="5">
         <f t="shared" si="1"/>
@@ -14816,7 +14817,7 @@
       </c>
       <c r="X25" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y25" s="5">
         <f t="shared" si="1"/>
@@ -14824,7 +14825,7 @@
       </c>
       <c r="Z25" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="1"/>
@@ -14948,7 +14949,7 @@
       </c>
       <c r="D35" s="14" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 2), O25:AC25, 0))</f>
-        <v>Presidio</v>
+        <v>Rocket Facility</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14961,7 +14962,7 @@
       </c>
       <c r="D36" s="18" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 3), O25:AC25, 0))</f>
-        <v>Streets of Milan</v>
+        <v>Rocket Facility</v>
       </c>
     </row>
   </sheetData>

--- a/R63 Data.xlsx
+++ b/R63 Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brett\Downloads\excel-filter-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA3F42B-FBAE-42FB-9D5E-016E9DABE754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC91A16E-91A7-4C4E-B1B0-8CF66079088C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="3210" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{B81E1BB1-8459-4D85-A2AA-65951E65A37B}"/>
   </bookViews>
   <sheets>
     <sheet name="Old Bow" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Match Analyzer BA" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">BA!$A$1:$AG$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">BA!$A$1:$AG$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Old Bow'!$A$1:$AD$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="127">
   <si>
     <t>Player</t>
   </si>
@@ -685,7 +685,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -937,6 +937,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7298,7 +7304,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA548192-1F03-46EA-8AB8-115EB9A7CE5D}">
-  <dimension ref="A1:AG46"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -7428,8 +7434,8 @@
       <c r="B2" s="34">
         <v>95</v>
       </c>
-      <c r="C2" s="66">
-        <f t="shared" ref="C2:C12" si="0">B2/(E2+F2)</f>
+      <c r="C2" s="90">
+        <f>B2/(E2+F2)</f>
         <v>13.571428571428571</v>
       </c>
       <c r="D2" s="35">
@@ -7438,88 +7444,88 @@
       <c r="E2" s="34">
         <v>3</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="91">
         <v>4</v>
       </c>
       <c r="G2" s="75">
-        <f t="shared" ref="G2:G12" si="1">E2/(E2+F2)</f>
+        <f>E2/(E2+F2)</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="H2" s="34">
         <v>17</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="91">
         <v>14</v>
       </c>
       <c r="J2" s="75">
-        <f t="shared" ref="J2:J12" si="2">H2/(H2+I2)</f>
+        <f>H2/(H2+I2)</f>
         <v>0.54838709677419351</v>
       </c>
       <c r="K2" s="34">
         <v>69</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="91">
         <v>62</v>
       </c>
       <c r="M2" s="75">
-        <f t="shared" ref="M2:M12" si="3">K2/(K2+L2)</f>
+        <f>K2/(K2+L2)</f>
         <v>0.52671755725190839</v>
       </c>
       <c r="N2" s="34">
         <v>1</v>
       </c>
-      <c r="O2" s="2">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2">
-        <v>2</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF2" s="2">
+      <c r="O2" s="91">
+        <v>1</v>
+      </c>
+      <c r="P2" s="91">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="91">
+        <v>0</v>
+      </c>
+      <c r="R2" s="91">
+        <v>0</v>
+      </c>
+      <c r="S2" s="91">
+        <v>0</v>
+      </c>
+      <c r="T2" s="91">
+        <v>0</v>
+      </c>
+      <c r="U2" s="91">
+        <v>2</v>
+      </c>
+      <c r="V2" s="91">
+        <v>0</v>
+      </c>
+      <c r="W2" s="91">
+        <v>0</v>
+      </c>
+      <c r="X2" s="91">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="91">
+        <v>2</v>
+      </c>
+      <c r="AB2" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="91">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="91">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="91">
         <v>1</v>
       </c>
       <c r="AG2" s="47">
@@ -7534,7 +7540,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="66">
-        <f t="shared" si="0"/>
+        <f>B3/(E3+F3)</f>
         <v>9</v>
       </c>
       <c r="D3" s="47">
@@ -7547,7 +7553,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="75">
-        <f t="shared" si="1"/>
+        <f>E3/(E3+F3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="34">
@@ -7557,7 +7563,7 @@
         <v>3</v>
       </c>
       <c r="J3" s="75">
-        <f t="shared" si="2"/>
+        <f>H3/(H3+I3)</f>
         <v>0.4</v>
       </c>
       <c r="K3" s="34">
@@ -7567,7 +7573,7 @@
         <v>11</v>
       </c>
       <c r="M3" s="75">
-        <f t="shared" si="3"/>
+        <f>K3/(K3+L3)</f>
         <v>0.5</v>
       </c>
       <c r="N3" s="34">
@@ -7639,7 +7645,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="66">
-        <f t="shared" si="0"/>
+        <f>B4/(E4+F4)</f>
         <v>10.5</v>
       </c>
       <c r="D4" s="47">
@@ -7652,7 +7658,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="75">
-        <f t="shared" si="1"/>
+        <f>E4/(E4+F4)</f>
         <v>0.5</v>
       </c>
       <c r="H4" s="34">
@@ -7662,7 +7668,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="75">
-        <f t="shared" si="2"/>
+        <f>H4/(H4+I4)</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="K4" s="34">
@@ -7672,7 +7678,7 @@
         <v>20</v>
       </c>
       <c r="M4" s="75">
-        <f t="shared" si="3"/>
+        <f>K4/(K4+L4)</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="N4" s="34">
@@ -7744,7 +7750,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="66">
-        <f t="shared" si="0"/>
+        <f>B5/(E5+F5)</f>
         <v>6</v>
       </c>
       <c r="D5" s="65">
@@ -7757,7 +7763,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="75">
-        <f t="shared" si="1"/>
+        <f>E5/(E5+F5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="36">
@@ -7767,7 +7773,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="75">
-        <f t="shared" si="2"/>
+        <f>H5/(H5+I5)</f>
         <v>0.25</v>
       </c>
       <c r="K5" s="36">
@@ -7777,7 +7783,7 @@
         <v>11</v>
       </c>
       <c r="M5" s="75">
-        <f t="shared" si="3"/>
+        <f>K5/(K5+L5)</f>
         <v>0.42105263157894735</v>
       </c>
       <c r="N5" s="36">
@@ -7846,11 +7852,11 @@
         <v>35</v>
       </c>
       <c r="B6" s="34">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C6" s="66">
-        <f t="shared" si="0"/>
-        <v>11.529411764705882</v>
+        <f>B6/(E6+F6)</f>
+        <v>11.333333333333334</v>
       </c>
       <c r="D6" s="35">
         <v>20</v>
@@ -7859,31 +7865,31 @@
         <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="75">
-        <f t="shared" si="1"/>
-        <v>0.35294117647058826</v>
+        <f>E6/(E6+F6)</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H6" s="34">
         <v>32</v>
       </c>
       <c r="I6" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J6" s="75">
-        <f t="shared" si="2"/>
-        <v>0.43835616438356162</v>
+        <f>H6/(H6+I6)</f>
+        <v>0.42105263157894735</v>
       </c>
       <c r="K6" s="34">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L6" s="2">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="M6" s="75">
-        <f t="shared" si="3"/>
-        <v>0.4935064935064935</v>
+        <f>K6/(K6+L6)</f>
+        <v>0.48113207547169812</v>
       </c>
       <c r="N6" s="34">
         <v>0</v>
@@ -7954,7 +7960,7 @@
         <v>88</v>
       </c>
       <c r="C7" s="66">
-        <f t="shared" si="0"/>
+        <f>B7/(E7+F7)</f>
         <v>8</v>
       </c>
       <c r="D7" s="35">
@@ -7967,7 +7973,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="75">
-        <f t="shared" si="1"/>
+        <f>E7/(E7+F7)</f>
         <v>0.81818181818181823</v>
       </c>
       <c r="H7" s="34">
@@ -7977,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="J7" s="75">
-        <f t="shared" si="2"/>
+        <f>H7/(H7+I7)</f>
         <v>0.65217391304347827</v>
       </c>
       <c r="K7" s="34">
@@ -7987,7 +7993,7 @@
         <v>79</v>
       </c>
       <c r="M7" s="75">
-        <f t="shared" si="3"/>
+        <f>K7/(K7+L7)</f>
         <v>0.572972972972973</v>
       </c>
       <c r="N7" s="34">
@@ -8056,11 +8062,11 @@
         <v>42</v>
       </c>
       <c r="B8" s="34">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C8" s="66">
-        <f t="shared" si="0"/>
-        <v>17.100000000000001</v>
+        <f>B8/(E8+F8)</f>
+        <v>16.09090909090909</v>
       </c>
       <c r="D8" s="35">
         <v>31</v>
@@ -8069,31 +8075,31 @@
         <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="75">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
+        <f>E8/(E8+F8)</f>
+        <v>0.54545454545454541</v>
       </c>
       <c r="H8" s="34">
         <v>22</v>
       </c>
       <c r="I8" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J8" s="75">
-        <f t="shared" si="2"/>
-        <v>0.51162790697674421</v>
+        <f>H8/(H8+I8)</f>
+        <v>0.47826086956521741</v>
       </c>
       <c r="K8" s="34">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" s="2">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="M8" s="75">
-        <f t="shared" si="3"/>
-        <v>0.5056179775280899</v>
+        <f>K8/(K8+L8)</f>
+        <v>0.48404255319148937</v>
       </c>
       <c r="N8" s="34">
         <v>0</v>
@@ -8161,47 +8167,47 @@
         <v>25</v>
       </c>
       <c r="B9" s="34">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C9" s="66">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>B9/(E9+F9)</f>
+        <v>8.5</v>
       </c>
       <c r="D9" s="35">
         <v>12</v>
       </c>
       <c r="E9" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
       <c r="G9" s="75">
-        <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <f>E9/(E9+F9)</f>
+        <v>0.75</v>
       </c>
       <c r="H9" s="34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
       </c>
       <c r="J9" s="75">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f>H9/(H9+I9)</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K9" s="34">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L9" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" s="75">
-        <f t="shared" si="3"/>
-        <v>0.58695652173913049</v>
+        <f>K9/(K9+L9)</f>
+        <v>0.6428571428571429</v>
       </c>
       <c r="N9" s="34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
@@ -8219,7 +8225,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="2">
         <v>0</v>
@@ -8243,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="AB9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC9" s="2">
         <v>0</v>
@@ -8269,7 +8275,7 @@
         <v>67</v>
       </c>
       <c r="C10" s="66">
-        <f t="shared" si="0"/>
+        <f>B10/(E10+F10)</f>
         <v>13.4</v>
       </c>
       <c r="D10" s="65">
@@ -8282,7 +8288,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="75">
-        <f t="shared" si="1"/>
+        <f>E10/(E10+F10)</f>
         <v>0.2</v>
       </c>
       <c r="H10" s="36">
@@ -8292,7 +8298,7 @@
         <v>14</v>
       </c>
       <c r="J10" s="75">
-        <f t="shared" si="2"/>
+        <f>H10/(H10+I10)</f>
         <v>0.39130434782608697</v>
       </c>
       <c r="K10" s="36">
@@ -8302,7 +8308,7 @@
         <v>51</v>
       </c>
       <c r="M10" s="75">
-        <f t="shared" si="3"/>
+        <f>K10/(K10+L10)</f>
         <v>0.43333333333333335</v>
       </c>
       <c r="N10" s="36">
@@ -8374,7 +8380,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="66">
-        <f t="shared" si="0"/>
+        <f>B11/(E11+F11)</f>
         <v>14.2</v>
       </c>
       <c r="D11" s="35">
@@ -8387,7 +8393,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="75">
-        <f t="shared" si="1"/>
+        <f>E11/(E11+F11)</f>
         <v>0.4</v>
       </c>
       <c r="H11" s="34">
@@ -8397,7 +8403,7 @@
         <v>12</v>
       </c>
       <c r="J11" s="75">
-        <f t="shared" si="2"/>
+        <f>H11/(H11+I11)</f>
         <v>0.47826086956521741</v>
       </c>
       <c r="K11" s="34">
@@ -8407,7 +8413,7 @@
         <v>51</v>
       </c>
       <c r="M11" s="75">
-        <f t="shared" si="3"/>
+        <f>K11/(K11+L11)</f>
         <v>0.45744680851063829</v>
       </c>
       <c r="N11" s="34">
@@ -8479,7 +8485,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="66">
-        <f t="shared" si="0"/>
+        <f>B12/(E12+F12)</f>
         <v>3</v>
       </c>
       <c r="D12" s="65">
@@ -8492,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="75">
-        <f t="shared" si="1"/>
+        <f>E12/(E12+F12)</f>
         <v>0</v>
       </c>
       <c r="H12" s="36">
@@ -8502,7 +8508,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="75">
-        <f t="shared" si="2"/>
+        <f>H12/(H12+I12)</f>
         <v>0.4</v>
       </c>
       <c r="K12" s="36">
@@ -8512,7 +8518,7 @@
         <v>13</v>
       </c>
       <c r="M12" s="75">
-        <f t="shared" si="3"/>
+        <f>K12/(K12+L12)</f>
         <v>0.43478260869565216</v>
       </c>
       <c r="N12" s="36">
@@ -8685,7 +8691,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="66">
-        <f t="shared" ref="C14:C46" si="4">B14/(E14+F14)</f>
+        <f>B14/(E14+F14)</f>
         <v>9</v>
       </c>
       <c r="D14" s="47">
@@ -8698,7 +8704,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="75">
-        <f t="shared" ref="G14:G46" si="5">E14/(E14+F14)</f>
+        <f>E14/(E14+F14)</f>
         <v>0</v>
       </c>
       <c r="H14" s="34">
@@ -8708,7 +8714,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="75">
-        <f t="shared" ref="J14:J46" si="6">H14/(H14+I14)</f>
+        <f>H14/(H14+I14)</f>
         <v>0.25</v>
       </c>
       <c r="K14" s="34">
@@ -8718,7 +8724,7 @@
         <v>9</v>
       </c>
       <c r="M14" s="75">
-        <f t="shared" ref="M14:M46" si="7">K14/(K14+L14)</f>
+        <f>K14/(K14+L14)</f>
         <v>0.4</v>
       </c>
       <c r="N14" s="34">
@@ -8790,7 +8796,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="66">
-        <f t="shared" si="4"/>
+        <f>B15/(E15+F15)</f>
         <v>3</v>
       </c>
       <c r="D15" s="47">
@@ -8803,7 +8809,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="75">
-        <f t="shared" si="5"/>
+        <f>E15/(E15+F15)</f>
         <v>0</v>
       </c>
       <c r="H15" s="34">
@@ -8813,7 +8819,7 @@
         <v>3</v>
       </c>
       <c r="J15" s="75">
-        <f t="shared" si="6"/>
+        <f>H15/(H15+I15)</f>
         <v>0</v>
       </c>
       <c r="K15" s="34">
@@ -8823,7 +8829,7 @@
         <v>9</v>
       </c>
       <c r="M15" s="75">
-        <f t="shared" si="7"/>
+        <f>K15/(K15+L15)</f>
         <v>0.30769230769230771</v>
       </c>
       <c r="N15" s="34">
@@ -8895,7 +8901,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="66">
-        <f t="shared" si="4"/>
+        <f>B16/(E16+F16)</f>
         <v>10.666666666666666</v>
       </c>
       <c r="D16" s="35">
@@ -8908,7 +8914,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="75">
-        <f t="shared" si="5"/>
+        <f>E16/(E16+F16)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="H16" s="34">
@@ -8918,7 +8924,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="75">
-        <f t="shared" si="6"/>
+        <f>H16/(H16+I16)</f>
         <v>0.61538461538461542</v>
       </c>
       <c r="K16" s="34">
@@ -8928,7 +8934,7 @@
         <v>27</v>
       </c>
       <c r="M16" s="75">
-        <f t="shared" si="7"/>
+        <f>K16/(K16+L16)</f>
         <v>0.5423728813559322</v>
       </c>
       <c r="N16" s="34">
@@ -8997,47 +9003,47 @@
         <v>50</v>
       </c>
       <c r="B17" s="34">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C17" s="66">
-        <f t="shared" si="4"/>
-        <v>21.111111111111111</v>
+        <f>B17/(E17+F17)</f>
+        <v>20.526315789473685</v>
       </c>
       <c r="D17" s="35">
         <v>31</v>
       </c>
       <c r="E17" s="34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="2">
         <v>8</v>
       </c>
       <c r="G17" s="75">
-        <f t="shared" si="5"/>
-        <v>0.55555555555555558</v>
+        <f>E17/(E17+F17)</f>
+        <v>0.57894736842105265</v>
       </c>
       <c r="H17" s="34">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I17" s="2">
         <v>36</v>
       </c>
       <c r="J17" s="75">
-        <f t="shared" si="6"/>
-        <v>0.52631578947368418</v>
+        <f>H17/(H17+I17)</f>
+        <v>0.54430379746835444</v>
       </c>
       <c r="K17" s="34">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="L17" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M17" s="75">
-        <f t="shared" si="7"/>
-        <v>0.50609756097560976</v>
+        <f>K17/(K17+L17)</f>
+        <v>0.51775147928994081</v>
       </c>
       <c r="N17" s="34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2">
         <v>2</v>
@@ -9055,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" s="2">
         <v>1</v>
@@ -9079,7 +9085,7 @@
         <v>2</v>
       </c>
       <c r="AB17" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17" s="2">
         <v>1</v>
@@ -9105,7 +9111,7 @@
         <v>87</v>
       </c>
       <c r="C18" s="66">
-        <f t="shared" si="4"/>
+        <f>B18/(E18+F18)</f>
         <v>12.428571428571429</v>
       </c>
       <c r="D18" s="35">
@@ -9118,7 +9124,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="75">
-        <f t="shared" si="5"/>
+        <f>E18/(E18+F18)</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="H18" s="34">
@@ -9128,7 +9134,7 @@
         <v>18</v>
       </c>
       <c r="J18" s="75">
-        <f t="shared" si="6"/>
+        <f>H18/(H18+I18)</f>
         <v>0.41935483870967744</v>
       </c>
       <c r="K18" s="34">
@@ -9138,7 +9144,7 @@
         <v>68</v>
       </c>
       <c r="M18" s="75">
-        <f t="shared" si="7"/>
+        <f>K18/(K18+L18)</f>
         <v>0.43333333333333335</v>
       </c>
       <c r="N18" s="34">
@@ -9207,47 +9213,47 @@
         <v>102</v>
       </c>
       <c r="B19" s="34">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C19" s="66">
-        <f t="shared" si="4"/>
-        <v>17.5</v>
+        <f>B19/(E19+F19)</f>
+        <v>18</v>
       </c>
       <c r="D19" s="35">
         <v>31</v>
       </c>
       <c r="E19" s="34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2">
         <v>2</v>
       </c>
       <c r="G19" s="75">
-        <f t="shared" si="5"/>
-        <v>0.66666666666666663</v>
+        <f>E19/(E19+F19)</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H19" s="34">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I19" s="2">
         <v>12</v>
       </c>
       <c r="J19" s="75">
-        <f t="shared" si="6"/>
-        <v>0.55555555555555558</v>
+        <f>H19/(H19+I19)</f>
+        <v>0.6</v>
       </c>
       <c r="K19" s="34">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L19" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M19" s="75">
-        <f t="shared" si="7"/>
-        <v>0.52830188679245282</v>
+        <f>K19/(K19+L19)</f>
+        <v>0.56034482758620685</v>
       </c>
       <c r="N19" s="34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2">
         <v>0</v>
@@ -9265,7 +9271,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" s="2">
         <v>1</v>
@@ -9289,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="AB19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC19" s="2">
         <v>1</v>
@@ -9312,11 +9318,11 @@
         <v>1</v>
       </c>
       <c r="B20" s="34">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C20" s="66">
-        <f t="shared" si="4"/>
-        <v>29.111111111111111</v>
+        <f>B20/(E20+F20)</f>
+        <v>27.5</v>
       </c>
       <c r="D20" s="35">
         <v>44</v>
@@ -9325,31 +9331,31 @@
         <v>4</v>
       </c>
       <c r="F20" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="75">
-        <f t="shared" si="5"/>
-        <v>0.44444444444444442</v>
+        <f>E20/(E20+F20)</f>
+        <v>0.4</v>
       </c>
       <c r="H20" s="34">
         <v>16</v>
       </c>
       <c r="I20" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J20" s="75">
-        <f t="shared" si="6"/>
-        <v>0.42105263157894735</v>
+        <f>H20/(H20+I20)</f>
+        <v>0.3902439024390244</v>
       </c>
       <c r="K20" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L20" s="2">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="M20" s="75">
-        <f t="shared" si="7"/>
-        <v>0.46987951807228917</v>
+        <f>K20/(K20+L20)</f>
+        <v>0.44886363636363635</v>
       </c>
       <c r="N20" s="34">
         <v>1</v>
@@ -9420,7 +9426,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="66">
-        <f t="shared" si="4"/>
+        <f>B21/(E21+F21)</f>
         <v>9.5</v>
       </c>
       <c r="D21" s="65">
@@ -9433,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="75">
-        <f t="shared" si="5"/>
+        <f>E21/(E21+F21)</f>
         <v>1</v>
       </c>
       <c r="H21" s="36">
@@ -9443,7 +9449,7 @@
         <v>4</v>
       </c>
       <c r="J21" s="75">
-        <f t="shared" si="6"/>
+        <f>H21/(H21+I21)</f>
         <v>0.6</v>
       </c>
       <c r="K21" s="36">
@@ -9453,7 +9459,7 @@
         <v>19</v>
       </c>
       <c r="M21" s="75">
-        <f t="shared" si="7"/>
+        <f>K21/(K21+L21)</f>
         <v>0.55813953488372092</v>
       </c>
       <c r="N21" s="36">
@@ -9525,7 +9531,7 @@
         <v>244</v>
       </c>
       <c r="C22" s="66">
-        <f t="shared" si="4"/>
+        <f>B22/(E22+F22)</f>
         <v>20.333333333333332</v>
       </c>
       <c r="D22" s="35">
@@ -9538,7 +9544,7 @@
         <v>8</v>
       </c>
       <c r="G22" s="75">
-        <f t="shared" si="5"/>
+        <f>E22/(E22+F22)</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="H22" s="34">
@@ -9548,7 +9554,7 @@
         <v>31</v>
       </c>
       <c r="J22" s="75">
-        <f t="shared" si="6"/>
+        <f>H22/(H22+I22)</f>
         <v>0.43636363636363634</v>
       </c>
       <c r="K22" s="34">
@@ -9558,7 +9564,7 @@
         <v>116</v>
       </c>
       <c r="M22" s="75">
-        <f t="shared" si="7"/>
+        <f>K22/(K22+L22)</f>
         <v>0.49122807017543857</v>
       </c>
       <c r="N22" s="34">
@@ -9627,11 +9633,11 @@
         <v>28</v>
       </c>
       <c r="B23" s="34">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C23" s="66">
-        <f t="shared" si="4"/>
-        <v>16.2</v>
+        <f>B23/(E23+F23)</f>
+        <v>15.636363636363637</v>
       </c>
       <c r="D23" s="35">
         <v>22</v>
@@ -9640,31 +9646,31 @@
         <v>5</v>
       </c>
       <c r="F23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="75">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f>E23/(E23+F23)</f>
+        <v>0.45454545454545453</v>
       </c>
       <c r="H23" s="34">
         <v>20</v>
       </c>
       <c r="I23" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" s="75">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
+        <f>H23/(H23+I23)</f>
+        <v>0.46511627906976744</v>
       </c>
       <c r="K23" s="34">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L23" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="M23" s="75">
-        <f t="shared" si="7"/>
-        <v>0.51190476190476186</v>
+        <f>K23/(K23+L23)</f>
+        <v>0.4887640449438202</v>
       </c>
       <c r="N23" s="34">
         <v>0</v>
@@ -9732,47 +9738,47 @@
         <v>53</v>
       </c>
       <c r="B24" s="34">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C24" s="66">
-        <f t="shared" si="4"/>
-        <v>17.777777777777779</v>
+        <f>B24/(E24+F24)</f>
+        <v>17</v>
       </c>
       <c r="D24" s="35">
         <v>36</v>
       </c>
       <c r="E24" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2">
         <v>6</v>
       </c>
       <c r="G24" s="75">
-        <f t="shared" si="5"/>
-        <v>0.33333333333333331</v>
+        <f>E24/(E24+F24)</f>
+        <v>0.4</v>
       </c>
       <c r="H24" s="34">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I24" s="2">
         <v>20</v>
       </c>
       <c r="J24" s="75">
-        <f t="shared" si="6"/>
-        <v>0.44444444444444442</v>
+        <f>H24/(H24+I24)</f>
+        <v>0.48717948717948717</v>
       </c>
       <c r="K24" s="34">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L24" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M24" s="75">
-        <f t="shared" si="7"/>
-        <v>0.48</v>
+        <f>K24/(K24+L24)</f>
+        <v>0.50624999999999998</v>
       </c>
       <c r="N24" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2">
         <v>1</v>
@@ -9790,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="2">
         <v>0</v>
@@ -9814,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC24" s="2">
         <v>0</v>
@@ -9840,7 +9846,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="66">
-        <f t="shared" si="4"/>
+        <f>B25/(E25+F25)</f>
         <v>5</v>
       </c>
       <c r="D25" s="35">
@@ -9853,7 +9859,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="75">
-        <f t="shared" si="5"/>
+        <f>E25/(E25+F25)</f>
         <v>0</v>
       </c>
       <c r="H25" s="34">
@@ -9863,7 +9869,7 @@
         <v>3</v>
       </c>
       <c r="J25" s="75">
-        <f t="shared" si="6"/>
+        <f>H25/(H25+I25)</f>
         <v>0</v>
       </c>
       <c r="K25" s="34">
@@ -9873,7 +9879,7 @@
         <v>9</v>
       </c>
       <c r="M25" s="75">
-        <f t="shared" si="7"/>
+        <f>K25/(K25+L25)</f>
         <v>0.18181818181818182</v>
       </c>
       <c r="N25" s="34">
@@ -9945,7 +9951,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="66">
-        <f t="shared" si="4"/>
+        <f>B26/(E26+F26)</f>
         <v>5.25</v>
       </c>
       <c r="D26" s="35">
@@ -9958,7 +9964,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="75">
-        <f t="shared" si="5"/>
+        <f>E26/(E26+F26)</f>
         <v>0.25</v>
       </c>
       <c r="H26" s="34">
@@ -9968,7 +9974,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="75">
-        <f t="shared" si="6"/>
+        <f>H26/(H26+I26)</f>
         <v>0.42105263157894735</v>
       </c>
       <c r="K26" s="34">
@@ -9978,7 +9984,7 @@
         <v>40</v>
       </c>
       <c r="M26" s="75">
-        <f t="shared" si="7"/>
+        <f>K26/(K26+L26)</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="N26" s="34">
@@ -10050,7 +10056,7 @@
         <v>166</v>
       </c>
       <c r="C27" s="66">
-        <f t="shared" si="4"/>
+        <f>B27/(E27+F27)</f>
         <v>23.714285714285715</v>
       </c>
       <c r="D27" s="35">
@@ -10063,7 +10069,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="75">
-        <f t="shared" si="5"/>
+        <f>E27/(E27+F27)</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="H27" s="34">
@@ -10073,7 +10079,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="75">
-        <f t="shared" si="6"/>
+        <f>H27/(H27+I27)</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="K27" s="34">
@@ -10083,7 +10089,7 @@
         <v>83</v>
       </c>
       <c r="M27" s="75">
-        <f t="shared" si="7"/>
+        <f>K27/(K27+L27)</f>
         <v>0.4713375796178344</v>
       </c>
       <c r="N27" s="34">
@@ -10149,53 +10155,53 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B28" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="66">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="D28" s="47">
-        <v>3</v>
+        <f>B28/(E28+F28)</f>
+        <v>4</v>
+      </c>
+      <c r="D28" s="35">
+        <v>4</v>
       </c>
       <c r="E28" s="34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="75">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>E28/(E28+F28)</f>
+        <v>0</v>
       </c>
       <c r="H28" s="34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="75">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f>H28/(H28+I28)</f>
+        <v>0</v>
       </c>
       <c r="K28" s="34">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" s="75">
-        <f t="shared" si="7"/>
-        <v>0.6428571428571429</v>
+        <f>K28/(K28+L28)</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="N28" s="34">
         <v>0</v>
       </c>
       <c r="O28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="2">
         <v>0</v>
@@ -10206,7 +10212,7 @@
       <c r="R28" s="2">
         <v>0</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" s="1">
         <v>0</v>
       </c>
       <c r="T28" s="2">
@@ -10222,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="2">
         <v>0</v>
@@ -10240,13 +10246,13 @@
         <v>0</v>
       </c>
       <c r="AD28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="47">
         <v>0</v>
@@ -10254,59 +10260,59 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="B29" s="34">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C29" s="66">
-        <f t="shared" si="4"/>
-        <v>9.3333333333333339</v>
-      </c>
-      <c r="D29" s="35">
-        <v>12</v>
+        <f>B29/(E29+F29)</f>
+        <v>3</v>
+      </c>
+      <c r="D29" s="47">
+        <v>3</v>
       </c>
       <c r="E29" s="34">
         <v>1</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="75">
-        <f t="shared" si="5"/>
-        <v>0.33333333333333331</v>
+        <f>E29/(E29+F29)</f>
+        <v>1</v>
       </c>
       <c r="H29" s="34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J29" s="75">
-        <f t="shared" si="6"/>
-        <v>0.46666666666666667</v>
+        <f>H29/(H29+I29)</f>
+        <v>1</v>
       </c>
       <c r="K29" s="34">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="L29" s="2">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="M29" s="75">
-        <f t="shared" si="7"/>
-        <v>0.44444444444444442</v>
+        <f>K29/(K29+L29)</f>
+        <v>0.6428571428571429</v>
       </c>
       <c r="N29" s="34">
         <v>0</v>
       </c>
       <c r="O29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="2">
         <v>0</v>
@@ -10327,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="X29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="2">
         <v>0</v>
@@ -10336,16 +10342,16 @@
         <v>0</v>
       </c>
       <c r="AA29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="2">
         <v>0</v>
       </c>
       <c r="AD29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" s="2">
         <v>1</v>
@@ -10359,65 +10365,65 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B30" s="34">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C30" s="66">
-        <f t="shared" si="4"/>
-        <v>23.25</v>
+        <f>B30/(E30+F30)</f>
+        <v>8.5</v>
       </c>
       <c r="D30" s="35">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E30" s="34">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+      <c r="G30" s="75">
+        <f>E30/(E30+F30)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="34">
         <v>9</v>
       </c>
-      <c r="F30" s="2">
-        <v>7</v>
-      </c>
-      <c r="G30" s="75">
-        <f t="shared" si="5"/>
-        <v>0.5625</v>
-      </c>
-      <c r="H30" s="34">
+      <c r="I30" s="2">
+        <v>8</v>
+      </c>
+      <c r="J30" s="75">
+        <f>H30/(H30+I30)</f>
+        <v>0.52941176470588236</v>
+      </c>
+      <c r="K30" s="34">
+        <v>34</v>
+      </c>
+      <c r="L30" s="2">
         <v>36</v>
       </c>
-      <c r="I30" s="2">
-        <v>31</v>
-      </c>
-      <c r="J30" s="75">
-        <f t="shared" si="6"/>
-        <v>0.53731343283582089</v>
-      </c>
-      <c r="K30" s="34">
-        <v>139</v>
-      </c>
-      <c r="L30" s="2">
-        <v>133</v>
-      </c>
       <c r="M30" s="75">
-        <f t="shared" si="7"/>
-        <v>0.51102941176470584</v>
+        <f>K30/(K30+L30)</f>
+        <v>0.48571428571428571</v>
       </c>
       <c r="N30" s="34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R30" s="2">
         <v>0</v>
       </c>
-      <c r="S30" s="1">
-        <v>1</v>
+      <c r="S30" s="2">
+        <v>0</v>
       </c>
       <c r="T30" s="2">
         <v>0</v>
@@ -10429,124 +10435,124 @@
         <v>0</v>
       </c>
       <c r="W30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB30" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC30" s="2">
         <v>0</v>
       </c>
       <c r="AD30" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG30" s="47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="B31" s="34">
-        <v>511</v>
+        <v>372</v>
       </c>
       <c r="C31" s="66">
-        <f t="shared" si="4"/>
-        <v>26.894736842105264</v>
+        <f>B31/(E31+F31)</f>
+        <v>23.25</v>
       </c>
       <c r="D31" s="35">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E31" s="34">
+        <v>9</v>
+      </c>
+      <c r="F31" s="2">
         <v>7</v>
       </c>
-      <c r="F31" s="2">
-        <v>12</v>
-      </c>
       <c r="G31" s="75">
-        <f t="shared" si="5"/>
-        <v>0.36842105263157893</v>
+        <f>E31/(E31+F31)</f>
+        <v>0.5625</v>
       </c>
       <c r="H31" s="34">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I31" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J31" s="75">
-        <f t="shared" si="6"/>
-        <v>0.45977011494252873</v>
+        <f>H31/(H31+I31)</f>
+        <v>0.53731343283582089</v>
       </c>
       <c r="K31" s="34">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L31" s="2">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="M31" s="75">
-        <f t="shared" si="7"/>
-        <v>0.47499999999999998</v>
+        <f>K31/(K31+L31)</f>
+        <v>0.51102941176470584</v>
       </c>
       <c r="N31" s="34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2">
+        <v>1</v>
+      </c>
+      <c r="P31" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>3</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
+        <v>1</v>
+      </c>
+      <c r="T31" s="2">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2">
+        <v>1</v>
+      </c>
+      <c r="X31" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="2">
         <v>4</v>
-      </c>
-      <c r="P31" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>1</v>
-      </c>
-      <c r="R31" s="1">
-        <v>1</v>
-      </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
-      <c r="T31" s="2">
-        <v>2</v>
-      </c>
-      <c r="U31" s="2">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2">
-        <v>1</v>
-      </c>
-      <c r="W31" s="2">
-        <v>3</v>
-      </c>
-      <c r="X31" s="2">
-        <v>3</v>
-      </c>
-      <c r="Y31" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="2">
-        <v>2</v>
       </c>
       <c r="AB31" s="2">
         <v>4</v>
@@ -10555,180 +10561,180 @@
         <v>0</v>
       </c>
       <c r="AD31" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE31" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG31" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="34">
+        <v>511</v>
+      </c>
+      <c r="C32" s="66">
+        <f>B32/(E32+F32)</f>
+        <v>26.894736842105264</v>
+      </c>
+      <c r="D32" s="35">
+        <v>37</v>
+      </c>
+      <c r="E32" s="34">
+        <v>7</v>
+      </c>
+      <c r="F32" s="2">
+        <v>12</v>
+      </c>
+      <c r="G32" s="75">
+        <f>E32/(E32+F32)</f>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="H32" s="34">
+        <v>40</v>
+      </c>
+      <c r="I32" s="2">
+        <v>47</v>
+      </c>
+      <c r="J32" s="75">
+        <f>H32/(H32+I32)</f>
+        <v>0.45977011494252873</v>
+      </c>
+      <c r="K32" s="34">
+        <v>171</v>
+      </c>
+      <c r="L32" s="2">
+        <v>189</v>
+      </c>
+      <c r="M32" s="75">
+        <f>K32/(K32+L32)</f>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="N32" s="34">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2">
+        <v>4</v>
+      </c>
+      <c r="P32" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>1</v>
+      </c>
+      <c r="R32" s="1">
+        <v>1</v>
+      </c>
+      <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2">
+        <v>2</v>
+      </c>
+      <c r="U32" s="2">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2">
+        <v>1</v>
+      </c>
+      <c r="W32" s="2">
+        <v>3</v>
+      </c>
+      <c r="X32" s="2">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="2">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="2">
         <v>5</v>
       </c>
-      <c r="B32" s="34">
-        <v>111</v>
-      </c>
-      <c r="C32" s="66">
-        <f t="shared" si="4"/>
-        <v>27.75</v>
-      </c>
-      <c r="D32" s="35">
-        <v>36</v>
-      </c>
-      <c r="E32" s="34">
-        <v>3</v>
-      </c>
-      <c r="F32" s="2">
-        <v>1</v>
-      </c>
-      <c r="G32" s="75">
-        <f t="shared" si="5"/>
-        <v>0.75</v>
-      </c>
-      <c r="H32" s="34">
-        <v>12</v>
-      </c>
-      <c r="I32" s="2">
-        <v>6</v>
-      </c>
-      <c r="J32" s="75">
-        <f t="shared" si="6"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K32" s="34">
-        <v>42</v>
-      </c>
-      <c r="L32" s="2">
-        <v>35</v>
-      </c>
-      <c r="M32" s="75">
-        <f t="shared" si="7"/>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="N32" s="34">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>2</v>
-      </c>
-      <c r="P32" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>1</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>0</v>
-      </c>
-      <c r="T32" s="2">
-        <v>0</v>
-      </c>
-      <c r="U32" s="2">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2">
-        <v>0</v>
-      </c>
-      <c r="W32" s="2">
-        <v>1</v>
-      </c>
-      <c r="X32" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="2">
-        <v>2</v>
-      </c>
-      <c r="AE32" s="2">
-        <v>3</v>
-      </c>
       <c r="AF32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG32" s="47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B33" s="34">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="C33" s="66">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f>B33/(E33+F33)</f>
+        <v>27.75</v>
       </c>
       <c r="D33" s="35">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E33" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
       </c>
       <c r="G33" s="75">
-        <f t="shared" si="5"/>
-        <v>0.66666666666666663</v>
+        <f>E33/(E33+F33)</f>
+        <v>0.75</v>
       </c>
       <c r="H33" s="34">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I33" s="2">
         <v>6</v>
       </c>
       <c r="J33" s="75">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
+        <f>H33/(H33+I33)</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K33" s="34">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="L33" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M33" s="75">
-        <f t="shared" si="7"/>
-        <v>0.46808510638297873</v>
+        <f>K33/(K33+L33)</f>
+        <v>0.54545454545454541</v>
       </c>
       <c r="N33" s="34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="2">
-        <v>0</v>
-      </c>
-      <c r="R33" s="2">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1">
         <v>0</v>
       </c>
       <c r="S33" s="2">
@@ -10744,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="W33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="2">
         <v>0</v>
@@ -10765,10 +10771,10 @@
         <v>0</v>
       </c>
       <c r="AD33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE33" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF33" s="2">
         <v>1</v>
@@ -10779,80 +10785,80 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" s="34">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="C34" s="66">
-        <f t="shared" si="4"/>
-        <v>18.25</v>
+        <f>B34/(E34+F34)</f>
+        <v>3</v>
       </c>
       <c r="D34" s="35">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E34" s="34">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G34" s="75">
-        <f t="shared" si="5"/>
-        <v>0.4375</v>
+        <f>E34/(E34+F34)</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H34" s="34">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="I34" s="2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="J34" s="75">
-        <f t="shared" si="6"/>
-        <v>0.53658536585365857</v>
+        <f>H34/(H34+I34)</f>
+        <v>0.5</v>
       </c>
       <c r="K34" s="34">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="L34" s="2">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="M34" s="75">
-        <f t="shared" si="7"/>
-        <v>0.48675496688741721</v>
+        <f>K34/(K34+L34)</f>
+        <v>0.46808510638297873</v>
       </c>
       <c r="N34" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P34" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R34" s="2">
         <v>0</v>
       </c>
-      <c r="S34" s="1">
-        <v>1</v>
+      <c r="S34" s="2">
+        <v>0</v>
       </c>
       <c r="T34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2">
         <v>0</v>
       </c>
       <c r="W34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y34" s="2">
         <v>0</v>
@@ -10861,10 +10867,10 @@
         <v>0</v>
       </c>
       <c r="AA34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" s="2">
         <v>0</v>
@@ -10873,238 +10879,238 @@
         <v>1</v>
       </c>
       <c r="AE34" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG34" s="47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B35" s="34">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="C35" s="66">
-        <f t="shared" si="4"/>
-        <v>21.8</v>
+        <f>B35/(E35+F35)</f>
+        <v>17.705882352941178</v>
       </c>
       <c r="D35" s="35">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E35" s="34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="75">
-        <f t="shared" si="5"/>
-        <v>0.33333333333333331</v>
+        <f>E35/(E35+F35)</f>
+        <v>0.41176470588235292</v>
       </c>
       <c r="H35" s="34">
+        <v>44</v>
+      </c>
+      <c r="I35" s="2">
+        <v>41</v>
+      </c>
+      <c r="J35" s="75">
+        <f>H35/(H35+I35)</f>
+        <v>0.51764705882352946</v>
+      </c>
+      <c r="K35" s="34">
+        <v>148</v>
+      </c>
+      <c r="L35" s="2">
+        <v>164</v>
+      </c>
+      <c r="M35" s="75">
+        <f>K35/(K35+L35)</f>
+        <v>0.47435897435897434</v>
+      </c>
+      <c r="N35" s="34">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>5</v>
+      </c>
+      <c r="P35" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>4</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1">
+        <v>1</v>
+      </c>
+      <c r="T35" s="2">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2">
+        <v>2</v>
+      </c>
+      <c r="V35" s="2">
+        <v>0</v>
+      </c>
+      <c r="W35" s="2">
+        <v>1</v>
+      </c>
+      <c r="X35" s="2">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="2">
+        <v>3</v>
+      </c>
+      <c r="AF35" s="2">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="34">
+        <v>342</v>
+      </c>
+      <c r="C36" s="66">
+        <f>B36/(E36+F36)</f>
+        <v>21.375</v>
+      </c>
+      <c r="D36" s="35">
+        <v>32</v>
+      </c>
+      <c r="E36" s="34">
+        <v>5</v>
+      </c>
+      <c r="F36" s="2">
+        <v>11</v>
+      </c>
+      <c r="G36" s="75">
+        <f>E36/(E36+F36)</f>
+        <v>0.3125</v>
+      </c>
+      <c r="H36" s="34">
         <v>29</v>
       </c>
-      <c r="I35" s="2">
-        <v>36</v>
-      </c>
-      <c r="J35" s="75">
-        <f t="shared" si="6"/>
-        <v>0.44615384615384618</v>
-      </c>
-      <c r="K35" s="34">
-        <v>126</v>
-      </c>
-      <c r="L35" s="2">
-        <v>136</v>
-      </c>
-      <c r="M35" s="75">
-        <f t="shared" si="7"/>
-        <v>0.48091603053435117</v>
-      </c>
-      <c r="N35" s="34">
-        <v>2</v>
-      </c>
-      <c r="O35" s="2">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>3</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
-      <c r="T35" s="2">
-        <v>0</v>
-      </c>
-      <c r="U35" s="2">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2">
-        <v>0</v>
-      </c>
-      <c r="W35" s="2">
-        <v>2</v>
-      </c>
-      <c r="X35" s="2">
-        <v>2</v>
-      </c>
-      <c r="Y35" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="2">
+      <c r="I36" s="2">
+        <v>39</v>
+      </c>
+      <c r="J36" s="75">
+        <f>H36/(H36+I36)</f>
+        <v>0.4264705882352941</v>
+      </c>
+      <c r="K36" s="34">
+        <v>127</v>
+      </c>
+      <c r="L36" s="2">
+        <v>145</v>
+      </c>
+      <c r="M36" s="75">
+        <f>K36/(K36+L36)</f>
+        <v>0.46691176470588236</v>
+      </c>
+      <c r="N36" s="34">
+        <v>2</v>
+      </c>
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>3</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2">
+        <v>0</v>
+      </c>
+      <c r="W36" s="2">
+        <v>2</v>
+      </c>
+      <c r="X36" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="2">
         <v>5</v>
       </c>
-      <c r="AC35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="2">
+      <c r="AC36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="2">
         <v>4</v>
       </c>
-      <c r="AE35" s="2">
-        <v>3</v>
-      </c>
-      <c r="AF35" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG35" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="36">
-        <v>12</v>
-      </c>
-      <c r="C36" s="66">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="D36" s="65">
-        <v>12</v>
-      </c>
-      <c r="E36" s="36">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="75">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H36" s="36">
-        <v>3</v>
-      </c>
-      <c r="I36" s="1">
-        <v>2</v>
-      </c>
-      <c r="J36" s="75">
-        <f t="shared" si="6"/>
-        <v>0.6</v>
-      </c>
-      <c r="K36" s="36">
-        <v>9</v>
-      </c>
-      <c r="L36" s="1">
-        <v>10</v>
-      </c>
-      <c r="M36" s="75">
-        <f t="shared" si="7"/>
-        <v>0.47368421052631576</v>
-      </c>
-      <c r="N36" s="34">
-        <v>0</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2">
-        <v>0</v>
-      </c>
-      <c r="T36" s="1">
-        <v>0</v>
-      </c>
-      <c r="U36" s="1">
-        <v>0</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0</v>
-      </c>
-      <c r="W36" s="1">
-        <v>1</v>
-      </c>
-      <c r="X36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF36" s="1">
-        <v>0</v>
+      <c r="AE36" s="2">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="2">
+        <v>3</v>
       </c>
       <c r="AG36" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B37" s="36">
-        <v>10</v>
-      </c>
-      <c r="C37" s="1">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="C37" s="66">
+        <f>B37/(E37+F37)</f>
+        <v>12</v>
       </c>
       <c r="D37" s="65">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E37" s="36">
         <v>1</v>
@@ -11113,565 +11119,565 @@
         <v>0</v>
       </c>
       <c r="G37" s="75">
-        <f t="shared" si="5"/>
+        <f>E37/(E37+F37)</f>
         <v>1</v>
       </c>
       <c r="H37" s="36">
         <v>3</v>
       </c>
       <c r="I37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="75">
-        <f t="shared" si="6"/>
-        <v>0.75</v>
+        <f>H37/(H37+I37)</f>
+        <v>0.6</v>
       </c>
       <c r="K37" s="36">
         <v>9</v>
       </c>
       <c r="L37" s="1">
+        <v>10</v>
+      </c>
+      <c r="M37" s="75">
+        <f>K37/(K37+L37)</f>
+        <v>0.47368421052631576</v>
+      </c>
+      <c r="N37" s="34">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="1">
+        <v>0</v>
+      </c>
+      <c r="U37" s="1">
+        <v>0</v>
+      </c>
+      <c r="V37" s="1">
+        <v>0</v>
+      </c>
+      <c r="W37" s="1">
+        <v>1</v>
+      </c>
+      <c r="X37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="36">
+        <v>10</v>
+      </c>
+      <c r="C38" s="1">
+        <f>B38/(E38+F38)</f>
+        <v>10</v>
+      </c>
+      <c r="D38" s="65">
+        <v>10</v>
+      </c>
+      <c r="E38" s="36">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="75">
+        <f>E38/(E38+F38)</f>
+        <v>1</v>
+      </c>
+      <c r="H38" s="36">
+        <v>3</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="75">
+        <f>H38/(H38+I38)</f>
+        <v>0.75</v>
+      </c>
+      <c r="K38" s="36">
+        <v>9</v>
+      </c>
+      <c r="L38" s="1">
         <v>5</v>
       </c>
-      <c r="M37" s="75">
-        <f t="shared" si="7"/>
+      <c r="M38" s="75">
+        <f>K38/(K38+L38)</f>
         <v>0.6428571428571429</v>
       </c>
-      <c r="N37" s="36">
-        <v>0</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>0</v>
-      </c>
-      <c r="R37" s="1">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1">
-        <v>0</v>
-      </c>
-      <c r="T37" s="1">
-        <v>0</v>
-      </c>
-      <c r="U37" s="1">
-        <v>0</v>
-      </c>
-      <c r="V37" s="1">
-        <v>0</v>
-      </c>
-      <c r="W37" s="1">
-        <v>0</v>
-      </c>
-      <c r="X37" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="34">
-        <v>440</v>
-      </c>
-      <c r="C38" s="66">
-        <f t="shared" si="4"/>
-        <v>23.157894736842106</v>
-      </c>
-      <c r="D38" s="35">
-        <v>37</v>
-      </c>
-      <c r="E38" s="34">
-        <v>15</v>
-      </c>
-      <c r="F38" s="2">
-        <v>4</v>
-      </c>
-      <c r="G38" s="75">
-        <f t="shared" si="5"/>
-        <v>0.78947368421052633</v>
-      </c>
-      <c r="H38" s="34">
-        <v>51</v>
-      </c>
-      <c r="I38" s="2">
-        <v>30</v>
-      </c>
-      <c r="J38" s="75">
-        <f t="shared" si="6"/>
-        <v>0.62962962962962965</v>
-      </c>
-      <c r="K38" s="34">
-        <v>188</v>
-      </c>
-      <c r="L38" s="2">
-        <v>149</v>
-      </c>
-      <c r="M38" s="75">
-        <f t="shared" si="7"/>
-        <v>0.55786350148367958</v>
-      </c>
-      <c r="N38" s="34">
-        <v>2</v>
-      </c>
-      <c r="O38" s="2">
-        <v>2</v>
-      </c>
-      <c r="P38" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2">
+      <c r="N38" s="36">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
         <v>0</v>
       </c>
       <c r="S38" s="1">
         <v>0</v>
       </c>
-      <c r="T38" s="2">
-        <v>0</v>
-      </c>
-      <c r="U38" s="2">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2">
-        <v>0</v>
-      </c>
-      <c r="W38" s="2">
-        <v>1</v>
-      </c>
-      <c r="X38" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y38" s="2">
-        <v>2</v>
-      </c>
-      <c r="Z38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB38" s="2">
-        <v>7</v>
-      </c>
-      <c r="AC38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="2">
-        <v>7</v>
-      </c>
-      <c r="AE38" s="2">
-        <v>4</v>
-      </c>
-      <c r="AF38" s="2">
-        <v>5</v>
-      </c>
-      <c r="AG38" s="47">
-        <v>3</v>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B39" s="34">
-        <v>38</v>
+        <v>459</v>
       </c>
       <c r="C39" s="66">
-        <f t="shared" si="4"/>
-        <v>19</v>
+        <f>B39/(E39+F39)</f>
+        <v>22.95</v>
       </c>
       <c r="D39" s="35">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E39" s="34">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G39" s="75">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>E39/(E39+F39)</f>
+        <v>0.8</v>
       </c>
       <c r="H39" s="34">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="I39" s="2">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J39" s="75">
-        <f t="shared" si="6"/>
-        <v>0.75</v>
+        <f>H39/(H39+I39)</f>
+        <v>0.6428571428571429</v>
       </c>
       <c r="K39" s="34">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="L39" s="2">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="M39" s="75">
-        <f t="shared" si="7"/>
-        <v>0.58823529411764708</v>
+        <f>K39/(K39+L39)</f>
+        <v>0.56772334293948123</v>
       </c>
       <c r="N39" s="34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P39" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R39" s="2">
         <v>0</v>
       </c>
-      <c r="S39" s="2">
+      <c r="S39" s="1">
         <v>0</v>
       </c>
       <c r="T39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" s="2">
         <v>0</v>
       </c>
       <c r="W39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="2">
         <v>1</v>
       </c>
       <c r="AA39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB39" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD39" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE39" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF39" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG39" s="47">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B40" s="36">
-        <v>82</v>
+        <v>18</v>
+      </c>
+      <c r="B40" s="34">
+        <v>38</v>
       </c>
       <c r="C40" s="66">
-        <f t="shared" si="4"/>
-        <v>20.5</v>
-      </c>
-      <c r="D40" s="65">
-        <v>28</v>
-      </c>
-      <c r="E40" s="36">
-        <v>2</v>
-      </c>
-      <c r="F40" s="1">
-        <v>2</v>
+        <f>B40/(E40+F40)</f>
+        <v>19</v>
+      </c>
+      <c r="D40" s="35">
+        <v>24</v>
+      </c>
+      <c r="E40" s="34">
+        <v>2</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
       </c>
       <c r="G40" s="75">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="36">
-        <v>10</v>
-      </c>
-      <c r="I40" s="1">
-        <v>10</v>
+        <f>E40/(E40+F40)</f>
+        <v>1</v>
+      </c>
+      <c r="H40" s="34">
+        <v>6</v>
+      </c>
+      <c r="I40" s="2">
+        <v>2</v>
       </c>
       <c r="J40" s="75">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="K40" s="36">
-        <v>39</v>
-      </c>
-      <c r="L40" s="1">
-        <v>42</v>
+        <f>H40/(H40+I40)</f>
+        <v>0.75</v>
+      </c>
+      <c r="K40" s="34">
+        <v>20</v>
+      </c>
+      <c r="L40" s="2">
+        <v>14</v>
       </c>
       <c r="M40" s="75">
-        <f t="shared" si="7"/>
-        <v>0.48148148148148145</v>
-      </c>
-      <c r="N40" s="36">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1">
-        <v>1</v>
-      </c>
-      <c r="P40" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1">
-        <v>0</v>
-      </c>
-      <c r="T40" s="1">
-        <v>1</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0</v>
-      </c>
-      <c r="V40" s="1">
+        <f>K40/(K40+L40)</f>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="N40" s="34">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>1</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2">
         <v>0</v>
       </c>
       <c r="W40" s="2">
-        <v>1</v>
-      </c>
-      <c r="X40" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="X40" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="2">
+        <v>0</v>
       </c>
       <c r="AE40" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="65">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="47">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="34">
-        <v>158</v>
+        <v>113</v>
+      </c>
+      <c r="B41" s="36">
+        <v>82</v>
       </c>
       <c r="C41" s="66">
-        <f t="shared" si="4"/>
-        <v>17.555555555555557</v>
-      </c>
-      <c r="D41" s="35">
-        <v>25</v>
-      </c>
-      <c r="E41" s="34">
-        <v>4</v>
-      </c>
-      <c r="F41" s="2">
-        <v>5</v>
+        <f>B41/(E41+F41)</f>
+        <v>20.5</v>
+      </c>
+      <c r="D41" s="65">
+        <v>28</v>
+      </c>
+      <c r="E41" s="36">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1">
+        <v>2</v>
       </c>
       <c r="G41" s="75">
-        <f t="shared" si="5"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="H41" s="34">
-        <v>18</v>
-      </c>
-      <c r="I41" s="2">
-        <v>23</v>
+        <f>E41/(E41+F41)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="36">
+        <v>10</v>
+      </c>
+      <c r="I41" s="1">
+        <v>10</v>
       </c>
       <c r="J41" s="75">
-        <f t="shared" si="6"/>
-        <v>0.43902439024390244</v>
-      </c>
-      <c r="K41" s="34">
-        <v>79</v>
-      </c>
-      <c r="L41" s="2">
-        <v>86</v>
+        <f>H41/(H41+I41)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K41" s="36">
+        <v>39</v>
+      </c>
+      <c r="L41" s="1">
+        <v>42</v>
       </c>
       <c r="M41" s="75">
-        <f t="shared" si="7"/>
-        <v>0.47878787878787876</v>
-      </c>
-      <c r="N41" s="34">
-        <v>0</v>
-      </c>
-      <c r="O41" s="2">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>0</v>
-      </c>
-      <c r="R41" s="2">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
-        <v>0</v>
-      </c>
-      <c r="T41" s="2">
-        <v>1</v>
-      </c>
-      <c r="U41" s="2">
-        <v>1</v>
-      </c>
-      <c r="V41" s="2">
-        <v>1</v>
+        <f>K41/(K41+L41)</f>
+        <v>0.48148148148148145</v>
+      </c>
+      <c r="N41" s="36">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>0</v>
+      </c>
+      <c r="T41" s="1">
+        <v>1</v>
+      </c>
+      <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0</v>
       </c>
       <c r="W41" s="2">
         <v>1</v>
       </c>
-      <c r="X41" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="2">
-        <v>2</v>
-      </c>
-      <c r="Z41" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="2">
-        <v>4</v>
-      </c>
-      <c r="AC41" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="2">
-        <v>3</v>
+      <c r="X41" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>1</v>
       </c>
       <c r="AE41" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="47">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="65">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B42" s="34">
+        <v>169</v>
+      </c>
+      <c r="C42" s="66">
+        <f>B42/(E42+F42)</f>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D42" s="35">
         <v>25</v>
       </c>
-      <c r="C42" s="66">
-        <f t="shared" si="4"/>
-        <v>12.5</v>
-      </c>
-      <c r="D42" s="47">
-        <v>13</v>
-      </c>
       <c r="E42" s="34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" s="75">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>E42/(E42+F42)</f>
+        <v>0.5</v>
       </c>
       <c r="H42" s="34">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I42" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J42" s="75">
-        <f t="shared" si="6"/>
-        <v>0.75</v>
+        <f>H42/(H42+I42)</f>
+        <v>0.47727272727272729</v>
       </c>
       <c r="K42" s="34">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="L42" s="2">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="M42" s="75">
-        <f t="shared" si="7"/>
-        <v>0.55882352941176472</v>
+        <f>K42/(K42+L42)</f>
+        <v>0.50285714285714289</v>
       </c>
       <c r="N42" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" s="2">
         <v>0</v>
@@ -11680,43 +11686,43 @@
         <v>0</v>
       </c>
       <c r="T42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="2">
         <v>0</v>
       </c>
       <c r="Y42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA42" s="2">
         <v>1</v>
       </c>
       <c r="AB42" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF42" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG42" s="47">
         <v>0</v>
@@ -11724,428 +11730,533 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="34">
+        <v>25</v>
+      </c>
+      <c r="C43" s="66">
+        <f>B43/(E43+F43)</f>
+        <v>12.5</v>
+      </c>
+      <c r="D43" s="47">
+        <v>13</v>
+      </c>
+      <c r="E43" s="34">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="75">
+        <f>E43/(E43+F43)</f>
+        <v>1</v>
+      </c>
+      <c r="H43" s="34">
+        <v>6</v>
+      </c>
+      <c r="I43" s="2">
+        <v>2</v>
+      </c>
+      <c r="J43" s="75">
+        <f>H43/(H43+I43)</f>
+        <v>0.75</v>
+      </c>
+      <c r="K43" s="34">
+        <v>19</v>
+      </c>
+      <c r="L43" s="2">
+        <v>15</v>
+      </c>
+      <c r="M43" s="75">
+        <f>K43/(K43+L43)</f>
+        <v>0.55882352941176472</v>
+      </c>
+      <c r="N43" s="34">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2">
+        <v>1</v>
+      </c>
+      <c r="P43" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>1</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2">
+        <v>0</v>
+      </c>
+      <c r="W43" s="2">
+        <v>0</v>
+      </c>
+      <c r="X43" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG43" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="34">
+      <c r="B44" s="34">
         <v>256</v>
       </c>
-      <c r="C43" s="66">
-        <f t="shared" si="4"/>
+      <c r="C44" s="66">
+        <f>B44/(E44+F44)</f>
         <v>25.6</v>
       </c>
-      <c r="D43" s="35">
+      <c r="D44" s="35">
         <v>41</v>
       </c>
-      <c r="E43" s="34">
-        <v>3</v>
-      </c>
-      <c r="F43" s="2">
+      <c r="E44" s="34">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2">
         <v>7</v>
       </c>
-      <c r="G43" s="75">
-        <f t="shared" si="5"/>
+      <c r="G44" s="75">
+        <f>E44/(E44+F44)</f>
         <v>0.3</v>
       </c>
-      <c r="H43" s="34">
+      <c r="H44" s="34">
         <v>19</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I44" s="2">
         <v>25</v>
       </c>
-      <c r="J43" s="75">
-        <f t="shared" si="6"/>
+      <c r="J44" s="75">
+        <f>H44/(H44+I44)</f>
         <v>0.43181818181818182</v>
       </c>
-      <c r="K43" s="34">
+      <c r="K44" s="34">
         <v>86</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L44" s="2">
         <v>97</v>
       </c>
-      <c r="M43" s="75">
-        <f t="shared" si="7"/>
+      <c r="M44" s="75">
+        <f>K44/(K44+L44)</f>
         <v>0.46994535519125685</v>
       </c>
-      <c r="N43" s="34">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2">
-        <v>3</v>
-      </c>
-      <c r="P43" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>2</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
-      <c r="T43" s="2">
-        <v>1</v>
-      </c>
-      <c r="U43" s="2">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2">
-        <v>0</v>
-      </c>
-      <c r="W43" s="2">
-        <v>1</v>
-      </c>
-      <c r="X43" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="2">
+      <c r="N44" s="34">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2">
+        <v>3</v>
+      </c>
+      <c r="P44" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>2</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <v>1</v>
+      </c>
+      <c r="U44" s="2">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2">
+        <v>0</v>
+      </c>
+      <c r="W44" s="2">
+        <v>1</v>
+      </c>
+      <c r="X44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2">
         <v>4</v>
       </c>
-      <c r="AB43" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE43" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF43" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG43" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="AB44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE44" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B44" s="36">
+      <c r="B45" s="36">
         <v>85</v>
       </c>
-      <c r="C44" s="66">
-        <f t="shared" si="4"/>
+      <c r="C45" s="66">
+        <f>B45/(E45+F45)</f>
         <v>14.166666666666666</v>
       </c>
-      <c r="D44" s="65">
+      <c r="D45" s="65">
         <v>24</v>
       </c>
-      <c r="E44" s="36">
-        <v>3</v>
-      </c>
-      <c r="F44" s="1">
-        <v>3</v>
-      </c>
-      <c r="G44" s="75">
-        <f t="shared" si="5"/>
+      <c r="E45" s="36">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3</v>
+      </c>
+      <c r="G45" s="75">
+        <f>E45/(E45+F45)</f>
         <v>0.5</v>
       </c>
-      <c r="H44" s="36">
+      <c r="H45" s="36">
         <v>15</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I45" s="1">
         <v>13</v>
       </c>
-      <c r="J44" s="75">
-        <f t="shared" si="6"/>
+      <c r="J45" s="75">
+        <f>H45/(H45+I45)</f>
         <v>0.5357142857142857</v>
       </c>
-      <c r="K44" s="36">
+      <c r="K45" s="36">
         <v>65</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L45" s="1">
         <v>61</v>
       </c>
-      <c r="M44" s="75">
-        <f t="shared" si="7"/>
+      <c r="M45" s="75">
+        <f>K45/(K45+L45)</f>
         <v>0.51587301587301593</v>
       </c>
-      <c r="N44" s="34">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>3</v>
-      </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>1</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="1">
-        <v>0</v>
-      </c>
-      <c r="X44" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y44" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC44" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF44" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG44" s="47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="N45" s="34">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>3</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>1</v>
+      </c>
+      <c r="V45" s="1">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>2</v>
+      </c>
+      <c r="AF45" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="34">
+      <c r="B46" s="34">
         <v>18</v>
       </c>
-      <c r="C45" s="66">
-        <f t="shared" si="4"/>
+      <c r="C46" s="66">
+        <f>B46/(E46+F46)</f>
         <v>18</v>
       </c>
-      <c r="D45" s="47">
+      <c r="D46" s="47">
         <v>18</v>
       </c>
-      <c r="E45" s="34">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="75">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H45" s="34">
-        <v>3</v>
-      </c>
-      <c r="I45" s="2">
-        <v>2</v>
-      </c>
-      <c r="J45" s="75">
-        <f t="shared" si="6"/>
+      <c r="E46" s="34">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="75">
+        <f>E46/(E46+F46)</f>
+        <v>1</v>
+      </c>
+      <c r="H46" s="34">
+        <v>3</v>
+      </c>
+      <c r="I46" s="2">
+        <v>2</v>
+      </c>
+      <c r="J46" s="75">
+        <f>H46/(H46+I46)</f>
         <v>0.6</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K46" s="34">
         <v>11</v>
       </c>
-      <c r="L45" s="2">
+      <c r="L46" s="2">
         <v>10</v>
       </c>
-      <c r="M45" s="75">
-        <f t="shared" si="7"/>
+      <c r="M46" s="75">
+        <f>K46/(K46+L46)</f>
         <v>0.52380952380952384</v>
       </c>
-      <c r="N45" s="34">
-        <v>0</v>
-      </c>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>0</v>
-      </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2">
-        <v>0</v>
-      </c>
-      <c r="U45" s="2">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2">
-        <v>0</v>
-      </c>
-      <c r="W45" s="2">
-        <v>0</v>
-      </c>
-      <c r="X45" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="N46" s="34">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2">
+        <v>0</v>
+      </c>
+      <c r="W46" s="2">
+        <v>0</v>
+      </c>
+      <c r="X46" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="38">
+      <c r="B47" s="38">
         <v>6</v>
       </c>
-      <c r="C46" s="67">
-        <f t="shared" si="4"/>
+      <c r="C47" s="67">
+        <f>B47/(E47+F47)</f>
         <v>6</v>
       </c>
-      <c r="D46" s="40">
+      <c r="D47" s="40">
         <v>6</v>
       </c>
-      <c r="E46" s="38">
-        <v>0</v>
-      </c>
-      <c r="F46" s="48">
-        <v>1</v>
-      </c>
-      <c r="G46" s="76">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="38">
-        <v>0</v>
-      </c>
-      <c r="I46" s="48">
-        <v>3</v>
-      </c>
-      <c r="J46" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="38">
+      <c r="E47" s="38">
+        <v>0</v>
+      </c>
+      <c r="F47" s="48">
+        <v>1</v>
+      </c>
+      <c r="G47" s="76">
+        <f>E47/(E47+F47)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="38">
+        <v>0</v>
+      </c>
+      <c r="I47" s="48">
+        <v>3</v>
+      </c>
+      <c r="J47" s="76">
+        <f>H47/(H47+I47)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="38">
         <v>4</v>
       </c>
-      <c r="L46" s="48">
+      <c r="L47" s="48">
         <v>9</v>
       </c>
-      <c r="M46" s="76">
-        <f t="shared" si="7"/>
+      <c r="M47" s="76">
+        <f>K47/(K47+L47)</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="N46" s="38">
-        <v>0</v>
-      </c>
-      <c r="O46" s="48">
-        <v>0</v>
-      </c>
-      <c r="P46" s="48">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="48">
-        <v>0</v>
-      </c>
-      <c r="R46" s="48">
-        <v>0</v>
-      </c>
-      <c r="S46" s="48">
-        <v>0</v>
-      </c>
-      <c r="T46" s="48">
-        <v>0</v>
-      </c>
-      <c r="U46" s="48">
-        <v>0</v>
-      </c>
-      <c r="V46" s="48">
-        <v>0</v>
-      </c>
-      <c r="W46" s="48">
-        <v>0</v>
-      </c>
-      <c r="X46" s="48">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="48">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="48">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="49">
+      <c r="N47" s="38">
+        <v>0</v>
+      </c>
+      <c r="O47" s="48">
+        <v>0</v>
+      </c>
+      <c r="P47" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="48">
+        <v>0</v>
+      </c>
+      <c r="R47" s="48">
+        <v>0</v>
+      </c>
+      <c r="S47" s="48">
+        <v>0</v>
+      </c>
+      <c r="T47" s="48">
+        <v>0</v>
+      </c>
+      <c r="U47" s="48">
+        <v>0</v>
+      </c>
+      <c r="V47" s="48">
+        <v>0</v>
+      </c>
+      <c r="W47" s="48">
+        <v>0</v>
+      </c>
+      <c r="X47" s="48">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="48">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="48">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="49">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG46" xr:uid="{DA548192-1F03-46EA-8AB8-115EB9A7CE5D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG46">
-      <sortCondition ref="A1:A46"/>
+  <autoFilter ref="A1:AG47" xr:uid="{DA548192-1F03-46EA-8AB8-115EB9A7CE5D}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG47">
+      <sortCondition ref="A1:A47"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12374,131 +12485,131 @@
         <v>37</v>
       </c>
       <c r="C3" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>95</v>
       </c>
       <c r="D3" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>13.571428571428571</v>
       </c>
       <c r="E3" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>19</v>
       </c>
       <c r="F3" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="G3" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
       <c r="H3" s="73">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="I3" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>17</v>
       </c>
       <c r="J3" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>14</v>
       </c>
       <c r="K3" s="73">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0.54838709677419351</v>
       </c>
       <c r="L3" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>69</v>
       </c>
       <c r="M3" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>62</v>
       </c>
       <c r="N3" s="73">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0.52671755725190839</v>
       </c>
       <c r="O3" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P3" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Q3" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="R3" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="S3" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T3" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="U3" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="V3" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="W3" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X3" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Y3" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Z3" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AA3" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AB3" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC3" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AD3" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE3" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AF3" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG3" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH3" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$3,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -12508,131 +12619,131 @@
         <v>37</v>
       </c>
       <c r="C4" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>95</v>
       </c>
       <c r="D4" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>13.571428571428571</v>
       </c>
       <c r="E4" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>19</v>
       </c>
       <c r="F4" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="G4" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
       <c r="H4" s="73">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="I4" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>17</v>
       </c>
       <c r="J4" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>14</v>
       </c>
       <c r="K4" s="73">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0.54838709677419351</v>
       </c>
       <c r="L4" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>69</v>
       </c>
       <c r="M4" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>62</v>
       </c>
       <c r="N4" s="73">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0.52671755725190839</v>
       </c>
       <c r="O4" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P4" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Q4" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="R4" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="S4" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T4" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="U4" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="V4" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="W4" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X4" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Y4" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Z4" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AA4" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AB4" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC4" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AD4" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE4" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AF4" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG4" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH4" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$4,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -12642,131 +12753,131 @@
         <v>35</v>
       </c>
       <c r="C5" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>196</v>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>204</v>
       </c>
       <c r="D5" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>11.529411764705882</v>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>11.333333333333334</v>
       </c>
       <c r="E5" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>20</v>
       </c>
       <c r="F5" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>6</v>
       </c>
       <c r="G5" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>11</v>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>12</v>
       </c>
       <c r="H5" s="73">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>0.35294117647058826</v>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I5" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>32</v>
       </c>
       <c r="J5" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>41</v>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>44</v>
       </c>
       <c r="K5" s="73">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>0.43835616438356162</v>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>0.42105263157894735</v>
       </c>
       <c r="L5" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>152</v>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>153</v>
       </c>
       <c r="M5" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>156</v>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>165</v>
       </c>
       <c r="N5" s="73">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
-        <v>0.4935064935064935</v>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
+        <v>0.48113207547169812</v>
       </c>
       <c r="O5" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="P5" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Q5" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="R5" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
       <c r="S5" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="T5" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="U5" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="V5" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="W5" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X5" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
       <c r="Y5" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Z5" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AA5" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AB5" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AC5" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD5" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE5" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AF5" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG5" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH5" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$5,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -12776,131 +12887,131 @@
         <v>19</v>
       </c>
       <c r="C6" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>88</v>
       </c>
       <c r="D6" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>8</v>
       </c>
       <c r="E6" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>11</v>
       </c>
       <c r="F6" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>9</v>
       </c>
       <c r="G6" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="H6" s="73">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0.81818181818181823</v>
       </c>
       <c r="I6" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>30</v>
       </c>
       <c r="J6" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>16</v>
       </c>
       <c r="K6" s="73">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0.65217391304347827</v>
       </c>
       <c r="L6" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>106</v>
       </c>
       <c r="M6" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>79</v>
       </c>
       <c r="N6" s="73">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0.572972972972973</v>
       </c>
       <c r="O6" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="P6" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Q6" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="R6" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="S6" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="T6" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>5</v>
       </c>
       <c r="U6" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="V6" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="W6" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X6" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="Y6" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Z6" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AA6" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AB6" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AC6" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AD6" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE6" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AF6" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG6" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH6" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$6,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -12910,131 +13021,131 @@
         <v>25</v>
       </c>
       <c r="C7" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>24</v>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>34</v>
       </c>
       <c r="D7" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>8</v>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>8.5</v>
       </c>
       <c r="E7" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>12</v>
       </c>
       <c r="F7" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>2</v>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>3</v>
       </c>
       <c r="G7" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="H7" s="73">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>0.75</v>
+      </c>
+      <c r="I7" s="13">
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>10</v>
+      </c>
+      <c r="J7" s="26">
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>5</v>
+      </c>
+      <c r="K7" s="73">
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="I7" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>7</v>
-      </c>
-      <c r="J7" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>5</v>
-      </c>
-      <c r="K7" s="73">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>0.58333333333333337</v>
-      </c>
       <c r="L7" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>27</v>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>36</v>
       </c>
       <c r="M7" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>19</v>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>20</v>
       </c>
       <c r="N7" s="73">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>0.58695652173913049</v>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>0.6428571428571429</v>
       </c>
       <c r="O7" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P7" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Q7" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R7" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>2</v>
       </c>
       <c r="S7" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>1</v>
       </c>
       <c r="T7" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="U7" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="V7" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="W7" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="X7" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Y7" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Z7" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AA7" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AB7" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC7" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
+        <v>2</v>
       </c>
       <c r="AD7" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE7" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF7" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG7" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AH7" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$7,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -13044,131 +13155,131 @@
         <v>27</v>
       </c>
       <c r="C8" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>71</v>
       </c>
       <c r="D8" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>14.2</v>
       </c>
       <c r="E8" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>20</v>
       </c>
       <c r="F8" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="G8" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="H8" s="73">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0.4</v>
       </c>
       <c r="I8" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>11</v>
       </c>
       <c r="J8" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>12</v>
       </c>
       <c r="K8" s="73">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0.47826086956521741</v>
       </c>
       <c r="L8" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>43</v>
       </c>
       <c r="M8" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>51</v>
       </c>
       <c r="N8" s="73">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0.45744680851063829</v>
       </c>
       <c r="O8" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P8" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Q8" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R8" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="S8" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T8" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="U8" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="V8" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="W8" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="X8" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Y8" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Z8" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AA8" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB8" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC8" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD8" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE8" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF8" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG8" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH8" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$8,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -13178,131 +13289,131 @@
         <v>78</v>
       </c>
       <c r="C9" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="D9" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="E9" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="G9" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="H9" s="73" t="str">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="I9" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="J9" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="K9" s="73" t="str">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="L9" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="M9" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="N9" s="73" t="str">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="O9" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P9" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Q9" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R9" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="S9" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T9" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="U9" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="V9" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="W9" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="X9" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Y9" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Z9" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AA9" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB9" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC9" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD9" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE9" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF9" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG9" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH9" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$9,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -13312,152 +13423,152 @@
         <v>78</v>
       </c>
       <c r="C10" s="17">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="D10" s="60">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="E10" s="18">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="F10" s="17">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="G10" s="29">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="H10" s="74" t="str">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="I10" s="17">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="J10" s="29">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="K10" s="74" t="str">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="L10" s="17">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="M10" s="29">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="N10" s="74" t="str">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="O10" s="17">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P10" s="29">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Q10" s="29">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R10" s="29">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="S10" s="29">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T10" s="29">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="U10" s="29">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="V10" s="29">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="W10" s="29">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="X10" s="29">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Y10" s="29">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Z10" s="29">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AA10" s="29">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB10" s="29">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC10" s="29">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD10" s="29">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE10" s="29">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF10" s="29">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG10" s="29">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH10" s="18">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$10,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="D11" s="8">
         <f>SUM(D3:D10)</f>
-        <v>68.872268907563026</v>
+        <v>69.17619047619047</v>
       </c>
       <c r="H11" s="9">
         <f>AVERAGE(H3:H10)</f>
-        <v>0.51582208641032168</v>
+        <v>0.52644300144300138</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="9">
         <f>AVERAGE(K3:K10)</f>
-        <v>0.54148307897899628</v>
+        <v>0.55248804573378274</v>
       </c>
       <c r="N11" s="9">
         <f>AVERAGE(N3:N10)</f>
-        <v>0.52738631853884199</v>
+        <v>0.53464068571937817</v>
       </c>
       <c r="O11" s="5">
         <f>SUM(O3:O10)</f>
@@ -13473,11 +13584,11 @@
       </c>
       <c r="R11" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="0"/>
@@ -13517,7 +13628,7 @@
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="0"/>
@@ -13694,131 +13805,131 @@
         <v>35</v>
       </c>
       <c r="C17" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>196</v>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>204</v>
       </c>
       <c r="D17" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>11.529411764705882</v>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>11.333333333333334</v>
       </c>
       <c r="E17" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>20</v>
       </c>
       <c r="F17" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>6</v>
       </c>
       <c r="G17" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>11</v>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>12</v>
       </c>
       <c r="H17" s="27">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>0.35294117647058826</v>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I17" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>32</v>
       </c>
       <c r="J17" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>41</v>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>44</v>
       </c>
       <c r="K17" s="27">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>0.43835616438356162</v>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>0.42105263157894735</v>
       </c>
       <c r="L17" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>152</v>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>153</v>
       </c>
       <c r="M17" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>156</v>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>165</v>
       </c>
       <c r="N17" s="27">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
-        <v>0.4935064935064935</v>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
+        <v>0.48113207547169812</v>
       </c>
       <c r="O17" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="P17" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Q17" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="R17" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
       <c r="S17" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="T17" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="U17" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="V17" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="W17" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X17" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
       <c r="Y17" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Z17" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AA17" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AB17" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AC17" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD17" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE17" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AF17" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG17" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH17" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$17,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -13828,131 +13939,131 @@
         <v>42</v>
       </c>
       <c r="C18" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>171</v>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>177</v>
       </c>
       <c r="D18" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>17.100000000000001</v>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>16.09090909090909</v>
       </c>
       <c r="E18" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>31</v>
       </c>
       <c r="F18" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>6</v>
       </c>
       <c r="G18" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>5</v>
+      </c>
+      <c r="H18" s="27">
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="I18" s="13">
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>22</v>
+      </c>
+      <c r="J18" s="26">
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>24</v>
+      </c>
+      <c r="K18" s="27">
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>0.47826086956521741</v>
+      </c>
+      <c r="L18" s="13">
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>91</v>
+      </c>
+      <c r="M18" s="26">
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>97</v>
+      </c>
+      <c r="N18" s="27">
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>0.48404255319148937</v>
+      </c>
+      <c r="O18" s="13">
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="26">
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>2</v>
+      </c>
+      <c r="Q18" s="26">
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="26">
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>3</v>
+      </c>
+      <c r="S18" s="26">
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="26">
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="26">
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V18" s="26">
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>2</v>
+      </c>
+      <c r="W18" s="26">
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>1</v>
+      </c>
+      <c r="X18" s="26">
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>1</v>
+      </c>
+      <c r="Y18" s="26">
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="26">
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>4</v>
       </c>
-      <c r="H18" s="27">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0.6</v>
-      </c>
-      <c r="I18" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>22</v>
-      </c>
-      <c r="J18" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>21</v>
-      </c>
-      <c r="K18" s="27">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0.51162790697674421</v>
-      </c>
-      <c r="L18" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>90</v>
-      </c>
-      <c r="M18" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>88</v>
-      </c>
-      <c r="N18" s="27">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0.5056179775280899</v>
-      </c>
-      <c r="O18" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>2</v>
-      </c>
-      <c r="Q18" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
-      </c>
-      <c r="R18" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>3</v>
-      </c>
-      <c r="S18" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
-      </c>
-      <c r="T18" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>2</v>
-      </c>
-      <c r="V18" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>2</v>
-      </c>
-      <c r="W18" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
-      </c>
-      <c r="X18" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Y18" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
-        <v>4</v>
-      </c>
       <c r="AA18" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AB18" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC18" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD18" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AE18" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AF18" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AG18" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH18" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$18,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -13962,131 +14073,131 @@
         <v>52</v>
       </c>
       <c r="C19" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>87</v>
       </c>
       <c r="D19" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>12.428571428571429</v>
       </c>
       <c r="E19" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>19</v>
       </c>
       <c r="F19" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="G19" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>5</v>
       </c>
       <c r="H19" s="27">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="I19" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>13</v>
       </c>
       <c r="J19" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>18</v>
       </c>
       <c r="K19" s="27">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0.41935483870967744</v>
       </c>
       <c r="L19" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>52</v>
       </c>
       <c r="M19" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>68</v>
       </c>
       <c r="N19" s="27">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0.43333333333333335</v>
       </c>
       <c r="O19" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P19" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Q19" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R19" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="S19" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T19" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="U19" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="V19" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="W19" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="X19" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Y19" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Z19" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AA19" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB19" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC19" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD19" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE19" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF19" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG19" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH19" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$19,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14096,131 +14207,131 @@
         <v>19</v>
       </c>
       <c r="C20" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>88</v>
       </c>
       <c r="D20" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>8</v>
       </c>
       <c r="E20" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>11</v>
       </c>
       <c r="F20" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>9</v>
       </c>
       <c r="G20" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="H20" s="27">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0.81818181818181823</v>
       </c>
       <c r="I20" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>30</v>
       </c>
       <c r="J20" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>16</v>
       </c>
       <c r="K20" s="27">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0.65217391304347827</v>
       </c>
       <c r="L20" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>106</v>
       </c>
       <c r="M20" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>79</v>
       </c>
       <c r="N20" s="27">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0.572972972972973</v>
       </c>
       <c r="O20" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="P20" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Q20" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="R20" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="S20" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="T20" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>5</v>
       </c>
       <c r="U20" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="V20" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="W20" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X20" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="Y20" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Z20" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AA20" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AB20" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AC20" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AD20" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE20" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AF20" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG20" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH20" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$20,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14230,131 +14341,131 @@
         <v>3</v>
       </c>
       <c r="C21" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>166</v>
       </c>
       <c r="D21" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>23.714285714285715</v>
       </c>
       <c r="E21" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>27</v>
       </c>
       <c r="F21" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="G21" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>5</v>
       </c>
       <c r="H21" s="27">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="I21" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>16</v>
       </c>
       <c r="J21" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>20</v>
       </c>
       <c r="K21" s="27">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="L21" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>74</v>
       </c>
       <c r="M21" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>83</v>
       </c>
       <c r="N21" s="27">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0.4713375796178344</v>
       </c>
       <c r="O21" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P21" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Q21" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R21" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="S21" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T21" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="U21" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="V21" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="W21" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="X21" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="Y21" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Z21" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AA21" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB21" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC21" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD21" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE21" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF21" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG21" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AH21" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$21,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14364,131 +14475,131 @@
         <v>14</v>
       </c>
       <c r="C22" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>158</v>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>169</v>
       </c>
       <c r="D22" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>17.555555555555557</v>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>16.899999999999999</v>
       </c>
       <c r="E22" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>25</v>
       </c>
       <c r="F22" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>4</v>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>5</v>
       </c>
       <c r="G22" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>5</v>
       </c>
       <c r="H22" s="27">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>0.44444444444444442</v>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>0.5</v>
       </c>
       <c r="I22" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>18</v>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>21</v>
       </c>
       <c r="J22" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>23</v>
       </c>
       <c r="K22" s="27">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>0.43902439024390244</v>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>0.47727272727272729</v>
       </c>
       <c r="L22" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>79</v>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>88</v>
       </c>
       <c r="M22" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>86</v>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>87</v>
       </c>
       <c r="N22" s="27">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>0.47878787878787876</v>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>0.50285714285714289</v>
       </c>
       <c r="O22" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="P22" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Q22" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="R22" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>4</v>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>5</v>
       </c>
       <c r="S22" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>1</v>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>2</v>
       </c>
       <c r="T22" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>3</v>
       </c>
       <c r="U22" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="V22" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="W22" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="X22" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="Y22" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="Z22" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AA22" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB22" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AC22" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
-        <v>0</v>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
+        <v>1</v>
       </c>
       <c r="AD22" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>2</v>
       </c>
       <c r="AE22" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF22" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>1</v>
       </c>
       <c r="AG22" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH22" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$22,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14498,131 +14609,131 @@
         <v>80</v>
       </c>
       <c r="C23" s="13">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="D23" s="59">
-        <f>INDEX(BA!C2:C45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!C2:C46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="E23" s="14">
-        <f>INDEX(BA!D2:D45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!D2:D46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <f>INDEX(BA!E2:E45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!E2:E46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="G23" s="26">
-        <f>INDEX(BA!F2:F45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!F2:F46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="H23" s="27" t="str">
-        <f>INDEX(BA!G2:G45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!G2:G46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="I23" s="13">
-        <f>INDEX(BA!H2:H45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!H2:H46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="J23" s="26">
-        <f>INDEX(BA!I2:I45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!I2:I46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="K23" s="27" t="str">
-        <f>INDEX(BA!J2:J45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!J2:J46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="L23" s="13">
-        <f>INDEX(BA!K2:K45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!K2:K46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="M23" s="26">
-        <f>INDEX(BA!L2:L45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!L2:L46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="N23" s="27" t="str">
-        <f>INDEX(BA!M2:M45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!M2:M46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>-</v>
       </c>
       <c r="O23" s="13">
-        <f>INDEX(BA!V2:V45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!V2:V46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="P23" s="26">
-        <f>INDEX(BA!Q2:Q45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Q2:Q46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Q23" s="26">
-        <f>INDEX(BA!U2:U45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!U2:U46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="R23" s="26">
-        <f>INDEX(BA!AB2:AB45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AB2:AB46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="S23" s="26">
-        <f>INDEX(BA!T2:T45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!T2:T46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="T23" s="26">
-        <f>INDEX(BA!AD2:AD45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AD2:AD46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="U23" s="26">
-        <f>INDEX(BA!AA2:AA45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AA2:AA46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="V23" s="26">
-        <f>INDEX(BA!AF2:AF45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AF2:AF46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="W23" s="26">
-        <f>INDEX(BA!P2:P45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!P2:P46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="X23" s="26">
-        <f>INDEX(BA!AE2:AE45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AE2:AE46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Y23" s="26">
-        <f>INDEX(BA!W2:W45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!W2:W46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="Z23" s="26">
-        <f>INDEX(BA!O2:O45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!O2:O46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AA23" s="26">
-        <f>INDEX(BA!X2:X45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!X2:X46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AB23" s="26">
-        <f>INDEX(BA!Z2:Z45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Z2:Z46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AC23" s="26">
-        <f>INDEX(BA!N2:N45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!N2:N46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AD23" s="26">
-        <f>INDEX(BA!Y2:Y45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!Y2:Y46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AE23" s="26">
-        <f>INDEX(BA!AG2:AG45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AG2:AG46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AF23" s="26">
-        <f>INDEX(BA!AC2:AC45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!AC2:AC46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AG23" s="26">
-        <f>INDEX(BA!S2:S45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!S2:S46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="AH23" s="14">
-        <f>INDEX(BA!R2:R45,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!R2:R46,MATCH('Match Analyzer BA'!$B$23,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14632,7 +14743,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="17">
-        <f>INDEX(BA!B2:B45,MATCH('Match Analyzer BA'!$B$24,BA!$A$2:$A$45,0))</f>
+        <f>INDEX(BA!B2:B46,MATCH('Match Analyzer BA'!$B$24,BA!$A$2:$A$46,0))</f>
         <v>0</v>
       </c>
       <c r="D24" s="60">
@@ -14763,21 +14874,21 @@
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="D25" s="8">
         <f>SUM(D17:D24)</f>
-        <v>90.327824463118588</v>
+        <v>88.467099567099581</v>
       </c>
       <c r="H25" s="9">
         <f>AVERAGE(H17:H24)</f>
-        <v>0.46449933508757041</v>
+        <v>0.46139971139971142</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="9">
         <f>AVERAGE(K17:K24)</f>
-        <v>0.48416360963363475</v>
+        <v>0.48209323743574872</v>
       </c>
       <c r="N25" s="9">
         <f>AVERAGE(N17:N24)</f>
-        <v>0.49259270595776722</v>
+        <v>0.49094594290741184</v>
       </c>
       <c r="O25" s="5">
         <f>SUM(O17:O24)</f>
@@ -14793,11 +14904,11 @@
       </c>
       <c r="R25" s="5">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S25" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" s="5">
         <f t="shared" si="1"/>
@@ -14837,7 +14948,7 @@
       </c>
       <c r="AC25" s="5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD25" s="5" t="e">
         <f t="shared" si="1"/>
@@ -14958,7 +15069,7 @@
       </c>
       <c r="C36" s="17" t="str">
         <f>INDEX(O2:AC2, MATCH(LARGE(O11:AC11, 3), O11:AC11, 0))</f>
-        <v>Presidio</v>
+        <v>Streets of Milan</v>
       </c>
       <c r="D36" s="18" t="str">
         <f>INDEX(O16:AC16, MATCH(LARGE(O25:AC25, 3), O25:AC25, 0))</f>
@@ -15007,13 +15118,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Team Builder" prompt="Select Player name from drop down list" xr:uid="{E3F0B27D-B9F0-4BB5-8456-75066D0F630B}">
           <x14:formula1>
-            <xm:f>BA!$A$2:$A$45</xm:f>
+            <xm:f>BA!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>B17:B24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="Select Player Name" prompt="Select Player Name" xr:uid="{7CF85145-1224-4D7F-A47C-6F9DFE0593DF}">
           <x14:formula1>
-            <xm:f>BA!$A$2:$A$45</xm:f>
+            <xm:f>BA!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B10</xm:sqref>
         </x14:dataValidation>
